--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -820,7 +820,7 @@
         <v>34</v>
       </c>
       <c r="AA2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="n">
         <v>13</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
@@ -972,149 +972,149 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>1.98</v>
+        <v>3.95</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U3" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W3" t="n">
         <v>2.74</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Z3" t="n">
         <v>80</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
         <v>36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG3" t="n">
-        <v>12</v>
-      </c>
       <c r="AH3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AK3" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AL3" t="n">
         <v>48</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.54</v>
+        <v>6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.64</v>
+        <v>18</v>
       </c>
       <c r="AR3" t="n">
-        <v>46</v>
+        <v>7.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.9</v>
+        <v>8.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.22</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AV3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>2.64</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.46</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.54</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.74</v>
+        <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.9</v>
+        <v>8.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G4" t="n">
         <v>2.02</v>
@@ -1160,7 +1160,7 @@
         <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>3.2</v>
       </c>
       <c r="G5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="I5" t="n">
-        <v>3.15</v>
+        <v>2.52</v>
       </c>
       <c r="J5" t="n">
         <v>2.74</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.02</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G6" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="H6" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I6" t="n">
         <v>3.75</v>
       </c>
       <c r="J6" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
         <v>3.45</v>
@@ -1566,7 +1566,7 @@
         <v>1.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>3.25</v>
       </c>
       <c r="I16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J16" t="n">
         <v>3.5</v>
@@ -3500,7 +3500,7 @@
         <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P16" t="n">
         <v>2.12</v>
@@ -3530,13 +3530,13 @@
         <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB16" t="n">
         <v>12.5</v>
@@ -3548,7 +3548,7 @@
         <v>14.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF16" t="n">
         <v>17</v>
@@ -3560,7 +3560,7 @@
         <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AJ16" t="n">
         <v>42</v>
@@ -3590,7 +3590,7 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AT16" t="n">
         <v>10.5</v>
@@ -3602,7 +3602,7 @@
         <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX16" t="n">
         <v>15</v>
@@ -3632,11 +3632,11 @@
         <v>15.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.94</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="X2" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN2" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="AO2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF2" t="n">
         <v>13</v>
       </c>
-      <c r="AC2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW2" t="n">
+      <c r="BG2" t="n">
         <v>30</v>
       </c>
-      <c r="AX2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.74</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="H3" t="n">
         <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
@@ -978,10 +978,10 @@
         <v>3.95</v>
       </c>
       <c r="O3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>1.84</v>
@@ -990,10 +990,10 @@
         <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T3" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
         <v>1.83</v>
@@ -1002,34 +1002,34 @@
         <v>1.12</v>
       </c>
       <c r="W3" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="X3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y3" t="n">
         <v>25</v>
       </c>
       <c r="Z3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AA3" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC3" t="n">
         <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
         <v>150</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
@@ -1044,7 +1044,7 @@
         <v>14</v>
       </c>
       <c r="AK3" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AL3" t="n">
         <v>48</v>
@@ -1056,19 +1056,19 @@
         <v>8.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>18</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.8</v>
+        <v>55</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>7</v>
@@ -1077,10 +1077,10 @@
         <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX3" t="n">
         <v>7.4</v>
@@ -1092,7 +1092,7 @@
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB3" t="n">
         <v>11</v>
@@ -1104,17 +1104,17 @@
         <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF3" t="n">
         <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>4.8</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J4" t="n">
         <v>3.25</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="H5" t="n">
-        <v>1.26</v>
+        <v>2.16</v>
       </c>
       <c r="I5" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G6" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H6" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I6" t="n">
         <v>3.75</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="G9" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="G10" t="n">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>2.86</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="G16" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="H16" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J16" t="n">
         <v>3.5</v>
@@ -3506,7 +3506,7 @@
         <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R16" t="n">
         <v>1.44</v>
@@ -3533,22 +3533,22 @@
         <v>14.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA16" t="n">
         <v>65</v>
       </c>
       <c r="AB16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AF16" t="n">
         <v>17</v>
@@ -3563,25 +3563,25 @@
         <v>44</v>
       </c>
       <c r="AJ16" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AK16" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM16" t="n">
         <v>80</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>13</v>
@@ -3590,13 +3590,13 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
         <v>12.5</v>
@@ -3614,7 +3614,7 @@
         <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BB16" t="n">
         <v>30</v>
@@ -3623,20 +3623,20 @@
         <v>22</v>
       </c>
       <c r="BD16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE16" t="n">
         <v>55</v>
       </c>
       <c r="BF16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG16" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="G20" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="H20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K20" t="n">
         <v>3.65</v>
-      </c>
-      <c r="I20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.7</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -760,10 +760,10 @@
         <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
         <v>3.85</v>
@@ -772,10 +772,10 @@
         <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -787,49 +787,49 @@
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
         <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="X2" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
         <v>46</v>
@@ -850,7 +850,7 @@
         <v>29</v>
       </c>
       <c r="AK2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL2" t="n">
         <v>38</v>
@@ -859,34 +859,34 @@
         <v>110</v>
       </c>
       <c r="AN2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR2" t="n">
         <v>18.5</v>
       </c>
-      <c r="AO2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>21</v>
-      </c>
       <c r="AS2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
         <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
         <v>12</v>
@@ -895,32 +895,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA2" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>8</v>
       </c>
       <c r="BB2" t="n">
         <v>21</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -954,22 +954,22 @@
         <v>1.47</v>
       </c>
       <c r="G3" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="H3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
         <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -978,34 +978,34 @@
         <v>3.95</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
         <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
         <v>25</v>
@@ -1017,10 +1017,10 @@
         <v>300</v>
       </c>
       <c r="AB3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD3" t="n">
         <v>30</v>
@@ -1029,10 +1029,10 @@
         <v>150</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
         <v>27</v>
@@ -1047,7 +1047,7 @@
         <v>970</v>
       </c>
       <c r="AL3" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
         <v>180</v>
@@ -1056,19 +1056,19 @@
         <v>8.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>18</v>
       </c>
       <c r="AR3" t="n">
-        <v>55</v>
+        <v>7.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
         <v>7</v>
@@ -1077,22 +1077,22 @@
         <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX3" t="n">
         <v>7.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB3" t="n">
         <v>11</v>
@@ -1101,20 +1101,20 @@
         <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BF3" t="n">
         <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G4" t="n">
         <v>2.02</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I4" t="n">
         <v>5.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H5" t="n">
         <v>2.16</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H6" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G9" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J9" t="n">
         <v>4.2</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G10" t="n">
         <v>2.32</v>
@@ -2318,10 +2318,10 @@
         <v>3.2</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H16" t="n">
         <v>3.15</v>
@@ -3506,7 +3506,7 @@
         <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R16" t="n">
         <v>1.44</v>
@@ -3518,7 +3518,7 @@
         <v>1.7</v>
       </c>
       <c r="U16" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3530,19 +3530,19 @@
         <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z16" t="n">
         <v>24</v>
       </c>
       <c r="AA16" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB16" t="n">
         <v>12</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD16" t="n">
         <v>14</v>
@@ -3563,13 +3563,13 @@
         <v>44</v>
       </c>
       <c r="AJ16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK16" t="n">
         <v>26</v>
       </c>
       <c r="AL16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM16" t="n">
         <v>80</v>
@@ -3590,13 +3590,13 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT16" t="n">
         <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV16" t="n">
         <v>12.5</v>
@@ -3611,10 +3611,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB16" t="n">
         <v>30</v>
@@ -3626,7 +3626,7 @@
         <v>32</v>
       </c>
       <c r="BE16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF16" t="n">
         <v>16</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>2.08</v>
       </c>
       <c r="G20" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="H20" t="n">
         <v>4.1</v>
@@ -4261,7 +4261,7 @@
         <v>5.5</v>
       </c>
       <c r="J20" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="K20" t="n">
         <v>3.65</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -760,76 +760,76 @@
         <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.34</v>
       </c>
-      <c r="M2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.36</v>
-      </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W2" t="n">
         <v>1.75</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA2" t="n">
         <v>75</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>46</v>
@@ -841,40 +841,40 @@
         <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI2" t="n">
         <v>55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR2" t="n">
         <v>18.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
         <v>8.6</v>
@@ -886,7 +886,7 @@
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AX2" t="n">
         <v>12</v>
@@ -895,32 +895,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
         <v>21</v>
       </c>
       <c r="BC2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -957,10 +957,10 @@
         <v>1.58</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3" t="n">
         <v>4.4</v>
@@ -969,37 +969,37 @@
         <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="R3" t="n">
         <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
         <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W3" t="n">
         <v>2.72</v>
@@ -1008,37 +1008,37 @@
         <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z3" t="n">
         <v>70</v>
       </c>
       <c r="AA3" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE3" t="n">
         <v>150</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ3" t="n">
         <v>14</v>
@@ -1047,43 +1047,43 @@
         <v>970</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO3" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ3" t="n">
         <v>18</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
         <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
         <v>9</v>
@@ -1092,29 +1092,29 @@
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB3" t="n">
         <v>11</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -1148,167 +1148,167 @@
         <v>1.89</v>
       </c>
       <c r="G4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H4" t="n">
         <v>4.7</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -1345,16 +1345,16 @@
         <v>4.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J6" t="n">
         <v>2.82</v>
       </c>
-      <c r="H6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.7</v>
-      </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -2121,13 +2121,13 @@
         <v>1.77</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
@@ -2148,7 +2148,7 @@
         <v>2.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -2315,16 +2315,16 @@
         <v>2.32</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>2.52</v>
       </c>
       <c r="H16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I16" t="n">
         <v>3.2</v>
@@ -3512,13 +3512,13 @@
         <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
         <v>1.7</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
         <v>12</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD16" t="n">
         <v>14</v>
@@ -3566,10 +3566,10 @@
         <v>36</v>
       </c>
       <c r="AK16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM16" t="n">
         <v>80</v>
@@ -3596,7 +3596,7 @@
         <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
         <v>12.5</v>
@@ -3611,7 +3611,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA16" t="n">
         <v>36</v>
@@ -3632,11 +3632,11 @@
         <v>16</v>
       </c>
       <c r="BG16" t="n">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="I20" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="K20" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>1.47</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 07:16:34</t>
+          <t>2026-03-03 09:27:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -760,13 +760,13 @@
         <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H2" t="n">
         <v>3.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J2" t="n">
         <v>3.45</v>
@@ -775,7 +775,7 @@
         <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -808,7 +808,7 @@
         <v>1.34</v>
       </c>
       <c r="W2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X2" t="n">
         <v>15</v>
@@ -871,7 +871,7 @@
         <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS2" t="n">
         <v>8</v>
@@ -901,7 +901,7 @@
         <v>7.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
         <v>70</v>
       </c>
       <c r="AA3" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AB3" t="n">
         <v>8</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -1148,22 +1148,22 @@
         <v>1.89</v>
       </c>
       <c r="G4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H4" t="n">
         <v>4.7</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
@@ -1178,7 +1178,7 @@
         <v>1.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
@@ -1187,16 +1187,16 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="U4" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="V4" t="n">
         <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="X4" t="n">
         <v>12.5</v>
@@ -1286,7 +1286,7 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
         <v>19.5</v>
@@ -1298,7 +1298,7 @@
         <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
         <v>14.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G5" t="n">
         <v>4.6</v>
@@ -1348,25 +1348,25 @@
         <v>2.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="J5" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
         <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
         <v>1.65</v>
@@ -1375,134 +1375,134 @@
         <v>2.24</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="H6" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>5.9</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>2.1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
         <v>3.8</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>2.52</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I16" t="n">
         <v>3.2</v>
@@ -3512,7 +3512,7 @@
         <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T16" t="n">
         <v>1.7</v>
@@ -3530,7 +3530,7 @@
         <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z16" t="n">
         <v>24</v>
@@ -3611,7 +3611,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
         <v>36</v>
@@ -3623,7 +3623,7 @@
         <v>22</v>
       </c>
       <c r="BD16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE16" t="n">
         <v>50</v>
@@ -3632,11 +3632,11 @@
         <v>16</v>
       </c>
       <c r="BG16" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G20" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="H20" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="I20" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J20" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="K20" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q20" t="n">
         <v>2.44</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,10 +760,10 @@
         <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I2" t="n">
         <v>3.9</v>
@@ -772,7 +772,7 @@
         <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -784,10 +784,10 @@
         <v>3.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
         <v>1.94</v>
@@ -799,16 +799,16 @@
         <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X2" t="n">
         <v>15</v>
@@ -826,7 +826,7 @@
         <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
         <v>16</v>
@@ -853,7 +853,7 @@
         <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -874,10 +874,10 @@
         <v>18</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2" t="n">
         <v>7</v>
@@ -898,7 +898,7 @@
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="BB2" t="n">
         <v>23</v>
@@ -910,7 +910,7 @@
         <v>7.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF2" t="n">
         <v>13.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G3" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="H3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J3" t="n">
         <v>4.4</v>
@@ -975,13 +975,13 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q3" t="n">
         <v>1.89</v>
@@ -993,31 +993,31 @@
         <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z3" t="n">
         <v>70</v>
       </c>
       <c r="AA3" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="AB3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AC3" t="n">
         <v>11</v>
@@ -1026,10 +1026,10 @@
         <v>32</v>
       </c>
       <c r="AE3" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
@@ -1044,7 +1044,7 @@
         <v>14</v>
       </c>
       <c r="AK3" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AL3" t="n">
         <v>44</v>
@@ -1053,22 +1053,22 @@
         <v>190</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO3" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.9</v>
+        <v>14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AT3" t="n">
         <v>6.8</v>
@@ -1077,10 +1077,10 @@
         <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX3" t="n">
         <v>7.2</v>
@@ -1092,29 +1092,29 @@
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3" t="n">
         <v>11</v>
       </c>
       <c r="BC3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF3" t="n">
         <v>7.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>4.7</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1184,19 +1184,19 @@
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="V4" t="n">
         <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="X4" t="n">
         <v>12.5</v>
@@ -1286,7 +1286,7 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB4" t="n">
         <v>19.5</v>
@@ -1298,7 +1298,7 @@
         <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF4" t="n">
         <v>14.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>3.55</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="I5" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="J5" t="n">
         <v>3.05</v>
@@ -1357,16 +1357,16 @@
         <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.65</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P5" t="n">
         <v>1.65</v>
@@ -1375,134 +1375,134 @@
         <v>2.24</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V5" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT5" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AS5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
         <v>21</v>
       </c>
       <c r="AX5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>44</v>
+        <v>4.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>44</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>95</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>3.35</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
         <v>2.92</v>
@@ -1551,159 +1551,159 @@
         <v>3.4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,184 +1713,184 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>US Latina Calcio</t>
+          <t>NK Aluminij</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T7" t="n">
         <v>1.01</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FC Basel</t>
+          <t>US Latina Calcio</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grasshoppers Zurich</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.42</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>FC Basel</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St Gallen</t>
+          <t>Grasshoppers Zurich</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="G10" t="n">
-        <v>2.34</v>
+        <v>1.76</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>St Gallen</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>2.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cavese 1919</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
@@ -2882,12 +2882,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
@@ -3076,12 +3076,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quindio</t>
+          <t>Cavese 1919</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,61 +3464,61 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="G16" t="n">
-        <v>2.52</v>
+        <v>4.2</v>
       </c>
       <c r="H16" t="n">
-        <v>3.15</v>
+        <v>2.32</v>
       </c>
       <c r="I16" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="K16" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.86</v>
+        <v>1.02</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3527,123 +3527,123 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="G17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO17" t="n">
         <v>1000</v>
       </c>
-      <c r="H17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,31 +3852,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Real Soacha Cundinamarc</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Internacional de Palmir</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,36 +4041,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>20:10:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarc</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Internacional de Palmir</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="G19" t="n">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="H19" t="n">
-        <v>2.58</v>
+        <v>4.1</v>
       </c>
       <c r="I19" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,201 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 11:39:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>20:10:00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Llaneros FC</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Internacional de Bogotá</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="H20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>2026-03-03 11:39:37</t>
+          <t>2026-03-03 13:50:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -766,7 +766,7 @@
         <v>3.55</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J2" t="n">
         <v>3.45</v>
@@ -790,13 +790,13 @@
         <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
         <v>1.79</v>
@@ -826,7 +826,7 @@
         <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>16</v>
@@ -874,31 +874,31 @@
         <v>18</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX2" t="n">
         <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>42</v>
+        <v>7.2</v>
       </c>
       <c r="BB2" t="n">
         <v>23</v>
@@ -907,20 +907,20 @@
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.48</v>
       </c>
       <c r="G3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H3" t="n">
         <v>7.6</v>
@@ -963,13 +963,13 @@
         <v>8.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K3" t="n">
         <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -978,19 +978,19 @@
         <v>3.85</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
         <v>1.97</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
         <v>2.08</v>
@@ -1014,10 +1014,10 @@
         <v>70</v>
       </c>
       <c r="AA3" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
         <v>11</v>
@@ -1029,10 +1029,10 @@
         <v>160</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
         <v>28</v>
@@ -1053,10 +1053,10 @@
         <v>190</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AP3" t="n">
         <v>14</v>
@@ -1065,34 +1065,34 @@
         <v>20</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
         <v>6.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV3" t="n">
         <v>23</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB3" t="n">
         <v>11</v>
@@ -1101,20 +1101,20 @@
         <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -1160,10 +1160,10 @@
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
@@ -1172,7 +1172,7 @@
         <v>2.92</v>
       </c>
       <c r="O4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P4" t="n">
         <v>1.65</v>
@@ -1184,7 +1184,7 @@
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="T4" t="n">
         <v>2.04</v>
@@ -1214,7 +1214,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
         <v>24</v>
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
@@ -1286,7 +1286,7 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
         <v>19.5</v>
@@ -1298,7 +1298,7 @@
         <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
         <v>14.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="H5" t="n">
         <v>2.26</v>
       </c>
       <c r="I5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J5" t="n">
         <v>3.05</v>
@@ -1363,7 +1363,7 @@
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O5" t="n">
         <v>1.42</v>
@@ -1378,19 +1378,19 @@
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U5" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="V5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
@@ -1420,7 +1420,7 @@
         <v>32</v>
       </c>
       <c r="AG5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
         <v>25</v>
@@ -1444,7 +1444,7 @@
         <v>80</v>
       </c>
       <c r="AO5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP5" t="n">
         <v>9.199999999999999</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="H6" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="J6" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
         <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R6" t="n">
         <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V6" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2.32</v>
       </c>
       <c r="AQ6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.18</v>
+        <v>4.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.28</v>
+        <v>4.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.97</v>
+        <v>7.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.88</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>3.95</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.26</v>
+        <v>4.7</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.1</v>
+        <v>12.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.04</v>
+        <v>3.75</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.12</v>
+        <v>4.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.28</v>
+        <v>4.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.22</v>
+        <v>4.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.26</v>
+        <v>4.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.32</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.32</v>
+        <v>19</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.32</v>
+        <v>4.7</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>4.5</v>
       </c>
       <c r="G7" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="I7" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,22 +1751,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="R7" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="S7" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,7 +1775,7 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="W7" t="n">
         <v>1.13</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -1912,179 +1912,179 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FC Giugliano</t>
+          <t>US Latina Calcio</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>US Latina Calcio</t>
+          <t>FC Giugliano</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P9" t="n">
         <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>1.63</v>
       </c>
       <c r="G10" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="H10" t="n">
         <v>4.9</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G11" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2536,7 +2536,7 @@
         <v>2.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -3673,16 +3673,16 @@
         <v>2.5</v>
       </c>
       <c r="H17" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K17" t="n">
         <v>3.55</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.6</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3769,7 +3769,7 @@
         <v>80</v>
       </c>
       <c r="AN17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
@@ -3820,17 +3820,17 @@
         <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BF17" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="G19" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="H19" t="n">
         <v>4.1</v>
       </c>
       <c r="I19" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="K19" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 16:01:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,10 +763,10 @@
         <v>2.26</v>
       </c>
       <c r="H2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J2" t="n">
         <v>3.45</v>
@@ -775,13 +775,13 @@
         <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O2" t="n">
         <v>1.32</v>
@@ -799,13 +799,13 @@
         <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U2" t="n">
         <v>2.14</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W2" t="n">
         <v>1.79</v>
@@ -832,10 +832,10 @@
         <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AF2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG2" t="n">
         <v>11.5</v>
@@ -847,7 +847,7 @@
         <v>55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK2" t="n">
         <v>25</v>
@@ -859,10 +859,10 @@
         <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AP2" t="n">
         <v>12.5</v>
@@ -871,13 +871,13 @@
         <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
         <v>7.2</v>
@@ -886,7 +886,7 @@
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="AX2" t="n">
         <v>12</v>
@@ -898,29 +898,29 @@
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2" t="n">
         <v>14.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -951,64 +951,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="X3" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z3" t="n">
         <v>70</v>
@@ -1017,13 +1017,13 @@
         <v>310</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AE3" t="n">
         <v>160</v>
@@ -1035,7 +1035,7 @@
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>980</v>
       </c>
       <c r="AI3" t="n">
         <v>140</v>
@@ -1047,74 +1047,74 @@
         <v>18</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AM3" t="n">
         <v>190</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO3" t="n">
         <v>220</v>
       </c>
       <c r="AP3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ3" t="n">
         <v>20</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.89</v>
       </c>
       <c r="G4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>4.7</v>
@@ -1163,19 +1163,19 @@
         <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
         <v>2.28</v>
@@ -1184,19 +1184,19 @@
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="U4" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="V4" t="n">
         <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
         <v>12.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H5" t="n">
         <v>2.26</v>
       </c>
       <c r="I5" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
         <v>3.05</v>
@@ -1357,13 +1357,13 @@
         <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
         <v>1.42</v>
@@ -1378,19 +1378,19 @@
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.89</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.76</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
@@ -1420,7 +1420,7 @@
         <v>32</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AH5" t="n">
         <v>25</v>
@@ -1444,7 +1444,7 @@
         <v>80</v>
       </c>
       <c r="AO5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP5" t="n">
         <v>9.199999999999999</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G6" t="n">
         <v>2.76</v>
@@ -1575,7 +1575,7 @@
         <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U6" t="n">
         <v>1.86</v>
@@ -1641,16 +1641,16 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.6</v>
+        <v>3.7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT6" t="n">
         <v>7.8</v>
@@ -1659,44 +1659,44 @@
         <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX6" t="n">
         <v>12.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC6" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC6" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD6" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF6" t="n">
         <v>19</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -1948,19 +1948,19 @@
         <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="P8" t="n">
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FC Basel</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grasshoppers Zurich</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.63</v>
+        <v>2.36</v>
       </c>
       <c r="G10" t="n">
-        <v>1.74</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X10" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE10" t="n">
         <v>4.9</v>
       </c>
-      <c r="I10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St Gallen</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.14</v>
+        <v>6.2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.32</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="I11" t="n">
-        <v>3.6</v>
+        <v>1.61</v>
       </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="K11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X11" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>190</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA11" t="n">
         <v>4.4</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>FC Basel</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Grasshoppers Zurich</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>2.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>St Gallen</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>2.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P14" t="n">
         <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -3279,177 +3279,177 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
         <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Quindio</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>2.86</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>2.74</v>
+        <v>1.02</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P16" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.48</v>
+        <v>8.6</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2</v>
+        <v>1.46</v>
       </c>
       <c r="I17" t="n">
-        <v>3.25</v>
+        <v>1.61</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K17" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>240</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>220</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU17" t="n">
         <v>4.4</v>
       </c>
-      <c r="O17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU17" t="n">
+      <c r="AV17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB17" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>30</v>
-      </c>
       <c r="BC17" t="n">
-        <v>22</v>
+        <v>7.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>50</v>
+        <v>7.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>16</v>
+        <v>7.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,378 +3847,1542 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarc</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Internacional de Palmir</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="G18" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="H18" t="n">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="I18" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P18" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 16:01:58</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Haras El Hodood</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Pyramids</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>11</v>
+      </c>
+      <c r="G19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:12:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ceramica Cleopatra</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>National Bank</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X20" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:12:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Italian Serie C</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Benevento</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Catania</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:12:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Real Santander</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Quindio</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:12:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:12:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Real Soacha Cundinamarc</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Internacional de Palmir</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:12:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>20:10:00</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Llaneros FC</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Internacional de Bogotá</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="F25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L25" t="n">
         <v>0</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N25" t="n">
         <v>0</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="P19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="P25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q25" t="n">
         <v>2.46</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S25" t="n">
         <v>0</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T25" t="n">
         <v>0</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U25" t="n">
         <v>0</v>
       </c>
-      <c r="V19" t="n">
+      <c r="V25" t="n">
         <v>0</v>
       </c>
-      <c r="W19" t="n">
+      <c r="W25" t="n">
         <v>0</v>
       </c>
-      <c r="X19" t="n">
+      <c r="X25" t="n">
         <v>0</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Y25" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="Z25" t="n">
         <v>0</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AA25" t="n">
         <v>0</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AB25" t="n">
         <v>0</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AC25" t="n">
         <v>0</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AD25" t="n">
         <v>0</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AE25" t="n">
         <v>0</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AF25" t="n">
         <v>0</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AG25" t="n">
         <v>0</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AH25" t="n">
         <v>0</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AI25" t="n">
         <v>0</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AJ25" t="n">
         <v>0</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AK25" t="n">
         <v>0</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AL25" t="n">
         <v>0</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AM25" t="n">
         <v>0</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AN25" t="n">
         <v>0</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AO25" t="n">
         <v>0</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AP25" t="n">
         <v>0</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AQ25" t="n">
         <v>0</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AR25" t="n">
         <v>0</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="AS25" t="n">
         <v>0</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="AT25" t="n">
         <v>0</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AU25" t="n">
         <v>0</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AV25" t="n">
         <v>0</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="AW25" t="n">
         <v>0</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="AX25" t="n">
         <v>0</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="AY25" t="n">
         <v>0</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="AZ25" t="n">
         <v>0</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BA25" t="n">
         <v>0</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BB25" t="n">
         <v>0</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BC25" t="n">
         <v>0</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BD25" t="n">
         <v>0</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BE25" t="n">
         <v>0</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BF25" t="n">
         <v>0</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BG25" t="n">
         <v>0</v>
       </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>2026-03-03 16:01:58</t>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -775,7 +775,7 @@
         <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -802,7 +802,7 @@
         <v>1.8</v>
       </c>
       <c r="U2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
         <v>1.34</v>
@@ -826,7 +826,7 @@
         <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
         <v>16</v>
@@ -853,7 +853,7 @@
         <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -874,7 +874,7 @@
         <v>22</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
         <v>8.6</v>
@@ -898,7 +898,7 @@
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB2" t="n">
         <v>21</v>
@@ -907,20 +907,20 @@
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>30</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF2" t="n">
         <v>14.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>38</v>
+        <v>8.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -951,148 +951,148 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA3" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AE3" t="n">
         <v>160</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AJ3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK3" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AL3" t="n">
         <v>980</v>
       </c>
       <c r="AM3" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="AP3" t="n">
         <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW3" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="BB3" t="n">
         <v>12</v>
@@ -1101,20 +1101,20 @@
         <v>15</v>
       </c>
       <c r="BD3" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
@@ -1178,7 +1178,7 @@
         <v>1.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H5" t="n">
         <v>2.26</v>
@@ -1378,7 +1378,7 @@
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="T5" t="n">
         <v>1.91</v>
@@ -1390,7 +1390,7 @@
         <v>1.67</v>
       </c>
       <c r="W5" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G6" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
@@ -1548,7 +1548,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1566,7 +1566,7 @@
         <v>1.71</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R6" t="n">
         <v>1.27</v>
@@ -1590,7 +1590,7 @@
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1599,13 +1599,13 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
         <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1617,7 +1617,7 @@
         <v>14.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU6" t="n">
         <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AX6" t="n">
         <v>12.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>19</v>
+        <v>5.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>4.5</v>
       </c>
       <c r="G7" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="H7" t="n">
         <v>1.42</v>
       </c>
       <c r="I7" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
         <v>13</v>
@@ -1775,7 +1775,7 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="W7" t="n">
         <v>1.13</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
         <v>2.88</v>
@@ -2354,13 +2354,13 @@
         <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
         <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X10" t="n">
         <v>12</v>
@@ -2453,7 +2453,7 @@
         <v>4.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC10" t="n">
         <v>4.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -2506,16 +2506,16 @@
         <v>6.2</v>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="H11" t="n">
         <v>1.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K11" t="n">
         <v>5.9</v>
@@ -2551,10 +2551,10 @@
         <v>2.16</v>
       </c>
       <c r="V11" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
         <v>29</v>
@@ -2623,7 +2623,7 @@
         <v>12.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AU11" t="n">
         <v>9.4</v>
@@ -2641,7 +2641,7 @@
         <v>4.3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA11" t="n">
         <v>4.4</v>
@@ -2653,7 +2653,7 @@
         <v>4.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE11" t="n">
         <v>4.8</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
         <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2721,28 +2721,28 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>2.42</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P12" t="n">
         <v>2.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V12" t="n">
         <v>1.2</v>
@@ -2751,116 +2751,116 @@
         <v>2.34</v>
       </c>
       <c r="X12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE12" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG12" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
         <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM12" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.08</v>
+        <v>2.66</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.14</v>
+        <v>32</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.96</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.06</v>
+        <v>2.64</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.16</v>
+        <v>2.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.96</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.02</v>
+        <v>2.58</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.14</v>
+        <v>2.78</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.02</v>
+        <v>2.56</v>
       </c>
       <c r="BC12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD12" t="n">
         <v>20</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.16</v>
+        <v>2.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G13" t="n">
         <v>2.32</v>
       </c>
       <c r="H13" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I13" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J13" t="n">
         <v>3.85</v>
@@ -2921,16 +2921,16 @@
         <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R13" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="S13" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T13" t="n">
         <v>1.53</v>
@@ -2939,7 +2939,7 @@
         <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
         <v>1.76</v>
@@ -3047,14 +3047,14 @@
         <v>4</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
         <v>14.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -3118,13 +3118,13 @@
         <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -3500,19 +3500,19 @@
         <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P16" t="n">
         <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R16" t="n">
         <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>11</v>
@@ -3676,13 +3676,13 @@
         <v>1.46</v>
       </c>
       <c r="I17" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,43 +3691,43 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U17" t="n">
         <v>1.62</v>
       </c>
       <c r="V17" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="W17" t="n">
         <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AA17" t="n">
         <v>970</v>
@@ -3739,10 +3739,10 @@
         <v>970</v>
       </c>
       <c r="AD17" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AF17" t="n">
         <v>100</v>
@@ -3751,10 +3751,10 @@
         <v>40</v>
       </c>
       <c r="AH17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI17" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
@@ -3763,7 +3763,7 @@
         <v>240</v>
       </c>
       <c r="AL17" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AM17" t="n">
         <v>300</v>
@@ -3778,7 +3778,7 @@
         <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AR17" t="n">
         <v>6.4</v>
@@ -3793,10 +3793,10 @@
         <v>4.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX17" t="n">
         <v>7</v>
@@ -3817,7 +3817,7 @@
         <v>7.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE17" t="n">
         <v>7.4</v>
@@ -3826,11 +3826,11 @@
         <v>7.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="G18" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H18" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="I18" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J18" t="n">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,22 +3885,22 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
         <v>1.42</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R18" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -3909,122 +3909,122 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W18" t="n">
         <v>1.56</v>
       </c>
       <c r="X18" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y18" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX18" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>2.82</v>
-      </c>
       <c r="AY18" t="n">
-        <v>2.74</v>
+        <v>11</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.96</v>
+        <v>19.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.15</v>
+        <v>5.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>1.33</v>
       </c>
       <c r="I19" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="J19" t="n">
         <v>4.2</v>
@@ -4076,7 +4076,7 @@
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
         <v>3.1</v>
@@ -4103,7 +4103,7 @@
         <v>1.51</v>
       </c>
       <c r="V19" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="W19" t="n">
         <v>1.06</v>
@@ -4112,10 +4112,10 @@
         <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AA19" t="n">
         <v>12.5</v>
@@ -4124,13 +4124,13 @@
         <v>36</v>
       </c>
       <c r="AC19" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF19" t="n">
         <v>160</v>
@@ -4139,7 +4139,7 @@
         <v>65</v>
       </c>
       <c r="AH19" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AI19" t="n">
         <v>75</v>
@@ -4160,7 +4160,7 @@
         <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AP19" t="n">
         <v>6.8</v>
@@ -4175,7 +4175,7 @@
         <v>9</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AU19" t="n">
         <v>9.6</v>
@@ -4184,41 +4184,41 @@
         <v>9.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AX19" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AY19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC19" t="n">
         <v>5.8</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA19" t="n">
+      <c r="BD19" t="n">
         <v>5.8</v>
       </c>
-      <c r="BB19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BE19" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="G20" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J20" t="n">
         <v>2.96</v>
@@ -4288,22 +4288,22 @@
         <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U20" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W20" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y20" t="n">
         <v>12.5</v>
@@ -4315,7 +4315,7 @@
         <v>95</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC20" t="n">
         <v>8.6</v>
@@ -4339,19 +4339,19 @@
         <v>95</v>
       </c>
       <c r="AJ20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK20" t="n">
         <v>42</v>
       </c>
       <c r="AL20" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM20" t="n">
         <v>210</v>
       </c>
       <c r="AN20" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO20" t="n">
         <v>95</v>
@@ -4360,13 +4360,13 @@
         <v>7.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR20" t="n">
-        <v>20</v>
+        <v>3.8</v>
       </c>
       <c r="AS20" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AT20" t="n">
         <v>6.8</v>
@@ -4375,10 +4375,10 @@
         <v>6.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AX20" t="n">
         <v>12.5</v>
@@ -4387,32 +4387,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BA20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB20" t="n">
         <v>4</v>
       </c>
-      <c r="BB20" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BC20" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BG20" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -4476,13 +4476,13 @@
         <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="R21" t="n">
         <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -4637,170 +4637,170 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="H22" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="I22" t="n">
-        <v>2.74</v>
+        <v>2.22</v>
       </c>
       <c r="J22" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>1.59</v>
+        <v>2.86</v>
       </c>
       <c r="O22" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="P22" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>2.22</v>
+        <v>4.4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V22" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="W22" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ22" t="n">
         <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -4900,10 +4900,10 @@
         <v>12</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE23" t="n">
         <v>34</v>
@@ -4939,7 +4939,7 @@
         <v>28</v>
       </c>
       <c r="AP23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ23" t="n">
         <v>13</v>
@@ -4948,7 +4948,7 @@
         <v>21</v>
       </c>
       <c r="AS23" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AT23" t="n">
         <v>11</v>
@@ -4984,7 +4984,7 @@
         <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF23" t="n">
         <v>16</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -5046,31 +5046,31 @@
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="O24" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="P24" t="n">
         <v>1.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>2.28</v>
+        <v>3.7</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V24" t="n">
         <v>1.36</v>
@@ -5082,40 +5082,40 @@
         <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE24" t="n">
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK24" t="n">
         <v>1000</v>
@@ -5133,62 +5133,62 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G25" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="H25" t="n">
         <v>4.2</v>
       </c>
       <c r="I25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J25" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="K25" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -784,7 +784,7 @@
         <v>3.65</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
         <v>1.91</v>
@@ -817,7 +817,7 @@
         <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA2" t="n">
         <v>75</v>
@@ -826,13 +826,13 @@
         <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="n">
         <v>14.5</v>
@@ -844,7 +844,7 @@
         <v>18.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
         <v>29</v>
@@ -853,7 +853,7 @@
         <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -865,7 +865,7 @@
         <v>980</v>
       </c>
       <c r="AP2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
         <v>11.5</v>
@@ -874,22 +874,22 @@
         <v>22</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
         <v>8.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY2" t="n">
         <v>9.800000000000001</v>
@@ -898,29 +898,29 @@
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BB2" t="n">
         <v>21</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF2" t="n">
         <v>14.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -954,19 +954,19 @@
         <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -978,10 +978,10 @@
         <v>3.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q3" t="n">
         <v>2.1</v>
@@ -996,13 +996,13 @@
         <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
         <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X3" t="n">
         <v>16</v>
@@ -1011,7 +1011,7 @@
         <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA3" t="n">
         <v>320</v>
@@ -1020,7 +1020,7 @@
         <v>7</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
         <v>34</v>
@@ -1029,16 +1029,16 @@
         <v>160</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AI3" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ3" t="n">
         <v>15</v>
@@ -1050,13 +1050,13 @@
         <v>980</v>
       </c>
       <c r="AM3" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO3" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AP3" t="n">
         <v>12</v>
@@ -1065,56 +1065,56 @@
         <v>17</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT3" t="n">
         <v>6.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3" t="n">
         <v>12</v>
       </c>
       <c r="BC3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>1.89</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,146 +1169,146 @@
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O4" t="n">
         <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="V4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="X4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H5" t="n">
         <v>2.26</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="J5" t="n">
         <v>3.05</v>
@@ -1357,7 +1357,7 @@
         <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
@@ -1369,28 +1369,28 @@
         <v>1.42</v>
       </c>
       <c r="P5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.65</v>
       </c>
-      <c r="Q5" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.67</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
@@ -1545,10 +1545,10 @@
         <v>3.65</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1563,37 +1563,37 @@
         <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
         <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="U6" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
         <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1602,22 +1602,22 @@
         <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1641,16 +1641,16 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR6" t="n">
         <v>5.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT6" t="n">
         <v>8.199999999999999</v>
@@ -1659,44 +1659,44 @@
         <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BB6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG6" t="n">
         <v>5.7</v>
       </c>
-      <c r="BC6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>6</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>1.42</v>
       </c>
       <c r="I7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="J7" t="n">
         <v>4.2</v>
@@ -1751,22 +1751,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O7" t="n">
         <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R7" t="n">
         <v>1.63</v>
       </c>
       <c r="S7" t="n">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,7 +1775,7 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="W7" t="n">
         <v>1.13</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -2342,19 +2342,19 @@
         <v>1.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
         <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="V10" t="n">
         <v>1.39</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -2506,16 +2506,16 @@
         <v>6.2</v>
       </c>
       <c r="G11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
         <v>1.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="J11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K11" t="n">
         <v>5.9</v>
@@ -2536,7 +2536,7 @@
         <v>2.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R11" t="n">
         <v>1.58</v>
@@ -2551,10 +2551,10 @@
         <v>2.16</v>
       </c>
       <c r="V11" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
         <v>29</v>
@@ -2605,7 +2605,7 @@
         <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AO11" t="n">
         <v>7.2</v>
@@ -2647,7 +2647,7 @@
         <v>4.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC11" t="n">
         <v>4.8</v>
@@ -2656,7 +2656,7 @@
         <v>4.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF11" t="n">
         <v>4.8</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="G12" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="H12" t="n">
         <v>5.1</v>
       </c>
       <c r="I12" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2727,28 +2727,28 @@
         <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="U12" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2811,7 +2811,7 @@
         <v>2.66</v>
       </c>
       <c r="AR12" t="n">
-        <v>32</v>
+        <v>2.76</v>
       </c>
       <c r="AS12" t="n">
         <v>2.9</v>
@@ -2820,7 +2820,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AV12" t="n">
         <v>2.64</v>
@@ -2838,10 +2838,10 @@
         <v>2.58</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BC12" t="n">
         <v>11.5</v>
@@ -2850,17 +2850,17 @@
         <v>20</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BF12" t="n">
         <v>4.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G13" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="H13" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="I13" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2921,16 +2921,16 @@
         <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R13" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="S13" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="T13" t="n">
         <v>1.53</v>
@@ -2939,122 +2939,122 @@
         <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="X13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="G17" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="I17" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="J17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,49 +3691,49 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P17" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q17" t="n">
         <v>2.32</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U17" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
         <v>970</v>
       </c>
       <c r="Y17" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>970</v>
       </c>
       <c r="AB17" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AC17" t="n">
         <v>970</v>
@@ -3742,52 +3742,52 @@
         <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AG17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI17" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AK17" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="AL17" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AM17" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AO17" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AP17" t="n">
         <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS17" t="n">
         <v>11</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AU17" t="n">
         <v>4.4</v>
@@ -3796,25 +3796,25 @@
         <v>4.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AZ17" t="n">
         <v>6.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB17" t="n">
         <v>7.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD17" t="n">
         <v>7.2</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="G18" t="n">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="H18" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="I18" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -3885,22 +3885,22 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>2.4</v>
+        <v>1.38</v>
       </c>
       <c r="O18" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="P18" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="R18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="X18" t="n">
         <v>8.6</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -4061,16 +4061,16 @@
         <v>17.5</v>
       </c>
       <c r="H19" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="I19" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K19" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4079,16 +4079,16 @@
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>1.72</v>
       </c>
       <c r="O19" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P19" t="n">
         <v>1.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="R19" t="n">
         <v>1.27</v>
@@ -4100,10 +4100,10 @@
         <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="W19" t="n">
         <v>1.06</v>
@@ -4121,7 +4121,7 @@
         <v>12.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AC19" t="n">
         <v>970</v>
@@ -4136,7 +4136,7 @@
         <v>160</v>
       </c>
       <c r="AG19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AH19" t="n">
         <v>46</v>
@@ -4175,7 +4175,7 @@
         <v>9</v>
       </c>
       <c r="AT19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU19" t="n">
         <v>9.6</v>
@@ -4184,41 +4184,41 @@
         <v>9.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AY19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC19" t="n">
         <v>5.9</v>
       </c>
-      <c r="BC19" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BD19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG19" t="n">
         <v>7.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         <v>3.45</v>
       </c>
       <c r="I20" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="J20" t="n">
         <v>2.96</v>
@@ -4282,25 +4282,25 @@
         <v>1.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R20" t="n">
         <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="V20" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W20" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X20" t="n">
         <v>10.5</v>
@@ -4327,13 +4327,13 @@
         <v>70</v>
       </c>
       <c r="AF20" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI20" t="n">
         <v>95</v>
@@ -4363,10 +4363,10 @@
         <v>9</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT20" t="n">
         <v>6.8</v>
@@ -4378,7 +4378,7 @@
         <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX20" t="n">
         <v>12.5</v>
@@ -4387,32 +4387,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BA20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD20" t="n">
         <v>4.2</v>
       </c>
-      <c r="BB20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD20" t="n">
+      <c r="BE20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF20" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BG20" t="n">
         <v>4.3</v>
       </c>
-      <c r="BF20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         <v>1.45</v>
       </c>
       <c r="P22" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q22" t="n">
         <v>2.3</v>
@@ -4691,16 +4691,16 @@
         <v>1.27</v>
       </c>
       <c r="X22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y22" t="n">
         <v>7.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA22" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AB22" t="n">
         <v>13</v>
@@ -4709,10 +4709,10 @@
         <v>8</v>
       </c>
       <c r="AD22" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF22" t="n">
         <v>32</v>
@@ -4739,25 +4739,25 @@
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO22" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP22" t="n">
         <v>9</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="AS22" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AU22" t="n">
         <v>6.4</v>
@@ -4766,10 +4766,10 @@
         <v>9.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AY22" t="n">
         <v>15</v>
@@ -4778,29 +4778,29 @@
         <v>18.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G23" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H23" t="n">
         <v>3.2</v>
@@ -4855,37 +4855,37 @@
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O23" t="n">
         <v>1.28</v>
       </c>
       <c r="P23" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
         <v>1.68</v>
       </c>
       <c r="U23" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W23" t="n">
         <v>1.67</v>
       </c>
       <c r="X23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y23" t="n">
         <v>14</v>
@@ -4924,28 +4924,28 @@
         <v>34</v>
       </c>
       <c r="AK23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM23" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO23" t="n">
         <v>28</v>
       </c>
       <c r="AP23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ23" t="n">
         <v>13</v>
       </c>
       <c r="AR23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS23" t="n">
         <v>46</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
         <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="T24" t="n">
         <v>1.97</v>
@@ -5082,40 +5082,40 @@
         <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
         <v>1000</v>
@@ -5133,62 +5133,62 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -5219,170 +5219,170 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G25" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="H25" t="n">
         <v>4.2</v>
       </c>
       <c r="I25" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J25" t="n">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="K25" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P25" t="n">
         <v>1.49</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH25"/>
+  <dimension ref="A1:BH26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -826,7 +826,7 @@
         <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
         <v>16.5</v>
@@ -874,7 +874,7 @@
         <v>22</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT2" t="n">
         <v>8.6</v>
@@ -898,7 +898,7 @@
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB2" t="n">
         <v>21</v>
@@ -910,17 +910,17 @@
         <v>7.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
         <v>14.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -957,10 +957,10 @@
         <v>1.6</v>
       </c>
       <c r="H3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
@@ -1014,7 +1014,7 @@
         <v>70</v>
       </c>
       <c r="AA3" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AB3" t="n">
         <v>7</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>1.89</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H4" t="n">
         <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
@@ -1169,13 +1169,13 @@
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O4" t="n">
         <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q4" t="n">
         <v>2.14</v>
@@ -1184,7 +1184,7 @@
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="T4" t="n">
         <v>2.04</v>
@@ -1196,7 +1196,7 @@
         <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H5" t="n">
         <v>2.26</v>
@@ -1360,7 +1360,7 @@
         <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
         <v>2.9</v>
@@ -1390,7 +1390,7 @@
         <v>1.65</v>
       </c>
       <c r="W5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
@@ -1420,7 +1420,7 @@
         <v>32</v>
       </c>
       <c r="AG5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
         <v>25</v>
@@ -1444,10 +1444,10 @@
         <v>80</v>
       </c>
       <c r="AO5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.2</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
@@ -1584,7 +1584,7 @@
         <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
         <v>14</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -2342,13 +2342,13 @@
         <v>1.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R10" t="n">
         <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T10" t="n">
         <v>1.95</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
         <v>1.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
         <v>4.6</v>
@@ -2542,7 +2542,7 @@
         <v>1.58</v>
       </c>
       <c r="S11" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T11" t="n">
         <v>1.64</v>
@@ -2551,7 +2551,7 @@
         <v>2.16</v>
       </c>
       <c r="V11" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="W11" t="n">
         <v>1.14</v>
@@ -2605,7 +2605,7 @@
         <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AO11" t="n">
         <v>7.2</v>
@@ -2647,7 +2647,7 @@
         <v>4.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC11" t="n">
         <v>4.8</v>
@@ -2656,17 +2656,17 @@
         <v>4.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.8</v>
+        <v>55</v>
       </c>
       <c r="BG11" t="n">
         <v>4.9</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="G12" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="H12" t="n">
         <v>5.1</v>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="J12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2721,7 +2721,7 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.19</v>
@@ -2745,10 +2745,10 @@
         <v>2.26</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W12" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2766,10 +2766,10 @@
         <v>16</v>
       </c>
       <c r="AC12" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE12" t="n">
         <v>80</v>
@@ -2781,19 +2781,19 @@
         <v>13.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
         <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK12" t="n">
         <v>21</v>
       </c>
       <c r="AL12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM12" t="n">
         <v>95</v>
@@ -2805,43 +2805,43 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AT12" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AX12" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY12" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="BC12" t="n">
         <v>11.5</v>
@@ -2850,17 +2850,17 @@
         <v>20</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>3.1</v>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
         <v>3.3</v>
@@ -2921,16 +2921,16 @@
         <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T13" t="n">
         <v>1.53</v>
@@ -2939,7 +2939,7 @@
         <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
         <v>1.65</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -3500,19 +3500,19 @@
         <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P16" t="n">
         <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="R16" t="n">
         <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -3658,31 +3658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="H17" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="I17" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K17" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,16 +3691,16 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>1.72</v>
       </c>
       <c r="O17" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P17" t="n">
         <v>1.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.32</v>
+        <v>1.94</v>
       </c>
       <c r="R17" t="n">
         <v>1.27</v>
@@ -3709,128 +3709,128 @@
         <v>3.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="V17" t="n">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="n">
         <v>6.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AC17" t="n">
         <v>970</v>
       </c>
       <c r="AD17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF17" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI17" t="n">
         <v>75</v>
       </c>
-      <c r="AG17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>55</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AQ17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR17" t="n">
         <v>5.7</v>
       </c>
-      <c r="AR17" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AS17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA17" t="n">
         <v>5.6</v>
       </c>
-      <c r="AX17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BB17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG17" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -3861,13 +3861,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G18" t="n">
         <v>3.3</v>
       </c>
       <c r="H18" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I18" t="n">
         <v>1000</v>
@@ -3882,13 +3882,13 @@
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N18" t="n">
         <v>1.38</v>
       </c>
       <c r="O18" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="P18" t="n">
         <v>1.38</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="G19" t="n">
-        <v>17.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="I19" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="J19" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4079,16 +4079,16 @@
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>1.72</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="P19" t="n">
         <v>1.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.94</v>
+        <v>2.32</v>
       </c>
       <c r="R19" t="n">
         <v>1.27</v>
@@ -4097,128 +4097,128 @@
         <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="V19" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y19" t="n">
         <v>6.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AA19" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AB19" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AC19" t="n">
         <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF19" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AG19" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AH19" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AI19" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AO19" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AP19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR19" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>9.6</v>
+        <v>4.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.4</v>
+        <v>4.7</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AX19" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AY19" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G20" t="n">
         <v>2.6</v>
       </c>
       <c r="H20" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I20" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
         <v>2.96</v>
@@ -4270,13 +4270,13 @@
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N20" t="n">
         <v>2.64</v>
       </c>
       <c r="O20" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P20" t="n">
         <v>1.55</v>
@@ -4297,13 +4297,13 @@
         <v>1.81</v>
       </c>
       <c r="V20" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y20" t="n">
         <v>12.5</v>
@@ -4312,7 +4312,7 @@
         <v>29</v>
       </c>
       <c r="AA20" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AB20" t="n">
         <v>9.199999999999999</v>
@@ -4321,7 +4321,7 @@
         <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE20" t="n">
         <v>70</v>
@@ -4354,7 +4354,7 @@
         <v>44</v>
       </c>
       <c r="AO20" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP20" t="n">
         <v>7.8</v>
@@ -4363,10 +4363,10 @@
         <v>9</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.9</v>
+        <v>16.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT20" t="n">
         <v>6.8</v>
@@ -4378,7 +4378,7 @@
         <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX20" t="n">
         <v>12.5</v>
@@ -4387,32 +4387,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BA20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD20" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD20" t="n">
+      <c r="BE20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF20" t="n">
         <v>4.2</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BG20" t="n">
         <v>4.4</v>
       </c>
-      <c r="BF20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>2.5</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I23" t="n">
         <v>3.25</v>
@@ -4849,7 +4849,7 @@
         <v>3.55</v>
       </c>
       <c r="L23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
@@ -4864,7 +4864,7 @@
         <v>2.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R23" t="n">
         <v>1.43</v>
@@ -4873,7 +4873,7 @@
         <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U23" t="n">
         <v>2.34</v>
@@ -4882,7 +4882,7 @@
         <v>1.45</v>
       </c>
       <c r="W23" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X23" t="n">
         <v>15</v>
@@ -4891,7 +4891,7 @@
         <v>14</v>
       </c>
       <c r="Z23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="n">
         <v>55</v>
@@ -4906,10 +4906,10 @@
         <v>13.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG23" t="n">
         <v>11.5</v>
@@ -4924,22 +4924,22 @@
         <v>34</v>
       </c>
       <c r="AK23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM23" t="n">
         <v>80</v>
       </c>
       <c r="AN23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AP23" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>13</v>
@@ -4963,16 +4963,16 @@
         <v>29</v>
       </c>
       <c r="AX23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY23" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB23" t="n">
         <v>30</v>
@@ -4987,14 +4987,14 @@
         <v>65</v>
       </c>
       <c r="BF23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG23" t="n">
         <v>25</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G25" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H25" t="n">
         <v>4.2</v>
       </c>
       <c r="I25" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J25" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5252,7 +5252,7 @@
         <v>1.49</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="R25" t="n">
         <v>1.17</v>
@@ -5267,7 +5267,7 @@
         <v>1.58</v>
       </c>
       <c r="V25" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W25" t="n">
         <v>1.76</v>
@@ -5321,7 +5321,7 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO25" t="n">
         <v>180</v>
@@ -5330,59 +5330,253 @@
         <v>3.15</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT25" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AU25" t="n">
         <v>6</v>
       </c>
       <c r="AV25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-04 00:36:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>22:20:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquilla</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Alianza FC Valledupar</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J26" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH25" t="inlineStr">
-        <is>
-          <t>2026-03-03 22:27:55</t>
+      <c r="K26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -757,88 +757,88 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
         <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U2" t="n">
         <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y2" t="n">
         <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
         <v>18.5</v>
@@ -847,46 +847,46 @@
         <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO2" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AP2" t="n">
         <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.6</v>
+        <v>15.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AX2" t="n">
         <v>11.5</v>
@@ -895,32 +895,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.4</v>
+        <v>50</v>
       </c>
       <c r="BB2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -954,58 +954,58 @@
         <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I3" t="n">
         <v>7.8</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
         <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
         <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="X3" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
@@ -1014,13 +1014,13 @@
         <v>70</v>
       </c>
       <c r="AA3" t="n">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="AB3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>34</v>
@@ -1029,10 +1029,10 @@
         <v>160</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
         <v>980</v>
@@ -1047,7 +1047,7 @@
         <v>19.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
         <v>220</v>
@@ -1056,22 +1056,22 @@
         <v>11</v>
       </c>
       <c r="AO3" t="n">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="AP3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU3" t="n">
         <v>8.6</v>
@@ -1080,41 +1080,41 @@
         <v>21</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB3" t="n">
         <v>12</v>
       </c>
       <c r="BC3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD3" t="n">
         <v>38</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>1.89</v>
       </c>
       <c r="G4" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1175,16 +1175,16 @@
         <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="T4" t="n">
         <v>2.04</v>
@@ -1193,122 +1193,122 @@
         <v>1.81</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="I5" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J5" t="n">
         <v>3.05</v>
@@ -1363,7 +1363,7 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O5" t="n">
         <v>1.42</v>
@@ -1387,10 +1387,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
@@ -1408,7 +1408,7 @@
         <v>14</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
         <v>14</v>
@@ -1426,7 +1426,7 @@
         <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
         <v>95</v>
@@ -1450,7 +1450,7 @@
         <v>9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR5" t="n">
         <v>11.5</v>
@@ -1459,7 +1459,7 @@
         <v>3.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
@@ -1498,11 +1498,11 @@
         <v>4.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
@@ -1545,7 +1545,7 @@
         <v>3.65</v>
       </c>
       <c r="J6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>3.5</v>
@@ -1557,43 +1557,43 @@
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q6" t="n">
         <v>2.12</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
         <v>1.81</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V6" t="n">
         <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1605,7 +1605,7 @@
         <v>8.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1644,13 +1644,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT6" t="n">
         <v>8.199999999999999</v>
@@ -1659,44 +1659,44 @@
         <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AY6" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
         <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>4.5</v>
       </c>
       <c r="G7" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="I7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="J7" t="n">
         <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1763,10 +1763,10 @@
         <v>1.35</v>
       </c>
       <c r="R7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S7" t="n">
-        <v>1.35</v>
+        <v>1.91</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>2.88</v>
       </c>
       <c r="O10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P10" t="n">
         <v>1.64</v>
@@ -2351,7 +2351,7 @@
         <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
         <v>1.9</v>
@@ -2375,7 +2375,7 @@
         <v>80</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC10" t="n">
         <v>8.4</v>
@@ -2387,7 +2387,7 @@
         <v>60</v>
       </c>
       <c r="AF10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG10" t="n">
         <v>14</v>
@@ -2399,7 +2399,7 @@
         <v>80</v>
       </c>
       <c r="AJ10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK10" t="n">
         <v>38</v>
@@ -2426,7 +2426,7 @@
         <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT10" t="n">
         <v>7.4</v>
@@ -2438,7 +2438,7 @@
         <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
         <v>13</v>
@@ -2450,29 +2450,29 @@
         <v>17.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
         <v>4.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG10" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="J11" t="n">
         <v>4.6</v>
@@ -2527,43 +2527,43 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
         <v>1.51</v>
       </c>
       <c r="R11" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
         <v>1.64</v>
       </c>
       <c r="U11" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V11" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y11" t="n">
         <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="n">
         <v>17</v>
@@ -2581,13 +2581,13 @@
         <v>17.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG11" t="n">
         <v>29</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
         <v>34</v>
@@ -2602,22 +2602,22 @@
         <v>80</v>
       </c>
       <c r="AM11" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN11" t="n">
         <v>90</v>
       </c>
       <c r="AO11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AP11" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR11" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>8.6</v>
       </c>
       <c r="AS11" t="n">
         <v>12.5</v>
@@ -2626,7 +2626,7 @@
         <v>4.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AV11" t="n">
         <v>9</v>
@@ -2635,38 +2635,38 @@
         <v>11</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AZ11" t="n">
         <v>4.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC11" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BD11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG11" t="n">
         <v>4.8</v>
       </c>
-      <c r="BD11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>55</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G12" t="n">
         <v>1.74</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J12" t="n">
         <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2721,7 +2721,7 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
         <v>1.19</v>
@@ -2748,7 +2748,7 @@
         <v>1.21</v>
       </c>
       <c r="W12" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G13" t="n">
         <v>2.54</v>
@@ -2900,7 +2900,7 @@
         <v>3.1</v>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
         <v>3.3</v>
@@ -2915,7 +2915,7 @@
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
         <v>1.17</v>
@@ -2936,13 +2936,13 @@
         <v>1.53</v>
       </c>
       <c r="U13" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="G17" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="H17" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="I17" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3706,22 +3706,22 @@
         <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
         <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="V17" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>15</v>
+        <v>980</v>
       </c>
       <c r="Y17" t="n">
         <v>6.8</v>
@@ -3733,25 +3733,25 @@
         <v>12.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AC17" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AD17" t="n">
         <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="AF17" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AG17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AH17" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AI17" t="n">
         <v>75</v>
@@ -3763,7 +3763,7 @@
         <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
@@ -3787,50 +3787,50 @@
         <v>9</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>9.6</v>
+        <v>4.3</v>
       </c>
       <c r="AV17" t="n">
         <v>9.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AX17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY17" t="n">
         <v>5.8</v>
       </c>
-      <c r="AY17" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB17" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG17" t="n">
         <v>7.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
         <v>26</v>
       </c>
       <c r="AA18" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB18" t="n">
         <v>8.800000000000001</v>
@@ -3936,7 +3936,7 @@
         <v>18.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF18" t="n">
         <v>17.5</v>
@@ -3951,22 +3951,22 @@
         <v>95</v>
       </c>
       <c r="AJ18" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK18" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL18" t="n">
         <v>80</v>
       </c>
       <c r="AM18" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO18" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP18" t="n">
         <v>7.2</v>
@@ -3978,7 +3978,7 @@
         <v>19</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT18" t="n">
         <v>6.6</v>
@@ -3990,7 +3990,7 @@
         <v>13.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX18" t="n">
         <v>12.5</v>
@@ -4002,29 +4002,29 @@
         <v>19.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF18" t="n">
         <v>5.2</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BG18" t="n">
         <v>5.4</v>
       </c>
-      <c r="BF18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -4061,10 +4061,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I19" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
@@ -4103,7 +4103,7 @@
         <v>1.66</v>
       </c>
       <c r="V19" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="W19" t="n">
         <v>1.12</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G22" t="n">
         <v>4.7</v>
       </c>
       <c r="H22" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
         <v>2.22</v>
       </c>
       <c r="J22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K22" t="n">
         <v>3.65</v>
@@ -4694,7 +4694,7 @@
         <v>12</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z22" t="n">
         <v>13</v>
@@ -4754,53 +4754,53 @@
         <v>10</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AT22" t="n">
         <v>10.5</v>
       </c>
       <c r="AU22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW22" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW22" t="n">
+      <c r="AX22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG22" t="n">
         <v>6.2</v>
       </c>
-      <c r="AX22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
         <v>3.15</v>
       </c>
       <c r="I23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>3.5</v>
@@ -4915,7 +4915,7 @@
         <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI23" t="n">
         <v>42</v>
@@ -4930,19 +4930,19 @@
         <v>34</v>
       </c>
       <c r="AM23" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN23" t="n">
         <v>18.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AP23" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR23" t="n">
         <v>20</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -5028,19 +5028,19 @@
         <v>2.28</v>
       </c>
       <c r="G24" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="H24" t="n">
         <v>2.96</v>
       </c>
       <c r="I24" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="J24" t="n">
         <v>2.86</v>
       </c>
       <c r="K24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5073,10 +5073,10 @@
         <v>1.73</v>
       </c>
       <c r="V24" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W24" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5094,7 +5094,7 @@
         <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD24" t="n">
         <v>1000</v>
@@ -5133,62 +5133,62 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G25" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="J25" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="K25" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5252,7 +5252,7 @@
         <v>1.49</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R25" t="n">
         <v>1.17</v>
@@ -5264,25 +5264,25 @@
         <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V25" t="n">
         <v>1.24</v>
       </c>
       <c r="W25" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="X25" t="n">
         <v>970</v>
       </c>
       <c r="Y25" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z25" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA25" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB25" t="n">
         <v>7.8</v>
@@ -5291,10 +5291,10 @@
         <v>970</v>
       </c>
       <c r="AD25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE25" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF25" t="n">
         <v>970</v>
@@ -5303,10 +5303,10 @@
         <v>970</v>
       </c>
       <c r="AH25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI25" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ25" t="n">
         <v>36</v>
@@ -5324,65 +5324,65 @@
         <v>38</v>
       </c>
       <c r="AO25" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP25" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.05</v>
+        <v>5.8</v>
       </c>
       <c r="AU25" t="n">
         <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX25" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AY25" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE25" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G26" t="n">
         <v>1.6</v>
@@ -5422,7 +5422,7 @@
         <v>7.4</v>
       </c>
       <c r="I26" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J26" t="n">
         <v>4.1</v>
@@ -5449,7 +5449,7 @@
         <v>2.02</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
         <v>3.6</v>
@@ -5467,116 +5467,116 @@
         <v>2.66</v>
       </c>
       <c r="X26" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="Y26" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD26" t="n">
         <v>30</v>
       </c>
-      <c r="Z26" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD26" t="n">
+      <c r="AE26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL26" t="n">
         <v>44</v>
       </c>
-      <c r="AE26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF26" t="n">
+      <c r="AM26" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR26" t="n">
         <v>11</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AS26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW26" t="n">
         <v>12</v>
       </c>
-      <c r="AH26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ26" t="n">
+      <c r="AX26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>20</v>
       </c>
-      <c r="AK26" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>2.88</v>
-      </c>
       <c r="BA26" t="n">
-        <v>3.15</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>2.72</v>
+        <v>12.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.8</v>
+        <v>15.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>2.98</v>
+        <v>10</v>
       </c>
       <c r="BE26" t="n">
-        <v>3.15</v>
+        <v>12.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG26" t="n">
-        <v>3.15</v>
+        <v>12.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-04 00:36:03</t>
+          <t>2026-03-04 02:43:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G2" t="n">
         <v>2.12</v>
@@ -772,7 +772,7 @@
         <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
         <v>1.42</v>
@@ -799,7 +799,7 @@
         <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U2" t="n">
         <v>2.12</v>
@@ -841,7 +841,7 @@
         <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
         <v>60</v>
@@ -871,7 +871,7 @@
         <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AS2" t="n">
         <v>15.5</v>
@@ -901,7 +901,7 @@
         <v>50</v>
       </c>
       <c r="BB2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -954,58 +954,58 @@
         <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H3" t="n">
         <v>7.4</v>
       </c>
       <c r="I3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P3" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="V3" t="n">
         <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
@@ -1014,7 +1014,7 @@
         <v>70</v>
       </c>
       <c r="AA3" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AB3" t="n">
         <v>6.8</v>
@@ -1029,7 +1029,7 @@
         <v>160</v>
       </c>
       <c r="AF3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
@@ -1038,7 +1038,7 @@
         <v>980</v>
       </c>
       <c r="AI3" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AJ3" t="n">
         <v>15</v>
@@ -1047,37 +1047,37 @@
         <v>19.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AM3" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="AN3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>310</v>
+      </c>
+      <c r="AP3" t="n">
         <v>11</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>290</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>15.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU3" t="n">
         <v>8.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
         <v>10</v>
@@ -1089,13 +1089,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
         <v>10</v>
       </c>
       <c r="BB3" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="BC3" t="n">
         <v>16.5</v>
@@ -1104,17 +1104,17 @@
         <v>38</v>
       </c>
       <c r="BE3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="G4" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
@@ -1163,16 +1163,16 @@
         <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P4" t="n">
         <v>1.66</v>
@@ -1193,22 +1193,22 @@
         <v>1.81</v>
       </c>
       <c r="V4" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W4" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="X4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA4" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB4" t="n">
         <v>8.199999999999999</v>
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
         <v>12.5</v>
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT4" t="n">
         <v>6.4</v>
@@ -1274,7 +1274,7 @@
         <v>17.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX4" t="n">
         <v>9.6</v>
@@ -1286,7 +1286,7 @@
         <v>19.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB4" t="n">
         <v>20</v>
@@ -1295,20 +1295,20 @@
         <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF4" t="n">
         <v>14.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I5" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J5" t="n">
         <v>3.05</v>
@@ -1369,28 +1369,28 @@
         <v>1.42</v>
       </c>
       <c r="P5" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V5" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
@@ -1572,7 +1572,7 @@
         <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="T6" t="n">
         <v>1.81</v>
@@ -1584,13 +1584,13 @@
         <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1644,7 +1644,7 @@
         <v>9.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="AR6" t="n">
         <v>5.7</v>
@@ -1653,7 +1653,7 @@
         <v>6.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU6" t="n">
         <v>6.2</v>
@@ -1677,7 +1677,7 @@
         <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>30</v>
+        <v>6.2</v>
       </c>
       <c r="BC6" t="n">
         <v>6</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="I7" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="J7" t="n">
         <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,58 +1751,58 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.56</v>
+        <v>6.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P7" t="n">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="R7" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="S7" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB7" t="n">
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AF7" t="n">
         <v>1000</v>
@@ -1811,7 +1811,7 @@
         <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
@@ -1832,65 +1832,65 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AP7" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
         <v>3.05</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2351,7 +2351,7 @@
         <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
         <v>1.9</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="J11" t="n">
         <v>4.6</v>
@@ -2530,19 +2530,19 @@
         <v>5.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R11" t="n">
         <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T11" t="n">
         <v>1.64</v>
@@ -2551,19 +2551,19 @@
         <v>2.18</v>
       </c>
       <c r="V11" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y11" t="n">
         <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AA11" t="n">
         <v>17</v>
@@ -2578,16 +2578,16 @@
         <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG11" t="n">
         <v>29</v>
       </c>
       <c r="AH11" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AI11" t="n">
         <v>34</v>
@@ -2599,13 +2599,13 @@
         <v>95</v>
       </c>
       <c r="AL11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN11" t="n">
         <v>80</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>90</v>
       </c>
       <c r="AO11" t="n">
         <v>7</v>
@@ -2614,7 +2614,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AR11" t="n">
         <v>9.6</v>
@@ -2623,7 +2623,7 @@
         <v>12.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AU11" t="n">
         <v>10</v>
@@ -2635,38 +2635,38 @@
         <v>11</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BG11" t="n">
         <v>4.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>1.74</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I12" t="n">
         <v>5.6</v>
@@ -2721,28 +2721,28 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="T12" t="n">
         <v>1.64</v>
       </c>
       <c r="U12" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
         <v>1.21</v>
@@ -2751,116 +2751,116 @@
         <v>2.34</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y12" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="Z12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE12" t="n">
         <v>60</v>
       </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AF12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC12" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>11.5</v>
       </c>
       <c r="BD12" t="n">
         <v>20</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.94</v>
+        <v>7.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G13" t="n">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2927,10 +2927,10 @@
         <v>1.54</v>
       </c>
       <c r="R13" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="S13" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="T13" t="n">
         <v>1.53</v>
@@ -2939,122 +2939,122 @@
         <v>2.36</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ13" t="n">
         <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP13" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -3673,16 +3673,16 @@
         <v>15</v>
       </c>
       <c r="H17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="I17" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K17" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,16 +3691,16 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>1.72</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P17" t="n">
         <v>1.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="R17" t="n">
         <v>1.27</v>
@@ -3709,13 +3709,13 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="U17" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="W17" t="n">
         <v>1.07</v>
@@ -3724,10 +3724,10 @@
         <v>980</v>
       </c>
       <c r="Y17" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AA17" t="n">
         <v>12.5</v>
@@ -3778,7 +3778,7 @@
         <v>6.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR17" t="n">
         <v>5.7</v>
@@ -3787,50 +3787,50 @@
         <v>9</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AV17" t="n">
         <v>9.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="AX17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>6.2</v>
       </c>
-      <c r="AY17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BA17" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BG17" t="n">
         <v>7.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -3861,58 +3861,58 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="G18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K18" t="n">
         <v>3.3</v>
       </c>
-      <c r="H18" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1000</v>
-      </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>1.38</v>
+        <v>2.52</v>
       </c>
       <c r="O18" t="n">
-        <v>1.12</v>
+        <v>1.56</v>
       </c>
       <c r="P18" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="R18" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="S18" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W18" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="X18" t="n">
         <v>8.6</v>
@@ -3924,7 +3924,7 @@
         <v>26</v>
       </c>
       <c r="AA18" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB18" t="n">
         <v>8.800000000000001</v>
@@ -3954,7 +3954,7 @@
         <v>48</v>
       </c>
       <c r="AK18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL18" t="n">
         <v>80</v>
@@ -3966,7 +3966,7 @@
         <v>50</v>
       </c>
       <c r="AO18" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
         <v>7.2</v>
@@ -3978,7 +3978,7 @@
         <v>19</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT18" t="n">
         <v>6.6</v>
@@ -3990,7 +3990,7 @@
         <v>13.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX18" t="n">
         <v>12.5</v>
@@ -4002,7 +4002,7 @@
         <v>19.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB18" t="n">
         <v>5.2</v>
@@ -4011,20 +4011,20 @@
         <v>5.1</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF18" t="n">
         <v>5.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I19" t="n">
         <v>1.59</v>
@@ -4070,7 +4070,7 @@
         <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4127,7 +4127,7 @@
         <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE19" t="n">
         <v>21</v>
@@ -4175,50 +4175,50 @@
         <v>11</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV19" t="n">
         <v>4.7</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>6.2</v>
       </c>
       <c r="BA19" t="n">
         <v>6.8</v>
       </c>
       <c r="BB19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC19" t="n">
         <v>7.6</v>
       </c>
-      <c r="BC19" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG19" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H20" t="n">
         <v>3.35</v>
@@ -4267,19 +4267,19 @@
         <v>3.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M20" t="n">
         <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O20" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P20" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q20" t="n">
         <v>2.54</v>
@@ -4306,10 +4306,10 @@
         <v>11</v>
       </c>
       <c r="Y20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA20" t="n">
         <v>80</v>
@@ -4354,7 +4354,7 @@
         <v>44</v>
       </c>
       <c r="AO20" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AP20" t="n">
         <v>7.8</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
         <v>6</v>
       </c>
       <c r="BA22" t="n">
-        <v>40</v>
+        <v>7.2</v>
       </c>
       <c r="BB22" t="n">
         <v>7.8</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
         <v>1.28</v>
       </c>
       <c r="P23" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
         <v>1.89</v>
@@ -4873,10 +4873,10 @@
         <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U23" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V23" t="n">
         <v>1.45</v>
@@ -4894,7 +4894,7 @@
         <v>21</v>
       </c>
       <c r="AA23" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB23" t="n">
         <v>12</v>
@@ -4915,7 +4915,7 @@
         <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI23" t="n">
         <v>42</v>
@@ -4930,19 +4930,19 @@
         <v>34</v>
       </c>
       <c r="AM23" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP23" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
         <v>20</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -5025,170 +5025,170 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.28</v>
+        <v>2.86</v>
       </c>
       <c r="G24" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="H24" t="n">
-        <v>2.96</v>
+        <v>2.54</v>
       </c>
       <c r="I24" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="K24" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="O24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AT24" t="n">
         <v>1.46</v>
       </c>
-      <c r="P24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AU24" t="n">
-        <v>3.25</v>
+        <v>1.43</v>
       </c>
       <c r="AV24" t="n">
-        <v>4</v>
+        <v>1.67</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.8</v>
+        <v>1.67</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>1.57</v>
       </c>
       <c r="AY24" t="n">
-        <v>3.8</v>
+        <v>1.67</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.3</v>
+        <v>1.59</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.9</v>
+        <v>1.67</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.6</v>
+        <v>1.67</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.6</v>
+        <v>1.67</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.8</v>
+        <v>1.67</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.1</v>
+        <v>1.67</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.6</v>
+        <v>1.67</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.9</v>
+        <v>1.67</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G25" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I25" t="n">
         <v>5.5</v>
@@ -5234,7 +5234,7 @@
         <v>2.58</v>
       </c>
       <c r="K25" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5270,7 +5270,7 @@
         <v>1.24</v>
       </c>
       <c r="W25" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X25" t="n">
         <v>970</v>
@@ -5327,13 +5327,13 @@
         <v>160</v>
       </c>
       <c r="AP25" t="n">
-        <v>3.25</v>
+        <v>6.8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS25" t="n">
         <v>5.2</v>
@@ -5348,16 +5348,16 @@
         <v>4.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX25" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AY25" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AZ25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA25" t="n">
         <v>5.2</v>
@@ -5366,23 +5366,23 @@
         <v>4.7</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE25" t="n">
         <v>5.3</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G26" t="n">
         <v>1.6</v>
       </c>
       <c r="H26" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I26" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="J26" t="n">
         <v>4.1</v>
@@ -5434,13 +5434,13 @@
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>1.86</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P26" t="n">
         <v>1.86</v>
@@ -5458,10 +5458,10 @@
         <v>2.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V26" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W26" t="n">
         <v>2.66</v>
@@ -5488,7 +5488,7 @@
         <v>30</v>
       </c>
       <c r="AE26" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF26" t="n">
         <v>8.6</v>
@@ -5515,7 +5515,7 @@
         <v>200</v>
       </c>
       <c r="AN26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
@@ -5527,10 +5527,10 @@
         <v>19</v>
       </c>
       <c r="AR26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT26" t="n">
         <v>6.4</v>
@@ -5542,7 +5542,7 @@
         <v>21</v>
       </c>
       <c r="AW26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX26" t="n">
         <v>7.6</v>
@@ -5554,7 +5554,7 @@
         <v>20</v>
       </c>
       <c r="BA26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB26" t="n">
         <v>12.5</v>
@@ -5563,20 +5563,20 @@
         <v>15.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE26" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF26" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG26" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH26"/>
+  <dimension ref="A1:BH28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G2" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="H2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I2" t="n">
         <v>3.85</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -787,28 +787,28 @@
         <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U2" t="n">
         <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="X2" t="n">
         <v>14.5</v>
@@ -832,13 +832,13 @@
         <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF2" t="n">
         <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
         <v>18</v>
@@ -847,10 +847,10 @@
         <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK2" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AL2" t="n">
         <v>38</v>
@@ -859,28 +859,28 @@
         <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
         <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS2" t="n">
-        <v>15.5</v>
+        <v>60</v>
       </c>
       <c r="AT2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
         <v>14.5</v>
@@ -898,7 +898,7 @@
         <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB2" t="n">
         <v>23</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -957,10 +957,10 @@
         <v>1.57</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
@@ -975,28 +975,28 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R3" t="n">
         <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T3" t="n">
         <v>2.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V3" t="n">
         <v>1.14</v>
@@ -1026,7 +1026,7 @@
         <v>34</v>
       </c>
       <c r="AE3" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AF3" t="n">
         <v>7.8</v>
@@ -1035,10 +1035,10 @@
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ3" t="n">
         <v>15</v>
@@ -1047,7 +1047,7 @@
         <v>19.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
         <v>260</v>
@@ -1095,7 +1095,7 @@
         <v>10</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
         <v>16.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -1148,52 +1148,52 @@
         <v>1.93</v>
       </c>
       <c r="G4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="O4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="V4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
         <v>1.94</v>
@@ -1211,7 +1211,7 @@
         <v>150</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
         <v>9</v>
@@ -1223,28 +1223,28 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
         <v>12.5</v>
       </c>
       <c r="AH4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>26</v>
       </c>
-      <c r="AI4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>27</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>28</v>
       </c>
       <c r="AL4" t="n">
         <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN4" t="n">
         <v>22</v>
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AT4" t="n">
         <v>6.4</v>
@@ -1271,10 +1271,10 @@
         <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX4" t="n">
         <v>9.6</v>
@@ -1283,10 +1283,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB4" t="n">
         <v>20</v>
@@ -1295,20 +1295,20 @@
         <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF4" t="n">
         <v>14.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -1342,61 +1342,61 @@
         <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H5" t="n">
         <v>2.24</v>
       </c>
       <c r="I5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
         <v>1.41</v>
       </c>
-      <c r="M5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.42</v>
-      </c>
       <c r="P5" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="U5" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="V5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z5" t="n">
         <v>17</v>
@@ -1405,16 +1405,16 @@
         <v>40</v>
       </c>
       <c r="AB5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
         <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF5" t="n">
         <v>32</v>
@@ -1423,43 +1423,43 @@
         <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK5" t="n">
         <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP5" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR5" t="n">
         <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.9</v>
+        <v>23</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
@@ -1477,32 +1477,32 @@
         <v>13</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA5" t="n">
         <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BC5" t="n">
         <v>4</v>
       </c>
       <c r="BD5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE5" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE5" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BG5" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
       </c>
       <c r="I6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1578,10 +1578,10 @@
         <v>1.81</v>
       </c>
       <c r="U6" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
         <v>1.6</v>
@@ -1644,13 +1644,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.7</v>
+        <v>18.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT6" t="n">
         <v>7.8</v>
@@ -1659,44 +1659,44 @@
         <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY6" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BA6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG6" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
         <v>2.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="R7" t="n">
         <v>1.78</v>
@@ -1775,7 +1775,7 @@
         <v>2.28</v>
       </c>
       <c r="V7" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="W7" t="n">
         <v>1.16</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -1954,13 +1954,13 @@
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -2115,59 +2115,59 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>2.74</v>
       </c>
       <c r="O9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W9" t="n">
         <v>1.37</v>
       </c>
-      <c r="P9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X9" t="n">
         <v>1000</v>
       </c>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>2.36</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H10" t="n">
         <v>3.3</v>
@@ -2321,7 +2321,7 @@
         <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
         <v>3.35</v>
@@ -2342,7 +2342,7 @@
         <v>1.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
         <v>1.23</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="H11" t="n">
         <v>1.5</v>
@@ -2518,7 +2518,7 @@
         <v>4.6</v>
       </c>
       <c r="K11" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2536,7 +2536,7 @@
         <v>2.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="R11" t="n">
         <v>1.6</v>
@@ -2545,7 +2545,7 @@
         <v>2.42</v>
       </c>
       <c r="T11" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="U11" t="n">
         <v>2.18</v>
@@ -2554,7 +2554,7 @@
         <v>2.74</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>29</v>
@@ -2644,7 +2644,7 @@
         <v>4.7</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="BB11" t="n">
         <v>5.9</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
         <v>2.34</v>
       </c>
       <c r="X12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y12" t="n">
         <v>980</v>
@@ -2763,7 +2763,7 @@
         <v>140</v>
       </c>
       <c r="AB12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
         <v>11</v>
@@ -2778,7 +2778,7 @@
         <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH12" t="n">
         <v>18.5</v>
@@ -2802,19 +2802,19 @@
         <v>7.6</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ12" t="n">
         <v>20</v>
       </c>
       <c r="AR12" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
@@ -2826,7 +2826,7 @@
         <v>17.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX12" t="n">
         <v>10.5</v>
@@ -2838,10 +2838,10 @@
         <v>14.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.2</v>
+        <v>44</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BC12" t="n">
         <v>13.5</v>
@@ -2850,7 +2850,7 @@
         <v>20</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF12" t="n">
         <v>6.2</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G13" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
         <v>3.85</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2936,16 +2936,16 @@
         <v>1.53</v>
       </c>
       <c r="U13" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X13" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Y13" t="n">
         <v>24</v>
@@ -2957,22 +2957,22 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC13" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD13" t="n">
         <v>18</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF13" t="n">
         <v>18.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
         <v>18</v>
@@ -3008,7 +3008,7 @@
         <v>21</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT13" t="n">
         <v>12.5</v>
@@ -3032,10 +3032,10 @@
         <v>12.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BC13" t="n">
         <v>16.5</v>
@@ -3044,7 +3044,7 @@
         <v>19.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF13" t="n">
         <v>7.6</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,31 +3076,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>2.8</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3109,34 +3109,34 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>1.41</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -3270,12 +3270,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cavese 1919</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -3306,19 +3306,19 @@
         <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="P15" t="n">
         <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Cavese 1919</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -3485,7 +3485,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -3500,19 +3500,19 @@
         <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P16" t="n">
         <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="R16" t="n">
         <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="G17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG17" t="n">
         <v>15</v>
       </c>
-      <c r="H17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X17" t="n">
-        <v>980</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z17" t="n">
+      <c r="AH17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
         <v>7.2</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AQ17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX17" t="n">
         <v>12.5</v>
       </c>
-      <c r="AB17" t="n">
-        <v>980</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>980</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>130</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>280</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AR17" t="n">
+      <c r="AY17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE17" t="n">
         <v>5.7</v>
       </c>
-      <c r="AS17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BF17" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,179 +3852,179 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9</v>
+        <v>1.02</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>2.52</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.56</v>
+        <v>1.02</v>
       </c>
       <c r="P18" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.66</v>
+        <v>1.42</v>
       </c>
       <c r="R18" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>5.5</v>
+        <v>1.42</v>
       </c>
       <c r="T18" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="G19" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="I19" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4079,146 +4079,146 @@
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
         <v>1.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="R19" t="n">
         <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="U19" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="Y19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>280</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP19" t="n">
         <v>6.8</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AQ19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS19" t="n">
         <v>9</v>
       </c>
-      <c r="AA19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>360</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>180</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>200</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>330</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>11</v>
-      </c>
       <c r="AT19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.8</v>
+        <v>15.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC19" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.42</v>
+        <v>7.2</v>
       </c>
       <c r="G20" t="n">
-        <v>2.62</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>3.35</v>
+        <v>1.5</v>
       </c>
       <c r="I20" t="n">
-        <v>3.8</v>
+        <v>1.59</v>
       </c>
       <c r="J20" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N20" t="n">
         <v>3.2</v>
       </c>
-      <c r="L20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.12</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.62</v>
-      </c>
       <c r="X20" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>360</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>180</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>330</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS20" t="n">
         <v>11</v>
       </c>
-      <c r="Y20" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AT20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG20" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AC20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
-        <v>1.02</v>
+        <v>2.96</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N21" t="n">
-        <v>1.25</v>
+        <v>2.66</v>
       </c>
       <c r="O21" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.42</v>
+        <v>2.54</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>1.42</v>
+        <v>5.1</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Quindio</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
-        <v>2.22</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="K22" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>2.86</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="P22" t="n">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.3</v>
+        <v>1.28</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>4.4</v>
+        <v>1.29</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
         <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,179 +4822,179 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.48</v>
+        <v>3.95</v>
       </c>
       <c r="G23" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J23" t="n">
         <v>3.15</v>
-      </c>
-      <c r="I23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.5</v>
       </c>
       <c r="K23" t="n">
         <v>3.55</v>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3</v>
+        <v>2.86</v>
       </c>
       <c r="O23" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>2.36</v>
+        <v>1.84</v>
       </c>
       <c r="V23" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="W23" t="n">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y23" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AA23" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AB23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB23" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR23" t="n">
+      <c r="BC23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG23" t="n">
         <v>20</v>
       </c>
-      <c r="AS23" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>25</v>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarc</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Internacional de Palmir</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.86</v>
+        <v>1.58</v>
       </c>
       <c r="G24" t="n">
-        <v>3.55</v>
+        <v>1.71</v>
       </c>
       <c r="H24" t="n">
-        <v>2.54</v>
+        <v>6.2</v>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>9.6</v>
       </c>
       <c r="J24" t="n">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="K24" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="P24" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="R24" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="U24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BC24" t="n">
         <v>1.71</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.67</v>
-      </c>
       <c r="BD24" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,378 +5205,766 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="G25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="I25" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="J25" t="n">
-        <v>2.58</v>
+        <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M25" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>2.46</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="P25" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.58</v>
+        <v>1.89</v>
       </c>
       <c r="R25" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="U25" t="n">
-        <v>1.6</v>
+        <v>2.36</v>
       </c>
       <c r="V25" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="W25" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="X25" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Y25" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA25" t="n">
         <v>38</v>
       </c>
-      <c r="AA25" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH25" t="n">
+      <c r="BB25" t="n">
         <v>30</v>
       </c>
-      <c r="AI25" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BC25" t="n">
-        <v>4.8</v>
+        <v>22</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.1</v>
+        <v>32</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.3</v>
+        <v>65</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.8</v>
+        <v>17</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.3</v>
+        <v>25</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Real Soacha Cundinamarc</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Internacional de Palmir</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-04 06:59:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>20:10:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X27" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-04 06:59:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>22:20:00</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Junior FC Barranquilla</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Alianza FC Valledupar</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="F28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H28" t="n">
+        <v>7</v>
+      </c>
+      <c r="I28" t="n">
+        <v>8</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X28" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB28" t="n">
         <v>7.2</v>
       </c>
-      <c r="I26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X26" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>270</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD26" t="n">
+      <c r="AC28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD28" t="n">
         <v>30</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AE28" t="n">
         <v>140</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AF28" t="n">
         <v>8.6</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AG28" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH26" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ26" t="n">
+      <c r="AH28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>14.5</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AK28" t="n">
         <v>18</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AL28" t="n">
         <v>44</v>
       </c>
-      <c r="AM26" t="n">
+      <c r="AM28" t="n">
         <v>200</v>
       </c>
-      <c r="AN26" t="n">
+      <c r="AN28" t="n">
         <v>10.5</v>
       </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
         <v>12</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="AQ28" t="n">
         <v>19</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AR28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD28" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF26" t="n">
+      <c r="BE28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF28" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BG26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BH26" t="inlineStr">
-        <is>
-          <t>2026-03-04 04:51:44</t>
+      <c r="BG28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH28"/>
+  <dimension ref="A1:BH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,31 +799,31 @@
         <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V2" t="n">
         <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="X2" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
@@ -835,7 +835,7 @@
         <v>46</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
@@ -844,13 +844,13 @@
         <v>18</v>
       </c>
       <c r="AI2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
         <v>27</v>
       </c>
       <c r="AK2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
         <v>38</v>
@@ -862,10 +862,10 @@
         <v>16.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
         <v>13</v>
@@ -883,13 +883,13 @@
         <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
         <v>9.800000000000001</v>
@@ -910,17 +910,17 @@
         <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>16.5</v>
+        <v>85</v>
       </c>
       <c r="BF2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H3" t="n">
         <v>7.6</v>
       </c>
       <c r="I3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
@@ -993,19 +993,19 @@
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V3" t="n">
         <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
@@ -1014,13 +1014,13 @@
         <v>70</v>
       </c>
       <c r="AA3" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AB3" t="n">
         <v>6.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
         <v>34</v>
@@ -1029,13 +1029,13 @@
         <v>170</v>
       </c>
       <c r="AF3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI3" t="n">
         <v>160</v>
@@ -1044,16 +1044,16 @@
         <v>15</v>
       </c>
       <c r="AK3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AM3" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO3" t="n">
         <v>310</v>
@@ -1062,59 +1062,59 @@
         <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS3" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>10</v>
       </c>
       <c r="AT3" t="n">
         <v>5.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>24</v>
+        <v>7.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX3" t="n">
         <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>7.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB3" t="n">
         <v>12</v>
       </c>
       <c r="BC3" t="n">
-        <v>16.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -1145,76 +1145,76 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H4" t="n">
         <v>4.5</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q4" t="n">
         <v>2.26</v>
       </c>
       <c r="R4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
         <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="U4" t="n">
         <v>1.86</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W4" t="n">
         <v>1.94</v>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA4" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC4" t="n">
         <v>8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9</v>
       </c>
       <c r="AD4" t="n">
         <v>23</v>
@@ -1223,92 +1223,92 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK4" t="n">
         <v>25</v>
       </c>
-      <c r="AI4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>27</v>
-      </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
         <v>180</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AS4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT4" t="n">
         <v>5.8</v>
       </c>
-      <c r="AT4" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AU4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA4" t="n">
         <v>7</v>
       </c>
-      <c r="AV4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BB4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC4" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF4" t="n">
         <v>14.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J5" t="n">
         <v>3.1</v>
@@ -1357,7 +1357,7 @@
         <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
@@ -1366,7 +1366,7 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="P5" t="n">
         <v>1.69</v>
@@ -1378,19 +1378,19 @@
         <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="U5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V5" t="n">
         <v>1.67</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X5" t="n">
         <v>14</v>
@@ -1429,16 +1429,16 @@
         <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
         <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
         <v>75</v>
@@ -1447,37 +1447,37 @@
         <v>30</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AR5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY5" t="n">
         <v>11.5</v>
       </c>
-      <c r="AS5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>13</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
         <v>4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G6" t="n">
         <v>2.68</v>
@@ -1542,34 +1542,34 @@
         <v>3.25</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
         <v>3.85</v>
@@ -1581,16 +1581,16 @@
         <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1599,104 +1599,104 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AQ6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT6" t="n">
         <v>7</v>
       </c>
-      <c r="AT6" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="AX6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB6" t="n">
         <v>5.3</v>
       </c>
-      <c r="AY6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ6" t="n">
+      <c r="BC6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD6" t="n">
         <v>5.5</v>
       </c>
-      <c r="BA6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE6" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K7" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,58 +1751,58 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="O7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.14</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.16</v>
-      </c>
       <c r="X7" t="n">
         <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
         <v>1000</v>
@@ -1811,7 +1811,7 @@
         <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
@@ -1832,65 +1832,65 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -1921,64 +1921,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.4</v>
+        <v>2.52</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1987,22 +1987,22 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -2115,61 +2115,61 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="P9" t="n">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.98</v>
+        <v>2.52</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -2181,10 +2181,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.15</v>
+        <v>7.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AS9" t="n">
         <v>4</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.92</v>
+        <v>5.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BA9" t="n">
         <v>4</v>
       </c>
       <c r="BB9" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BD9" t="n">
         <v>4</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -2321,13 +2321,13 @@
         <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K10" t="n">
         <v>3.35</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
@@ -2336,7 +2336,7 @@
         <v>2.88</v>
       </c>
       <c r="O10" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="P10" t="n">
         <v>1.64</v>
@@ -2351,10 +2351,10 @@
         <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
         <v>1.39</v>
@@ -2387,7 +2387,7 @@
         <v>60</v>
       </c>
       <c r="AF10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG10" t="n">
         <v>14</v>
@@ -2408,7 +2408,7 @@
         <v>60</v>
       </c>
       <c r="AM10" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
         <v>36</v>
@@ -2417,37 +2417,37 @@
         <v>70</v>
       </c>
       <c r="AP10" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AS10" t="n">
         <v>4.9</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AV10" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AW10" t="n">
         <v>4.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
         <v>4.9</v>
@@ -2456,23 +2456,23 @@
         <v>4.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BD10" t="n">
         <v>4.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>6.2</v>
       </c>
       <c r="G11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="H11" t="n">
         <v>1.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="J11" t="n">
         <v>4.6</v>
@@ -2521,25 +2521,25 @@
         <v>5.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P11" t="n">
         <v>2.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S11" t="n">
         <v>2.42</v>
@@ -2548,125 +2548,125 @@
         <v>1.73</v>
       </c>
       <c r="U11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V11" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z11" t="n">
         <v>11.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AB11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AD11" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE11" t="n">
         <v>15.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AP11" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="AU11" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.7</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
         <v>21</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG11" t="n">
         <v>4.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -2700,22 +2700,22 @@
         <v>1.64</v>
       </c>
       <c r="G12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H12" t="n">
         <v>5.1</v>
       </c>
       <c r="I12" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K12" t="n">
         <v>4.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
@@ -2724,143 +2724,143 @@
         <v>5.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R12" t="n">
         <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="U12" t="n">
         <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X12" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y12" t="n">
         <v>25</v>
       </c>
-      <c r="Y12" t="n">
-        <v>980</v>
-      </c>
       <c r="Z12" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AA12" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC12" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>11</v>
       </c>
       <c r="AD12" t="n">
         <v>22</v>
       </c>
       <c r="AE12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
         <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AK12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AL12" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AM12" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AN12" t="n">
         <v>7.6</v>
       </c>
       <c r="AO12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>44</v>
+        <v>5.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BC12" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BD12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>36</v>
+        <v>5.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -2891,61 +2891,61 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G13" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="H13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="J13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M13" t="n">
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R13" t="n">
         <v>1.62</v>
       </c>
       <c r="S13" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="T13" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="U13" t="n">
         <v>2.56</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="X13" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y13" t="n">
         <v>24</v>
@@ -2957,22 +2957,22 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD13" t="n">
         <v>18</v>
       </c>
       <c r="AE13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH13" t="n">
         <v>18</v>
@@ -2981,13 +2981,13 @@
         <v>42</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK13" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AL13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -3002,49 +3002,49 @@
         <v>10.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX13" t="n">
         <v>12.5</v>
       </c>
-      <c r="AU13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AY13" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ13" t="n">
         <v>12.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.7</v>
+        <v>20</v>
       </c>
       <c r="BC13" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>19.5</v>
+        <v>3.85</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="BF13" t="n">
         <v>7.6</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT14" t="n">
         <v>6.6</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -3279,46 +3279,46 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>2.24</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.41</v>
+        <v>2.16</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S15" t="n">
-        <v>1.41</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -3327,10 +3327,10 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -3473,58 +3473,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>1.9</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>2.72</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3539,10 +3539,10 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
@@ -3581,69 +3581,69 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="G17" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="H17" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="I17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.85</v>
       </c>
-      <c r="J17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="T17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.49</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.35</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="X17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC17" t="n">
         <v>8.6</v>
       </c>
-      <c r="Y17" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8</v>
-      </c>
       <c r="AD17" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AF17" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AG17" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AK17" t="n">
         <v>42</v>
       </c>
       <c r="AL17" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP17" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV17" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J18" t="n">
-        <v>1.02</v>
+        <v>2.78</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.42</v>
+        <v>2.36</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S18" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,179 +4046,179 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X19" t="n">
         <v>10.5</v>
       </c>
-      <c r="G19" t="n">
-        <v>15</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X19" t="n">
-        <v>980</v>
-      </c>
       <c r="Y19" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP19" t="n">
         <v>6.4</v>
       </c>
-      <c r="Z19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>980</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>980</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>980</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>130</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>280</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AQ19" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.7</v>
+        <v>18.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="AT19" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>15.5</v>
+        <v>4.1</v>
       </c>
       <c r="AX19" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AY19" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7.6</v>
+        <v>16.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="BC19" t="n">
-        <v>9</v>
+        <v>3.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -4240,145 +4240,145 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>7.2</v>
+        <v>1.09</v>
       </c>
       <c r="G20" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="I20" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M20" t="n">
         <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="O20" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>1.02</v>
       </c>
       <c r="T20" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="V20" t="n">
-        <v>2.68</v>
+        <v>3.15</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Y20" t="n">
         <v>6.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AD20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AP20" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="AS20" t="n">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="AT20" t="n">
         <v>6</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AX20" t="n">
         <v>7.2</v>
@@ -4393,26 +4393,26 @@
         <v>6.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.42</v>
+        <v>6.8</v>
       </c>
       <c r="G21" t="n">
-        <v>2.62</v>
+        <v>10.5</v>
       </c>
       <c r="H21" t="n">
-        <v>3.35</v>
+        <v>1.48</v>
       </c>
       <c r="I21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV21" t="n">
         <v>3.8</v>
       </c>
-      <c r="J21" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="AW21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX21" t="n">
         <v>5.1</v>
       </c>
-      <c r="T21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AY21" t="n">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BA21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC21" t="n">
         <v>5.3</v>
       </c>
-      <c r="BB21" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD21" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="J22" t="n">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N22" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="O22" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.28</v>
+        <v>2.52</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S22" t="n">
-        <v>1.29</v>
+        <v>3.45</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,184 +4817,184 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Quindio</t>
+          <t>Trapani</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.95</v>
+        <v>1.58</v>
       </c>
       <c r="G23" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W23" t="n">
         <v>2</v>
       </c>
-      <c r="I23" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.27</v>
-      </c>
       <c r="X23" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
         <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -5016,40 +5016,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.58</v>
+        <v>3.9</v>
       </c>
       <c r="G24" t="n">
-        <v>1.71</v>
+        <v>4.8</v>
       </c>
       <c r="H24" t="n">
-        <v>6.2</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>9.6</v>
+        <v>2.22</v>
       </c>
       <c r="J24" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
         <v>1.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="O24" t="n">
         <v>1.44</v>
@@ -5064,55 +5064,55 @@
         <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="U24" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="V24" t="n">
-        <v>1.13</v>
+        <v>1.81</v>
       </c>
       <c r="W24" t="n">
-        <v>2.38</v>
+        <v>1.27</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ24" t="n">
         <v>1000</v>
@@ -5130,72 +5130,72 @@
         <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.52</v>
+        <v>8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>2.06</v>
+        <v>5.8</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.8</v>
+        <v>9.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.83</v>
+        <v>21</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.45</v>
+        <v>9.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.75</v>
+        <v>8.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.82</v>
+        <v>20</v>
       </c>
       <c r="AX24" t="n">
-        <v>2.44</v>
+        <v>5.8</v>
       </c>
       <c r="AY24" t="n">
-        <v>2.52</v>
+        <v>13.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.75</v>
+        <v>16.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.82</v>
+        <v>36</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.84</v>
+        <v>6.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.71</v>
+        <v>6.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.79</v>
+        <v>6.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.83</v>
+        <v>6.8</v>
       </c>
       <c r="BF24" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.83</v>
+        <v>18.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.48</v>
+        <v>1.56</v>
       </c>
       <c r="G25" t="n">
-        <v>2.5</v>
+        <v>1.76</v>
       </c>
       <c r="H25" t="n">
-        <v>3.15</v>
+        <v>6.2</v>
       </c>
       <c r="I25" t="n">
-        <v>3.2</v>
+        <v>9.6</v>
       </c>
       <c r="J25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU25" t="n">
         <v>3.5</v>
       </c>
-      <c r="K25" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N25" t="n">
+      <c r="AV25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC25" t="n">
         <v>4.3</v>
       </c>
-      <c r="O25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X25" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>48</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>22</v>
-      </c>
       <c r="BD25" t="n">
-        <v>32</v>
+        <v>4.9</v>
       </c>
       <c r="BE25" t="n">
-        <v>65</v>
+        <v>1.92</v>
       </c>
       <c r="BF25" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="BG25" t="n">
-        <v>25</v>
+        <v>1.93</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarc</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Internacional de Palmir</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="G26" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H26" t="n">
         <v>3.2</v>
       </c>
-      <c r="H26" t="n">
-        <v>2.62</v>
-      </c>
       <c r="I26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S26" t="n">
         <v>3.15</v>
       </c>
-      <c r="J26" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S26" t="n">
-        <v>4.9</v>
-      </c>
       <c r="T26" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="U26" t="n">
-        <v>1.74</v>
+        <v>2.36</v>
       </c>
       <c r="V26" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W26" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="X26" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY26" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AZ26" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.84</v>
+        <v>38</v>
       </c>
       <c r="BB26" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="BD26" t="n">
-        <v>2.84</v>
+        <v>32</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.22</v>
+        <v>65</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.4</v>
+        <v>25</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,156 +5593,156 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Real Soacha Cundinamarc</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Internacional de Palmir</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="G27" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2</v>
+        <v>2.64</v>
       </c>
       <c r="I27" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="J27" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="K27" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M27" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N27" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="P27" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="R27" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="U27" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="V27" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="W27" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="X27" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="Z27" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT27" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT27" t="n">
+      <c r="AU27" t="n">
         <v>5.8</v>
       </c>
-      <c r="AU27" t="n">
-        <v>6</v>
-      </c>
       <c r="AV27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX27" t="n">
         <v>4.4</v>
       </c>
-      <c r="AW27" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AY27" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AZ27" t="n">
         <v>4.6</v>
@@ -5751,26 +5751,26 @@
         <v>5.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BD27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BF27" t="n">
         <v>5.1</v>
       </c>
-      <c r="BE27" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG27" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-04 06:59:45</t>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>
@@ -5787,184 +5787,378 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>20:10:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-04 09:11:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>22:20:00</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Junior FC Barranquilla</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Alianza FC Valledupar</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F29" t="n">
         <v>1.55</v>
       </c>
-      <c r="G28" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="H28" t="n">
+      <c r="G29" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H29" t="n">
         <v>7</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I29" t="n">
         <v>8</v>
       </c>
-      <c r="J28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K28" t="n">
+      <c r="J29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" t="n">
         <v>4.5</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="L29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P29" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q29" t="n">
         <v>2.04</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R29" t="n">
         <v>1.31</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V28" t="n">
+      <c r="S29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V29" t="n">
         <v>1.14</v>
       </c>
-      <c r="W28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X28" t="n">
+      <c r="W29" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC29" t="n">
         <v>14</v>
       </c>
-      <c r="Y28" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>260</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>13</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>13</v>
-      </c>
-      <c r="BH28" t="inlineStr">
-        <is>
-          <t>2026-03-04 06:59:45</t>
+      <c r="BD29" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-04 09:11:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH29"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G2" t="n">
         <v>2.18</v>
       </c>
       <c r="H2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I2" t="n">
         <v>3.85</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
         <v>3.65</v>
@@ -781,25 +781,25 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R2" t="n">
         <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U2" t="n">
         <v>2.14</v>
@@ -817,7 +817,7 @@
         <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
+        <v>980</v>
       </c>
       <c r="AA2" t="n">
         <v>75</v>
@@ -829,19 +829,19 @@
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>980</v>
       </c>
       <c r="AE2" t="n">
         <v>46</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.5</v>
+        <v>980</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>980</v>
       </c>
       <c r="AH2" t="n">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="AI2" t="n">
         <v>55</v>
@@ -856,25 +856,25 @@
         <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN2" t="n">
-        <v>16.5</v>
+        <v>980</v>
       </c>
       <c r="AO2" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS2" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="AT2" t="n">
         <v>8.800000000000001</v>
@@ -886,10 +886,10 @@
         <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>40</v>
+        <v>15.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY2" t="n">
         <v>9.800000000000001</v>
@@ -898,10 +898,10 @@
         <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>48</v>
+        <v>16.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>23</v>
+        <v>6.8</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
@@ -910,7 +910,7 @@
         <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="BF2" t="n">
         <v>15</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="H3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
         <v>4.4</v>
@@ -975,22 +975,22 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P3" t="n">
         <v>1.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R3" t="n">
         <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
         <v>2.28</v>
@@ -1002,13 +1002,13 @@
         <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="X3" t="n">
         <v>13</v>
       </c>
       <c r="Y3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z3" t="n">
         <v>70</v>
@@ -1017,7 +1017,7 @@
         <v>340</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC3" t="n">
         <v>10.5</v>
@@ -1029,13 +1029,13 @@
         <v>170</v>
       </c>
       <c r="AF3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
         <v>160</v>
@@ -1047,74 +1047,74 @@
         <v>20</v>
       </c>
       <c r="AL3" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="AP3" t="n">
         <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
         <v>5.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AX3" t="n">
         <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.199999999999999</v>
+        <v>90</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -1154,13 +1154,13 @@
         <v>4.5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.43</v>
@@ -1172,7 +1172,7 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
         <v>1.68</v>
@@ -1184,10 +1184,10 @@
         <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
         <v>1.86</v>
@@ -1202,113 +1202,113 @@
         <v>12.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AA4" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AI4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AL4" t="n">
         <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.2</v>
+        <v>3.05</v>
       </c>
       <c r="AS4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU4" t="n">
         <v>7</v>
       </c>
-      <c r="AT4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6</v>
-      </c>
       <c r="AV4" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>55</v>
+        <v>3.15</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.5</v>
+        <v>2.92</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="BB4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>34</v>
+        <v>3.05</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.2</v>
+        <v>3.25</v>
       </c>
       <c r="BF4" t="n">
         <v>14.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>3.4</v>
       </c>
       <c r="G5" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I5" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
         <v>3.6</v>
@@ -1363,10 +1363,10 @@
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
         <v>1.69</v>
@@ -1378,19 +1378,19 @@
         <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T5" t="n">
         <v>1.74</v>
       </c>
       <c r="U5" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="V5" t="n">
         <v>1.67</v>
       </c>
       <c r="W5" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="X5" t="n">
         <v>14</v>
@@ -1447,37 +1447,37 @@
         <v>30</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU5" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AV5" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AY5" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BA5" t="n">
         <v>4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="H6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
         <v>3.05</v>
@@ -1551,46 +1551,46 @@
         <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S6" t="n">
         <v>3.15</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.85</v>
-      </c>
       <c r="T6" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="U6" t="n">
         <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1611,13 +1611,13 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.6</v>
+        <v>2.08</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.6</v>
+        <v>2.04</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.5</v>
+        <v>1.73</v>
       </c>
       <c r="AV6" t="n">
-        <v>10.5</v>
+        <v>2.08</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.5</v>
+        <v>30</v>
       </c>
       <c r="AX6" t="n">
-        <v>11.5</v>
+        <v>1.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13</v>
+        <v>1.93</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.6</v>
+        <v>2.04</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="BC6" t="n">
-        <v>21</v>
+        <v>1.98</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.5</v>
+        <v>2.02</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.9</v>
+        <v>2.08</v>
       </c>
       <c r="BF6" t="n">
-        <v>19</v>
+        <v>2.08</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.5</v>
+        <v>2.08</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G7" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="I7" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="J7" t="n">
         <v>4.3</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,34 +1751,34 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="O7" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="R7" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="S7" t="n">
         <v>1.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V7" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -1912,179 +1912,179 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>US Latina Calcio</t>
+          <t>S.S.D. Casarano Calcio</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="G8" t="n">
         <v>2.72</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.52</v>
+        <v>1.97</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="X8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y8" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC8" t="n">
+      <c r="AR8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AU8" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
         <v>12</v>
       </c>
       <c r="AW8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE8" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BF8" t="n">
-        <v>4</v>
+        <v>15.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -2106,34 +2106,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FC Giugliano</t>
+          <t>US Latina Calcio</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J9" t="n">
         <v>2.88</v>
       </c>
-      <c r="H9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.76</v>
-      </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M9" t="n">
         <v>1.12</v>
@@ -2142,37 +2142,37 @@
         <v>2.52</v>
       </c>
       <c r="O9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="U9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2181,22 +2181,22 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC9" t="n">
         <v>8.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2223,69 +2223,69 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.7</v>
+        <v>18</v>
       </c>
       <c r="AS9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU9" t="n">
         <v>5.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.45</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.45</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.7</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB9" t="n">
         <v>3.95</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BD9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG9" t="n">
         <v>4.1</v>
       </c>
-      <c r="BF9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>FC Giugliano</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="G10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BE10" t="n">
         <v>2.58</v>
       </c>
-      <c r="H10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X10" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5</v>
-      </c>
       <c r="BF10" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.8</v>
+        <v>2.54</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Estonian Esiliiga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,96 +2489,96 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>JK Welco Elekter</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>1.58</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>4.6</v>
+        <v>1.02</v>
       </c>
       <c r="K11" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P11" t="n">
         <v>1.25</v>
       </c>
-      <c r="M11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.48</v>
-      </c>
       <c r="Q11" t="n">
-        <v>1.56</v>
+        <v>1.08</v>
       </c>
       <c r="R11" t="n">
-        <v>1.59</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>2.42</v>
+        <v>1.08</v>
       </c>
       <c r="T11" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
         <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
         <v>1000</v>
@@ -2587,7 +2587,7 @@
         <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
@@ -2608,72 +2608,72 @@
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FC Basel</t>
+          <t>AZ Picerno ASD</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Grasshoppers Zurich</t>
+          <t>Atalanta B</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.64</v>
+        <v>2.82</v>
       </c>
       <c r="G12" t="n">
-        <v>1.75</v>
+        <v>3.45</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>2.84</v>
       </c>
       <c r="J12" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB12" t="n">
         <v>4.7</v>
       </c>
-      <c r="L12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="X12" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="BC12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG12" t="n">
         <v>20</v>
       </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>St Gallen</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G13" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="I13" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="L13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R13" t="n">
         <v>1.23</v>
       </c>
-      <c r="M13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.62</v>
-      </c>
       <c r="S13" t="n">
-        <v>2.28</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="U13" t="n">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="X13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="AC13" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AI13" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AK13" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AL13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>10.5</v>
+        <v>2.46</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AS13" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="AT13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AX13" t="n">
         <v>11</v>
       </c>
-      <c r="AU13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AY13" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12.5</v>
+        <v>2.26</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.95</v>
+        <v>2.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>20</v>
+        <v>2.34</v>
       </c>
       <c r="BC13" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.85</v>
+        <v>2.38</v>
       </c>
       <c r="BE13" t="n">
-        <v>4</v>
+        <v>2.46</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>2.46</v>
       </c>
       <c r="BG13" t="n">
-        <v>14.5</v>
+        <v>2.46</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,184 +3071,184 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.82</v>
+        <v>6.2</v>
       </c>
       <c r="G14" t="n">
-        <v>1.98</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X14" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA14" t="n">
         <v>4.5</v>
       </c>
-      <c r="I14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>5</v>
       </c>
-      <c r="AT14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW14" t="n">
+      <c r="BC14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD14" t="n">
         <v>4.8</v>
       </c>
-      <c r="AX14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BE14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG14" t="n">
         <v>5</v>
       </c>
-      <c r="BF14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Cavese 1919</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.2</v>
+        <v>1.74</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4</v>
+        <v>2.04</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
-        <v>2.24</v>
+        <v>3.05</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="P15" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R15" t="n">
         <v>1.21</v>
       </c>
       <c r="S15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR15" t="n">
         <v>4</v>
       </c>
-      <c r="T15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>FC Basel</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cavese 1919</t>
+          <t>Grasshoppers Zurich</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G16" t="n">
         <v>1.76</v>
       </c>
-      <c r="G16" t="n">
-        <v>1.9</v>
-      </c>
       <c r="H16" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="I16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X16" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE16" t="n">
         <v>7.2</v>
       </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU16" t="n">
+      <c r="BF16" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BG16" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>St Gallen</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.76</v>
+        <v>2.14</v>
       </c>
       <c r="G17" t="n">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="H17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P17" t="n">
         <v>2.56</v>
       </c>
-      <c r="I17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="Q17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X17" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS17" t="n">
         <v>3.95</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X17" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AT17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV17" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AW17" t="n">
-        <v>4.5</v>
+        <v>24</v>
       </c>
       <c r="AX17" t="n">
         <v>14.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.7</v>
+        <v>19</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,179 +3852,179 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.46</v>
+        <v>1.86</v>
       </c>
       <c r="G18" t="n">
-        <v>2.74</v>
+        <v>1.98</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
-        <v>2.78</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="P18" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="U18" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="V18" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="W18" t="n">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="X18" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX18" t="n">
         <v>10</v>
       </c>
-      <c r="Z18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD18" t="n">
+      <c r="AY18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>17</v>
       </c>
-      <c r="AE18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY18" t="n">
+      <c r="BA18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE18" t="n">
         <v>5</v>
       </c>
-      <c r="AZ18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BF18" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="H19" t="n">
-        <v>3.65</v>
+        <v>2.12</v>
       </c>
       <c r="I19" t="n">
-        <v>4.3</v>
+        <v>2.54</v>
       </c>
       <c r="J19" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="K19" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
         <v>1.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="O19" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="P19" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="W19" t="n">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="X19" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
         <v>8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="AR19" t="n">
-        <v>18.5</v>
+        <v>3.95</v>
       </c>
       <c r="AS19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE19" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.09</v>
+        <v>2.72</v>
       </c>
       <c r="G20" t="n">
-        <v>16</v>
+        <v>3.05</v>
       </c>
       <c r="H20" t="n">
-        <v>1.35</v>
+        <v>2.6</v>
       </c>
       <c r="I20" t="n">
-        <v>1.45</v>
+        <v>3.15</v>
       </c>
       <c r="J20" t="n">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="K20" t="n">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
         <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
         <v>1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>1.02</v>
+        <v>3.55</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="V20" t="n">
-        <v>3.15</v>
+        <v>1.46</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.48</v>
       </c>
       <c r="X20" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD20" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>12</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO20" t="n">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.7</v>
+        <v>13.5</v>
       </c>
       <c r="AS20" t="n">
         <v>4.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AU20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA20" t="n">
         <v>4.6</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BB20" t="n">
         <v>4.6</v>
       </c>
-      <c r="AW20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BC20" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -4434,142 +4434,142 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>16</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V21" t="n">
+        <v>3</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y21" t="n">
         <v>6.8</v>
       </c>
-      <c r="G21" t="n">
+      <c r="Z21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
         <v>10.5</v>
       </c>
-      <c r="H21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>12</v>
-      </c>
       <c r="AP21" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="AS21" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AW21" t="n">
         <v>4.3</v>
@@ -4578,42 +4578,42 @@
         <v>5.1</v>
       </c>
       <c r="AY21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AZ21" t="n">
         <v>4.8</v>
       </c>
       <c r="BA21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BC21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF21" t="n">
         <v>5.3</v>
       </c>
-      <c r="BD21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BG21" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>2.36</v>
+        <v>1.02</v>
       </c>
       <c r="O22" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="P22" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="T22" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trapani</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.58</v>
+        <v>2.26</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>2.74</v>
       </c>
       <c r="H23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU23" t="n">
         <v>6.2</v>
       </c>
-      <c r="I23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Quindio</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.9</v>
+        <v>2.32</v>
       </c>
       <c r="G24" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="I24" t="n">
-        <v>2.22</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
-        <v>3.15</v>
+        <v>1.09</v>
       </c>
       <c r="K24" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="O24" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="P24" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="R24" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="S24" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="T24" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="V24" t="n">
-        <v>1.81</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="X24" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC24" t="n">
         <v>8</v>
       </c>
       <c r="AD24" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="AG24" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
         <v>55</v>
       </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO24" t="n">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>3.45</v>
       </c>
       <c r="AQ24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE24" t="n">
         <v>5.8</v>
       </c>
-      <c r="AR24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BF24" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>18.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.56</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>1.76</v>
+        <v>10.5</v>
       </c>
       <c r="H25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>85</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT25" t="n">
         <v>6.2</v>
       </c>
-      <c r="I25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR25" t="n">
+      <c r="AU25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG25" t="n">
         <v>4.9</v>
       </c>
-      <c r="AS25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>1.93</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G26" t="n">
-        <v>2.46</v>
+        <v>2.92</v>
       </c>
       <c r="H26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K26" t="n">
         <v>3.2</v>
       </c>
-      <c r="I26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L26" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="M26" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="N26" t="n">
-        <v>4.3</v>
+        <v>1.47</v>
       </c>
       <c r="O26" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.12</v>
       </c>
       <c r="S26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AW26" t="n">
         <v>3.15</v>
       </c>
-      <c r="T26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X26" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>48</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>30</v>
-      </c>
       <c r="AX26" t="n">
-        <v>15</v>
+        <v>3.3</v>
       </c>
       <c r="AY26" t="n">
-        <v>10.5</v>
+        <v>2.64</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14.5</v>
+        <v>2.92</v>
       </c>
       <c r="BA26" t="n">
-        <v>38</v>
+        <v>3.2</v>
       </c>
       <c r="BB26" t="n">
-        <v>30</v>
+        <v>3.1</v>
       </c>
       <c r="BC26" t="n">
-        <v>22</v>
+        <v>3.05</v>
       </c>
       <c r="BD26" t="n">
-        <v>32</v>
+        <v>3.15</v>
       </c>
       <c r="BE26" t="n">
-        <v>65</v>
+        <v>3.35</v>
       </c>
       <c r="BF26" t="n">
-        <v>17</v>
+        <v>3.3</v>
       </c>
       <c r="BG26" t="n">
-        <v>25</v>
+        <v>3.3</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarc</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Internacional de Palmir</t>
+          <t>Trapani</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.8</v>
+        <v>1.66</v>
       </c>
       <c r="G27" t="n">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="H27" t="n">
-        <v>2.64</v>
+        <v>6.2</v>
       </c>
       <c r="I27" t="n">
-        <v>3.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="L27" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="M27" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="O27" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="P27" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="R27" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
         <v>1.97</v>
       </c>
       <c r="U27" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="V27" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="W27" t="n">
-        <v>1.44</v>
+        <v>2.04</v>
       </c>
       <c r="X27" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AP27" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU27" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AV27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG27" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS27" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,378 +5787,1154 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.08</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>2.36</v>
+        <v>4.8</v>
       </c>
       <c r="H28" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>4.9</v>
+        <v>2.22</v>
       </c>
       <c r="J28" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="K28" t="n">
         <v>3.65</v>
       </c>
       <c r="L28" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>2.34</v>
+        <v>1.24</v>
       </c>
       <c r="O28" t="n">
-        <v>1.56</v>
+        <v>1.09</v>
       </c>
       <c r="P28" t="n">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.56</v>
+        <v>2.12</v>
       </c>
       <c r="R28" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S28" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="U28" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V28" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="W28" t="n">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV28" t="n">
         <v>9.6</v>
       </c>
-      <c r="Y28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>14</v>
-      </c>
       <c r="AW28" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.800000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="AY28" t="n">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AZ28" t="n">
         <v>18.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BB28" t="n">
         <v>4.4</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-04 09:11:02</t>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Boca Juniors de Cali</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-04 11:19:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-04 11:19:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Real Soacha Cundinamarc</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Internacional de Palmir</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-04 11:19:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>20:10:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X32" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-04 11:19:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>22:20:00</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Junior FC Barranquilla</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Alianza FC Valledupar</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="H29" t="n">
+      <c r="F33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6</v>
+      </c>
+      <c r="I33" t="n">
+        <v>9</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X33" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB33" t="n">
         <v>7</v>
       </c>
-      <c r="I29" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>4</v>
-      </c>
-      <c r="K29" t="n">
+      <c r="AC33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC33" t="n">
         <v>4.5</v>
       </c>
-      <c r="L29" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>260</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
+      <c r="BD33" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF33" t="n">
         <v>10</v>
       </c>
-      <c r="AQ29" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>2026-03-04 09:11:02</t>
+      <c r="BG33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-04 11:19:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -769,7 +769,7 @@
         <v>3.85</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>3.65</v>
@@ -787,7 +787,7 @@
         <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
         <v>2.02</v>
@@ -796,10 +796,10 @@
         <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U2" t="n">
         <v>2.14</v>
@@ -817,7 +817,7 @@
         <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>980</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
         <v>75</v>
@@ -829,19 +829,19 @@
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>980</v>
+        <v>15.5</v>
       </c>
       <c r="AE2" t="n">
         <v>46</v>
       </c>
       <c r="AF2" t="n">
-        <v>980</v>
+        <v>13.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>980</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>980</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
         <v>55</v>
@@ -859,10 +859,10 @@
         <v>95</v>
       </c>
       <c r="AN2" t="n">
-        <v>980</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="AP2" t="n">
         <v>12.5</v>
@@ -871,10 +871,10 @@
         <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS2" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="AT2" t="n">
         <v>8.800000000000001</v>
@@ -886,10 +886,10 @@
         <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>15.5</v>
+        <v>40</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
         <v>9.800000000000001</v>
@@ -898,19 +898,19 @@
         <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>16.5</v>
+        <v>48</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="BF2" t="n">
         <v>15</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -951,61 +951,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G3" t="n">
         <v>1.58</v>
       </c>
       <c r="H3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I3" t="n">
         <v>7.8</v>
       </c>
-      <c r="I3" t="n">
-        <v>8</v>
-      </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y3" t="n">
         <v>22</v>
@@ -1014,107 +1014,107 @@
         <v>70</v>
       </c>
       <c r="AA3" t="n">
-        <v>340</v>
+        <v>280</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC3" t="n">
         <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AF3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AJ3" t="n">
         <v>15</v>
       </c>
       <c r="AK3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM3" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AN3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO3" t="n">
-        <v>370</v>
+        <v>230</v>
       </c>
       <c r="AP3" t="n">
         <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW3" t="n">
         <v>9.6</v>
       </c>
-      <c r="AS3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BB3" t="n">
         <v>12.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>90</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -1145,109 +1145,109 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="G4" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="I4" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T4" t="n">
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V4" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="X4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Z4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF4" t="n">
         <v>10</v>
       </c>
-      <c r="AD4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>15</v>
-      </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.05</v>
+        <v>30</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
         <v>7</v>
@@ -1274,41 +1274,41 @@
         <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="AX4" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.92</v>
+        <v>19</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="BB4" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.05</v>
+        <v>7.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>4.1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I5" t="n">
         <v>2.48</v>
@@ -1369,7 +1369,7 @@
         <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
         <v>2.16</v>
@@ -1378,7 +1378,7 @@
         <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
         <v>1.74</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -1536,25 +1536,25 @@
         <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H6" t="n">
         <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
         <v>3.2</v>
@@ -1563,140 +1563,140 @@
         <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="T6" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
         <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
         <v>10</v>
       </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AQ6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>17</v>
+        <v>3.75</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.04</v>
+        <v>4</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.8</v>
+        <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.73</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.08</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>30</v>
+        <v>3.95</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.9</v>
+        <v>11.5</v>
       </c>
       <c r="AY6" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.93</v>
+        <v>3.55</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.04</v>
+        <v>4</v>
       </c>
       <c r="BB6" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.98</v>
+        <v>3.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.02</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.08</v>
+        <v>4.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.08</v>
+        <v>17.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.08</v>
+        <v>4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -1727,94 +1727,94 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="I7" t="n">
         <v>1.66</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="K7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="O7" t="n">
         <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R7" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="T7" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="U7" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="V7" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB7" t="n">
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AF7" t="n">
         <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ7" t="n">
         <v>1000</v>
@@ -1832,65 +1832,65 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="AP7" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.22</v>
       </c>
       <c r="G8" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H8" t="n">
         <v>3.15</v>
@@ -1933,13 +1933,13 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K8" t="n">
         <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
@@ -1951,28 +1951,28 @@
         <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
         <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="T8" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X8" t="n">
         <v>16.5</v>
@@ -2029,22 +2029,22 @@
         <v>50</v>
       </c>
       <c r="AP8" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
         <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
         <v>4</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AV8" t="n">
         <v>12</v>
@@ -2053,22 +2053,22 @@
         <v>3.95</v>
       </c>
       <c r="AX8" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
         <v>4</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.9</v>
+        <v>23</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.8</v>
+        <v>19</v>
       </c>
       <c r="BD8" t="n">
         <v>3.95</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -2118,25 +2118,25 @@
         <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H9" t="n">
         <v>3.45</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
         <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="M9" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
         <v>2.52</v>
@@ -2157,16 +2157,16 @@
         <v>4.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="U9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X9" t="n">
         <v>10.5</v>
@@ -2235,10 +2235,10 @@
         <v>4.1</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.4</v>
+        <v>2.88</v>
       </c>
       <c r="AV9" t="n">
         <v>12</v>
@@ -2253,7 +2253,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>3.75</v>
       </c>
       <c r="BA9" t="n">
         <v>4.1</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -2309,31 +2309,31 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J10" t="n">
         <v>2.74</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.46</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O10" t="n">
         <v>1.54</v>
@@ -2342,25 +2342,25 @@
         <v>1.51</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="R10" t="n">
         <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="U10" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ10" t="n">
         <v>4</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.63</v>
+        <v>4.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AV10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY10" t="n">
         <v>4.8</v>
       </c>
-      <c r="AW10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.94</v>
+        <v>1.49</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.58</v>
+        <v>2.04</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.78</v>
+        <v>6.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -2527,22 +2527,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="O11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P11" t="n">
         <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G12" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="H12" t="n">
         <v>2.5</v>
@@ -2712,7 +2712,7 @@
         <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2724,7 +2724,7 @@
         <v>3.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P12" t="n">
         <v>1.79</v>
@@ -2736,10 +2736,10 @@
         <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="T12" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="U12" t="n">
         <v>2.04</v>
@@ -2760,7 +2760,7 @@
         <v>20</v>
       </c>
       <c r="AA12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB12" t="n">
         <v>13</v>
@@ -2826,19 +2826,19 @@
         <v>9.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
         <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB12" t="n">
         <v>4.7</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="H13" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
         <v>3.35</v>
@@ -2927,7 +2927,7 @@
         <v>2.32</v>
       </c>
       <c r="R13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
         <v>4.5</v>
@@ -2945,116 +2945,116 @@
         <v>1.63</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB13" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR13" t="n">
         <v>20</v>
       </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>17</v>
-      </c>
       <c r="AS13" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.96</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.18</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.38</v>
+        <v>4.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.26</v>
+        <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.34</v>
+        <v>4.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>23</v>
+        <v>4.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.38</v>
+        <v>4.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.46</v>
+        <v>5</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.46</v>
+        <v>4.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.46</v>
+        <v>4.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>5.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
@@ -3124,10 +3124,10 @@
         <v>1.59</v>
       </c>
       <c r="S14" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="T14" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="U14" t="n">
         <v>2.16</v>
@@ -3154,7 +3154,7 @@
         <v>32</v>
       </c>
       <c r="AC14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD14" t="n">
         <v>12</v>
@@ -3163,7 +3163,7 @@
         <v>17.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG14" t="n">
         <v>29</v>
@@ -3178,7 +3178,7 @@
         <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL14" t="n">
         <v>1000</v>
@@ -3205,7 +3205,7 @@
         <v>12.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU14" t="n">
         <v>10</v>
@@ -3217,7 +3217,7 @@
         <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AY14" t="n">
         <v>21</v>
@@ -3226,29 +3226,29 @@
         <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD14" t="n">
         <v>5</v>
       </c>
-      <c r="BC14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE14" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG14" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -3282,10 +3282,10 @@
         <v>1.74</v>
       </c>
       <c r="G15" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
         <v>7.4</v>
@@ -3315,22 +3315,22 @@
         <v>2.22</v>
       </c>
       <c r="R15" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S15" t="n">
         <v>3.7</v>
       </c>
       <c r="T15" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="U15" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="V15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W15" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="G16" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="H16" t="n">
         <v>5.1</v>
       </c>
       <c r="I16" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
         <v>4.3</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
@@ -3506,7 +3506,7 @@
         <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R16" t="n">
         <v>1.57</v>
@@ -3515,25 +3515,25 @@
         <v>2.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="U16" t="n">
         <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X16" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y16" t="n">
         <v>25</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
@@ -3542,40 +3542,40 @@
         <v>14</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF16" t="n">
         <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AK16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AL16" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO16" t="n">
         <v>60</v>
@@ -3587,22 +3587,22 @@
         <v>20</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV16" t="n">
         <v>17.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
@@ -3614,7 +3614,7 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BB16" t="n">
         <v>15</v>
@@ -3623,20 +3623,20 @@
         <v>13.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF16" t="n">
         <v>6.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G17" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="H17" t="n">
         <v>3.15</v>
       </c>
       <c r="I17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
         <v>3.8</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.24</v>
@@ -3715,10 +3715,10 @@
         <v>2.34</v>
       </c>
       <c r="V17" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="X17" t="n">
         <v>32</v>
@@ -3730,7 +3730,7 @@
         <v>34</v>
       </c>
       <c r="AA17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
         <v>18.5</v>
@@ -3778,25 +3778,25 @@
         <v>22</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS17" t="n">
         <v>3.95</v>
       </c>
       <c r="AT17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV17" t="n">
         <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX17" t="n">
         <v>14.5</v>
@@ -3817,7 +3817,7 @@
         <v>17</v>
       </c>
       <c r="BD17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BE17" t="n">
         <v>3.95</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -3861,25 +3861,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G18" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H18" t="n">
         <v>4.5</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
         <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
@@ -3894,22 +3894,22 @@
         <v>1.86</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R18" t="n">
         <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U18" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W18" t="n">
         <v>2.02</v>
@@ -3918,7 +3918,7 @@
         <v>16</v>
       </c>
       <c r="Y18" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z18" t="n">
         <v>42</v>
@@ -3990,7 +3990,7 @@
         <v>14.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -3999,10 +3999,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17</v>
+        <v>4.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB18" t="n">
         <v>4.3</v>
@@ -4011,7 +4011,7 @@
         <v>4.3</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE18" t="n">
         <v>5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H19" t="n">
         <v>2.12</v>
       </c>
       <c r="I19" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="J19" t="n">
         <v>2.82</v>
       </c>
       <c r="K19" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L19" t="n">
         <v>1.46</v>
@@ -4100,13 +4100,13 @@
         <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="V19" t="n">
         <v>1.7</v>
       </c>
       <c r="W19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AZ19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG19" t="n">
         <v>4.5</v>
       </c>
-      <c r="BA19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="G20" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="I20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J20" t="n">
         <v>3.15</v>
       </c>
-      <c r="J20" t="n">
-        <v>2.92</v>
-      </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="L20" t="n">
         <v>1.44</v>
@@ -4279,10 +4279,10 @@
         <v>1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R20" t="n">
         <v>1.28</v>
@@ -4291,128 +4291,128 @@
         <v>3.55</v>
       </c>
       <c r="T20" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="U20" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="V20" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="X20" t="n">
         <v>14</v>
       </c>
       <c r="Y20" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR20" t="n">
         <v>12</v>
       </c>
-      <c r="Z20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP20" t="n">
+      <c r="AS20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV20" t="n">
         <v>10</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS20" t="n">
+      <c r="AW20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC20" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.4</v>
+        <v>19.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -4443,58 +4443,58 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="G21" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="H21" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="J21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S21" t="n">
         <v>3.9</v>
       </c>
-      <c r="K21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.1</v>
-      </c>
       <c r="T21" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
         <v>14.5</v>
@@ -4548,65 +4548,65 @@
         <v>1000</v>
       </c>
       <c r="AO21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP21" t="n">
         <v>10.5</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AQ21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG21" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -4834,25 +4834,25 @@
         <v>2.26</v>
       </c>
       <c r="G23" t="n">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="H23" t="n">
         <v>3.6</v>
       </c>
       <c r="I23" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M23" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N23" t="n">
         <v>2.56</v>
@@ -4870,19 +4870,19 @@
         <v>1.19</v>
       </c>
       <c r="S23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T23" t="n">
         <v>1.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="V23" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X23" t="n">
         <v>10.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -5025,31 +5025,31 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="G24" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="H24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1.09</v>
+        <v>2.86</v>
       </c>
       <c r="K24" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M24" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N24" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
         <v>1.56</v>
@@ -5058,25 +5058,25 @@
         <v>1.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="R24" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T24" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="U24" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W24" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X24" t="n">
         <v>8.4</v>
@@ -5085,7 +5085,7 @@
         <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
@@ -5109,13 +5109,13 @@
         <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK24" t="n">
         <v>42</v>
@@ -5130,65 +5130,65 @@
         <v>55</v>
       </c>
       <c r="AO24" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.85</v>
+        <v>8</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.9</v>
+        <v>19</v>
       </c>
       <c r="AS24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB24" t="n">
         <v>5.5</v>
       </c>
-      <c r="AT24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BC24" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.4</v>
+        <v>30</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -5219,58 +5219,58 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="G25" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="H25" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="I25" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
-        <v>1.09</v>
+        <v>3.95</v>
       </c>
       <c r="K25" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="L25" t="n">
         <v>1.4</v>
       </c>
       <c r="M25" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>1.58</v>
+        <v>3.15</v>
       </c>
       <c r="O25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="Q25" t="n">
         <v>2.32</v>
       </c>
       <c r="R25" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="U25" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="V25" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
         <v>12.5</v>
@@ -5297,7 +5297,7 @@
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AG25" t="n">
         <v>1000</v>
@@ -5327,40 +5327,40 @@
         <v>12</v>
       </c>
       <c r="AP25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.65</v>
+        <v>5.7</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY25" t="n">
         <v>6.8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB25" t="n">
         <v>8.199999999999999</v>
@@ -5372,17 +5372,17 @@
         <v>8</v>
       </c>
       <c r="BE25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -5413,19 +5413,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G26" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="H26" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I26" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="K26" t="n">
         <v>3.2</v>
@@ -5437,37 +5437,37 @@
         <v>1.12</v>
       </c>
       <c r="N26" t="n">
-        <v>1.47</v>
+        <v>2.64</v>
       </c>
       <c r="O26" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P26" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.5</v>
+        <v>2.52</v>
       </c>
       <c r="R26" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="T26" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="U26" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="V26" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W26" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y26" t="n">
         <v>10.5</v>
@@ -5491,7 +5491,7 @@
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG26" t="n">
         <v>12.5</v>
@@ -5515,68 +5515,68 @@
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>3.3</v>
+        <v>7.8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>2.54</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.94</v>
+        <v>16.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT26" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.76</v>
+        <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>3.3</v>
+        <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>2.64</v>
+        <v>11</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.92</v>
+        <v>6.2</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
       <c r="BC26" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.15</v>
+        <v>50</v>
       </c>
       <c r="BE26" t="n">
-        <v>3.35</v>
+        <v>8.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="BG26" t="n">
-        <v>3.3</v>
+        <v>7.8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -5607,130 +5607,130 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G27" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="H27" t="n">
         <v>6.2</v>
       </c>
       <c r="I27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S27" t="n">
         <v>4.3</v>
       </c>
-      <c r="L27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4</v>
-      </c>
       <c r="T27" t="n">
-        <v>1.97</v>
+        <v>2.24</v>
       </c>
       <c r="U27" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="V27" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W27" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="X27" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z27" t="n">
         <v>70</v>
       </c>
       <c r="AA27" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE27" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AF27" t="n">
         <v>11</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI27" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AJ27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>290</v>
+      </c>
+      <c r="AN27" t="n">
         <v>22</v>
       </c>
-      <c r="AK27" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>19</v>
-      </c>
       <c r="AO27" t="n">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="AP27" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV27" t="n">
         <v>20</v>
@@ -5739,22 +5739,22 @@
         <v>4.3</v>
       </c>
       <c r="AX27" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AY27" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>19</v>
+        <v>3.9</v>
       </c>
       <c r="BA27" t="n">
         <v>4.3</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BD27" t="n">
         <v>4.1</v>
@@ -5763,14 +5763,14 @@
         <v>4.3</v>
       </c>
       <c r="BF27" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG27" t="n">
         <v>4.4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -5801,19 +5801,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G28" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="I28" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="J28" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K28" t="n">
         <v>3.65</v>
@@ -5822,49 +5822,49 @@
         <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.24</v>
+        <v>2.86</v>
       </c>
       <c r="O28" t="n">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="R28" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="U28" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="V28" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="W28" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y28" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB28" t="n">
         <v>13</v>
@@ -5879,7 +5879,7 @@
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG28" t="n">
         <v>19</v>
@@ -5918,7 +5918,7 @@
         <v>10</v>
       </c>
       <c r="AS28" t="n">
-        <v>3.8</v>
+        <v>21</v>
       </c>
       <c r="AT28" t="n">
         <v>10.5</v>
@@ -5930,10 +5930,10 @@
         <v>9.6</v>
       </c>
       <c r="AW28" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX28" t="n">
-        <v>3.85</v>
+        <v>7.2</v>
       </c>
       <c r="AY28" t="n">
         <v>15</v>
@@ -5942,29 +5942,29 @@
         <v>18.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.1</v>
+        <v>40</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG28" t="n">
         <v>18</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -5995,19 +5995,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G29" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H29" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="J29" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K29" t="n">
         <v>4.6</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW29" t="n">
         <v>5.2</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>5.1</v>
       </c>
       <c r="AX29" t="n">
         <v>3.4</v>
       </c>
       <c r="AY29" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB29" t="n">
         <v>4.1</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD29" t="n">
         <v>4.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
         <v>3.55</v>
       </c>
       <c r="L30" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
         <v>1.06</v>
@@ -6222,7 +6222,7 @@
         <v>2.12</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R30" t="n">
         <v>1.43</v>
@@ -6276,7 +6276,7 @@
         <v>15.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ30" t="n">
         <v>34</v>
@@ -6297,16 +6297,16 @@
         <v>27</v>
       </c>
       <c r="AP30" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>20</v>
       </c>
       <c r="AS30" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT30" t="n">
         <v>11</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>2.9</v>
       </c>
       <c r="G31" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H31" t="n">
         <v>2.56</v>
@@ -6404,7 +6404,7 @@
         <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N31" t="n">
         <v>2.42</v>
@@ -6428,13 +6428,13 @@
         <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="V31" t="n">
         <v>1.48</v>
       </c>
       <c r="W31" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X31" t="n">
         <v>9.800000000000001</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -6577,13 +6577,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G32" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H32" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I32" t="n">
         <v>4.4</v>
@@ -6598,37 +6598,37 @@
         <v>1.5</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N32" t="n">
-        <v>2.08</v>
+        <v>2.46</v>
       </c>
       <c r="O32" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="P32" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="U32" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V32" t="n">
         <v>1.29</v>
       </c>
       <c r="W32" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X32" t="n">
         <v>970</v>
@@ -6697,10 +6697,10 @@
         <v>4.5</v>
       </c>
       <c r="AT32" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU32" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV32" t="n">
         <v>3.85</v>
@@ -6709,10 +6709,10 @@
         <v>4.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY32" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
         <v>4</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>
@@ -6774,61 +6774,61 @@
         <v>1.56</v>
       </c>
       <c r="G33" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I33" t="n">
         <v>9</v>
       </c>
       <c r="J33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
         <v>3.85</v>
       </c>
-      <c r="K33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.55</v>
-      </c>
       <c r="T33" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="U33" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="V33" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W33" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="X33" t="n">
         <v>13</v>
       </c>
       <c r="Y33" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="Z33" t="n">
         <v>60</v>
@@ -6855,13 +6855,13 @@
         <v>10.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK33" t="n">
         <v>19.5</v>
@@ -6870,7 +6870,7 @@
         <v>46</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN33" t="n">
         <v>11.5</v>
@@ -6882,16 +6882,16 @@
         <v>11</v>
       </c>
       <c r="AQ33" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="AU33" t="n">
         <v>8.199999999999999</v>
@@ -6900,41 +6900,41 @@
         <v>19.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX33" t="n">
         <v>7.6</v>
       </c>
       <c r="AY33" t="n">
-        <v>3.75</v>
+        <v>9</v>
       </c>
       <c r="AZ33" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="BB33" t="n">
         <v>13.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="BD33" t="n">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="BF33" t="n">
         <v>10</v>
       </c>
       <c r="BG33" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-04 11:19:42</t>
+          <t>2026-03-04 13:28:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -763,19 +763,19 @@
         <v>2.18</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.6</v>
       </c>
-      <c r="K2" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -790,25 +790,25 @@
         <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R2" t="n">
         <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U2" t="n">
         <v>2.14</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X2" t="n">
         <v>13.5</v>
@@ -823,7 +823,7 @@
         <v>75</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
@@ -835,7 +835,7 @@
         <v>46</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
@@ -856,7 +856,7 @@
         <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="n">
         <v>17</v>
@@ -910,7 +910,7 @@
         <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="BF2" t="n">
         <v>15</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -954,167 +954,167 @@
         <v>1.56</v>
       </c>
       <c r="G3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="V3" t="n">
         <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
         <v>22</v>
       </c>
       <c r="Z3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA3" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AC3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AJ3" t="n">
         <v>15</v>
       </c>
       <c r="AK3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AO3" t="n">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
         <v>18.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AY3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>8.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BB3" t="n">
         <v>12.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -1145,70 +1145,70 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="G4" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="H4" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
         <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
         <v>1.83</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y4" t="n">
         <v>16</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB4" t="n">
         <v>7.6</v>
@@ -1223,7 +1223,7 @@
         <v>110</v>
       </c>
       <c r="AF4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
@@ -1238,7 +1238,7 @@
         <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
         <v>1000</v>
@@ -1256,13 +1256,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>30</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
@@ -1271,10 +1271,10 @@
         <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW4" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AX4" t="n">
         <v>8.800000000000001</v>
@@ -1283,10 +1283,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
         <v>17.5</v>
@@ -1295,20 +1295,20 @@
         <v>19.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF4" t="n">
         <v>14</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I5" t="n">
         <v>2.48</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
@@ -1372,7 +1372,7 @@
         <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
         <v>1.26</v>
@@ -1381,19 +1381,19 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="U5" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="V5" t="n">
         <v>1.67</v>
       </c>
       <c r="W5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="n">
         <v>10.5</v>
@@ -1408,7 +1408,7 @@
         <v>14.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
         <v>14</v>
@@ -1423,7 +1423,7 @@
         <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
         <v>60</v>
@@ -1456,7 +1456,7 @@
         <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1477,32 +1477,32 @@
         <v>13</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BG5" t="n">
         <v>17.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H6" t="n">
         <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J6" t="n">
         <v>3.1</v>
@@ -1566,25 +1566,25 @@
         <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
         <v>3.75</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U6" t="n">
         <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X6" t="n">
         <v>14.5</v>
@@ -1608,13 +1608,13 @@
         <v>18</v>
       </c>
       <c r="AE6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
         <v>18.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH6" t="n">
         <v>22</v>
@@ -1623,7 +1623,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1647,10 +1647,10 @@
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AS6" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="AT6" t="n">
         <v>8</v>
@@ -1662,41 +1662,41 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.95</v>
+        <v>36</v>
       </c>
       <c r="AX6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BA6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB6" t="n">
         <v>4</v>
       </c>
-      <c r="BB6" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BC6" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF6" t="n">
         <v>17.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -1727,67 +1727,67 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G7" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="H7" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="I7" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="J7" t="n">
         <v>4.7</v>
       </c>
       <c r="K7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="R7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="S7" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
         <v>1.46</v>
       </c>
       <c r="U7" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="V7" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA7" t="n">
         <v>21</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD7" t="n">
         <v>13.5</v>
@@ -1808,7 +1808,7 @@
         <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH7" t="n">
         <v>21</v>
@@ -1823,7 +1823,7 @@
         <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
@@ -1838,59 +1838,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AR7" t="n">
         <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>4</v>
       </c>
-      <c r="AU7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BA7" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.22</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="H8" t="n">
         <v>3.15</v>
@@ -1933,10 +1933,10 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.41</v>
@@ -1957,22 +1957,22 @@
         <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
         <v>1.78</v>
       </c>
       <c r="U8" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X8" t="n">
         <v>16.5</v>
@@ -2029,49 +2029,49 @@
         <v>50</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR8" t="n">
         <v>17</v>
       </c>
       <c r="AS8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW8" t="n">
         <v>4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>3.95</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
         <v>4</v>
       </c>
       <c r="BB8" t="n">
-        <v>23</v>
+        <v>3.9</v>
       </c>
       <c r="BC8" t="n">
         <v>19</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
         <v>4.1</v>
@@ -2080,11 +2080,11 @@
         <v>15.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -2118,43 +2118,43 @@
         <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I9" t="n">
         <v>4.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N9" t="n">
         <v>2.52</v>
       </c>
       <c r="O9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P9" t="n">
         <v>1.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T9" t="n">
         <v>1.92</v>
@@ -2166,13 +2166,13 @@
         <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2196,7 +2196,7 @@
         <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2226,59 +2226,59 @@
         <v>7.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AR9" t="n">
         <v>18</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU9" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.88</v>
       </c>
       <c r="AV9" t="n">
         <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BA9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB9" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB9" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BC9" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BD9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF9" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BG9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I10" t="n">
         <v>3.3</v>
@@ -2324,13 +2324,13 @@
         <v>2.74</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
         <v>2.54</v>
@@ -2339,22 +2339,22 @@
         <v>1.54</v>
       </c>
       <c r="P10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
         <v>4.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V10" t="n">
         <v>1.44</v>
@@ -2375,7 +2375,7 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="AQ10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT10" t="n">
         <v>4</v>
       </c>
-      <c r="AR10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS10" t="n">
+      <c r="AU10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY10" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.49</v>
+        <v>1.97</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.6</v>
+        <v>1.78</v>
       </c>
       <c r="BG10" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.83</v>
+        <v>1.03</v>
       </c>
       <c r="O11" t="n">
         <v>1.09</v>
@@ -2545,7 +2545,7 @@
         <v>1.09</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -2703,22 +2703,22 @@
         <v>3.25</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I12" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="J12" t="n">
         <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
         <v>3.3</v>
@@ -2736,19 +2736,19 @@
         <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="T12" t="n">
         <v>1.69</v>
       </c>
       <c r="U12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V12" t="n">
         <v>1.54</v>
       </c>
       <c r="W12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X12" t="n">
         <v>15</v>
@@ -2760,7 +2760,7 @@
         <v>20</v>
       </c>
       <c r="AA12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB12" t="n">
         <v>13</v>
@@ -2769,7 +2769,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE12" t="n">
         <v>36</v>
@@ -2781,7 +2781,7 @@
         <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI12" t="n">
         <v>55</v>
@@ -2805,25 +2805,25 @@
         <v>32</v>
       </c>
       <c r="AP12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AR12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS12" t="n">
         <v>4.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU12" t="n">
         <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW12" t="n">
         <v>4.5</v>
@@ -2835,7 +2835,7 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
         <v>4.7</v>
@@ -2844,7 +2844,7 @@
         <v>4.7</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD12" t="n">
         <v>4.7</v>
@@ -2856,11 +2856,11 @@
         <v>4.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G13" t="n">
         <v>2.58</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I13" t="n">
         <v>3.7</v>
@@ -2906,7 +2906,7 @@
         <v>3.05</v>
       </c>
       <c r="K13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L13" t="n">
         <v>1.45</v>
@@ -2927,10 +2927,10 @@
         <v>2.32</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="T13" t="n">
         <v>1.95</v>
@@ -2942,7 +2942,7 @@
         <v>1.39</v>
       </c>
       <c r="W13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X13" t="n">
         <v>12</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -3091,10 +3091,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="J14" t="n">
         <v>4.6</v>
@@ -3103,7 +3103,7 @@
         <v>5.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
@@ -3115,10 +3115,10 @@
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R14" t="n">
         <v>1.59</v>
@@ -3133,10 +3133,10 @@
         <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X14" t="n">
         <v>29</v>
@@ -3178,7 +3178,7 @@
         <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
         <v>1000</v>
@@ -3229,16 +3229,16 @@
         <v>4.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC14" t="n">
         <v>5.1</v>
       </c>
       <c r="BD14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF14" t="n">
         <v>5.1</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="G15" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="H15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
         <v>3.05</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.41</v>
@@ -3309,16 +3309,16 @@
         <v>1.42</v>
       </c>
       <c r="P15" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
         <v>1.88</v>
@@ -3330,7 +3330,7 @@
         <v>1.17</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3345,10 +3345,10 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>10</v>
+        <v>980</v>
       </c>
       <c r="AD15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AR15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV15" t="n">
         <v>4</v>
       </c>
-      <c r="AS15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AW15" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>5.1</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J16" t="n">
         <v>4.3</v>
@@ -3503,7 +3503,7 @@
         <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q16" t="n">
         <v>1.58</v>
@@ -3512,16 +3512,16 @@
         <v>1.57</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="U16" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W16" t="n">
         <v>2.36</v>
@@ -3569,7 +3569,7 @@
         <v>19</v>
       </c>
       <c r="AL16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
@@ -3587,7 +3587,7 @@
         <v>20</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS16" t="n">
         <v>5.2</v>
@@ -3602,7 +3602,7 @@
         <v>17.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
@@ -3623,7 +3623,7 @@
         <v>13.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE16" t="n">
         <v>5.1</v>
@@ -3632,11 +3632,11 @@
         <v>6.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G17" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H17" t="n">
         <v>3.15</v>
@@ -3679,10 +3679,10 @@
         <v>3.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.24</v>
@@ -3709,7 +3709,7 @@
         <v>2.32</v>
       </c>
       <c r="T17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U17" t="n">
         <v>2.34</v>
@@ -3718,7 +3718,7 @@
         <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X17" t="n">
         <v>32</v>
@@ -3778,10 +3778,10 @@
         <v>22</v>
       </c>
       <c r="AQ17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR17" t="n">
-        <v>21</v>
+        <v>3.75</v>
       </c>
       <c r="AS17" t="n">
         <v>3.95</v>
@@ -3790,13 +3790,13 @@
         <v>12.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV17" t="n">
         <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX17" t="n">
         <v>14.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G18" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H18" t="n">
         <v>4.5</v>
@@ -3903,7 +3903,7 @@
         <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -3912,7 +3912,7 @@
         <v>1.26</v>
       </c>
       <c r="W18" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X18" t="n">
         <v>16</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -4058,19 +4058,19 @@
         <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="H19" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="I19" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="J19" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="L19" t="n">
         <v>1.46</v>
@@ -4079,146 +4079,146 @@
         <v>1.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R19" t="n">
         <v>1.22</v>
       </c>
       <c r="S19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY19" t="n">
         <v>4.2</v>
       </c>
-      <c r="T19" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE19" t="n">
         <v>3.25</v>
       </c>
-      <c r="AR19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA19" t="n">
+      <c r="BF19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG19" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -4252,16 +4252,16 @@
         <v>3.15</v>
       </c>
       <c r="G20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H20" t="n">
         <v>2.4</v>
       </c>
       <c r="I20" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K20" t="n">
         <v>3.55</v>
@@ -4270,7 +4270,7 @@
         <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N20" t="n">
         <v>3.2</v>
@@ -4282,31 +4282,31 @@
         <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R20" t="n">
         <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="T20" t="n">
         <v>1.81</v>
       </c>
       <c r="U20" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z20" t="n">
         <v>18</v>
@@ -4315,10 +4315,10 @@
         <v>42</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD20" t="n">
         <v>13.5</v>
@@ -4357,19 +4357,19 @@
         <v>30</v>
       </c>
       <c r="AP20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU20" t="n">
         <v>6.4</v>
@@ -4378,10 +4378,10 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.4</v>
+        <v>22</v>
       </c>
       <c r="AX20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY20" t="n">
         <v>12</v>
@@ -4390,29 +4390,29 @@
         <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF20" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF20" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BG20" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -4449,13 +4449,13 @@
         <v>14.5</v>
       </c>
       <c r="H21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="I21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="J21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K21" t="n">
         <v>5.3</v>
@@ -4476,22 +4476,22 @@
         <v>1.73</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="R21" t="n">
         <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T21" t="n">
         <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="W21" t="n">
         <v>1.07</v>
@@ -4500,7 +4500,7 @@
         <v>14.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="Z21" t="n">
         <v>7.8</v>
@@ -4575,38 +4575,38 @@
         <v>15</v>
       </c>
       <c r="AX21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY21" t="n">
         <v>5.2</v>
       </c>
-      <c r="AY21" t="n">
-        <v>5</v>
-      </c>
       <c r="AZ21" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BC21" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG21" t="n">
         <v>6.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G23" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H23" t="n">
         <v>3.6</v>
@@ -4843,43 +4843,43 @@
         <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="K23" t="n">
         <v>3.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N23" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2.56</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.52</v>
       </c>
       <c r="R23" t="n">
         <v>1.19</v>
       </c>
       <c r="S23" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="U23" t="n">
         <v>1.76</v>
       </c>
       <c r="V23" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W23" t="n">
         <v>1.64</v>
@@ -4900,7 +4900,7 @@
         <v>9</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD23" t="n">
         <v>21</v>
@@ -4945,16 +4945,16 @@
         <v>9</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.8</v>
+        <v>21</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT23" t="n">
         <v>6.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV23" t="n">
         <v>14.5</v>
@@ -4969,32 +4969,32 @@
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD23" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4</v>
       </c>
       <c r="BE23" t="n">
         <v>4.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>2.52</v>
       </c>
       <c r="G24" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H24" t="n">
         <v>3.35</v>
@@ -5058,7 +5058,7 @@
         <v>1.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="R24" t="n">
         <v>1.17</v>
@@ -5067,10 +5067,10 @@
         <v>5.5</v>
       </c>
       <c r="T24" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="V24" t="n">
         <v>1.38</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
         <v>9.4</v>
       </c>
       <c r="H25" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="J25" t="n">
         <v>3.95</v>
@@ -5255,16 +5255,16 @@
         <v>2.32</v>
       </c>
       <c r="R25" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="U25" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="V25" t="n">
         <v>2.68</v>
@@ -5351,7 +5351,7 @@
         <v>6</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.6</v>
+        <v>50</v>
       </c>
       <c r="AY25" t="n">
         <v>6.8</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -5413,37 +5413,37 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="G26" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H26" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I26" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J26" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
         <v>3.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M26" t="n">
         <v>1.12</v>
       </c>
       <c r="N26" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O26" t="n">
         <v>1.52</v>
       </c>
       <c r="P26" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q26" t="n">
         <v>2.52</v>
@@ -5458,13 +5458,13 @@
         <v>1.88</v>
       </c>
       <c r="U26" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="V26" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W26" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X26" t="n">
         <v>11</v>
@@ -5479,7 +5479,7 @@
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC26" t="n">
         <v>7.2</v>
@@ -5521,16 +5521,16 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR26" t="n">
         <v>16.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT26" t="n">
         <v>6.8</v>
@@ -5542,7 +5542,7 @@
         <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX26" t="n">
         <v>13</v>
@@ -5551,32 +5551,32 @@
         <v>11</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB26" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC26" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>50</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -5607,170 +5607,170 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G27" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H27" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="I27" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="J27" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K27" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="P27" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="U27" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="V27" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="W27" t="n">
         <v>2.16</v>
       </c>
       <c r="X27" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z27" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AA27" t="n">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AE27" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AF27" t="n">
         <v>11</v>
       </c>
       <c r="AG27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH27" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AI27" t="n">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="AJ27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK27" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL27" t="n">
-        <v>70</v>
+        <v>980</v>
       </c>
       <c r="AM27" t="n">
-        <v>290</v>
+        <v>180</v>
       </c>
       <c r="AN27" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AO27" t="n">
-        <v>310</v>
+        <v>170</v>
       </c>
       <c r="AP27" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AQ27" t="n">
         <v>12</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AU27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AX27" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ27" t="n">
-        <v>3.9</v>
+        <v>19</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BB27" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G28" t="n">
         <v>5</v>
@@ -5810,22 +5810,22 @@
         <v>1.94</v>
       </c>
       <c r="I28" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J28" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K28" t="n">
         <v>3.65</v>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M28" t="n">
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O28" t="n">
         <v>1.45</v>
@@ -5837,19 +5837,19 @@
         <v>2.32</v>
       </c>
       <c r="R28" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S28" t="n">
         <v>4.4</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U28" t="n">
         <v>1.82</v>
       </c>
       <c r="V28" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W28" t="n">
         <v>1.25</v>
@@ -5858,16 +5858,16 @@
         <v>12</v>
       </c>
       <c r="Y28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z28" t="n">
         <v>12</v>
       </c>
       <c r="AA28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB28" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AC28" t="n">
         <v>8</v>
@@ -5879,10 +5879,10 @@
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH28" t="n">
         <v>1000</v>
@@ -5906,65 +5906,65 @@
         <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP28" t="n">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="AQ28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS28" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>21</v>
-      </c>
       <c r="AT28" t="n">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX28" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX28" t="n">
+      <c r="AY28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA28" t="n">
         <v>7.2</v>
       </c>
-      <c r="AY28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>40</v>
-      </c>
       <c r="BB28" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BC28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE28" t="n">
         <v>8</v>
       </c>
-      <c r="BD28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF28" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>1.57</v>
       </c>
       <c r="G29" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H29" t="n">
         <v>6</v>
@@ -6046,7 +6046,7 @@
         <v>1.11</v>
       </c>
       <c r="W29" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -6189,10 +6189,10 @@
         </is>
       </c>
       <c r="F30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G30" t="n">
         <v>2.46</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2.48</v>
       </c>
       <c r="H30" t="n">
         <v>3.2</v>
@@ -6207,7 +6207,7 @@
         <v>3.55</v>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M30" t="n">
         <v>1.06</v>
@@ -6222,7 +6222,7 @@
         <v>2.12</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R30" t="n">
         <v>1.43</v>
@@ -6231,7 +6231,7 @@
         <v>3.15</v>
       </c>
       <c r="T30" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U30" t="n">
         <v>2.36</v>
@@ -6240,7 +6240,7 @@
         <v>1.44</v>
       </c>
       <c r="W30" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X30" t="n">
         <v>15.5</v>
@@ -6249,10 +6249,10 @@
         <v>14</v>
       </c>
       <c r="Z30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA30" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB30" t="n">
         <v>12</v>
@@ -6270,7 +6270,7 @@
         <v>16</v>
       </c>
       <c r="AG30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH30" t="n">
         <v>15.5</v>
@@ -6348,11 +6348,11 @@
         <v>16.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G31" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H31" t="n">
         <v>2.56</v>
@@ -6395,7 +6395,7 @@
         <v>3.05</v>
       </c>
       <c r="J31" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="K31" t="n">
         <v>3.7</v>
@@ -6434,7 +6434,7 @@
         <v>1.48</v>
       </c>
       <c r="W31" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X31" t="n">
         <v>9.800000000000001</v>
@@ -6491,62 +6491,62 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW31" t="n">
         <v>4.9</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>4.8</v>
       </c>
       <c r="AX31" t="n">
         <v>4.3</v>
       </c>
       <c r="AY31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB31" t="n">
         <v>5</v>
       </c>
-      <c r="BB31" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BC31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BD31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF31" t="n">
         <v>5</v>
       </c>
-      <c r="BE31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G32" t="n">
         <v>2.52</v>
@@ -6586,10 +6586,10 @@
         <v>3.8</v>
       </c>
       <c r="I32" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J32" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="K32" t="n">
         <v>3.4</v>
@@ -6604,13 +6604,13 @@
         <v>2.46</v>
       </c>
       <c r="O32" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P32" t="n">
         <v>1.48</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R32" t="n">
         <v>1.17</v>
@@ -6619,25 +6619,25 @@
         <v>5.5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U32" t="n">
         <v>1.6</v>
       </c>
       <c r="V32" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W32" t="n">
         <v>1.65</v>
       </c>
       <c r="X32" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y32" t="n">
         <v>12.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AA32" t="n">
         <v>130</v>
@@ -6649,7 +6649,7 @@
         <v>8.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AE32" t="n">
         <v>90</v>
@@ -6661,16 +6661,16 @@
         <v>15.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>30</v>
+        <v>980</v>
       </c>
       <c r="AI32" t="n">
         <v>120</v>
       </c>
       <c r="AJ32" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AK32" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AL32" t="n">
         <v>85</v>
@@ -6679,7 +6679,7 @@
         <v>250</v>
       </c>
       <c r="AN32" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AO32" t="n">
         <v>140</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>
@@ -6774,19 +6774,19 @@
         <v>1.56</v>
       </c>
       <c r="G33" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="H33" t="n">
         <v>7</v>
       </c>
       <c r="I33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J33" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L33" t="n">
         <v>1.38</v>
@@ -6801,7 +6801,7 @@
         <v>1.37</v>
       </c>
       <c r="P33" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q33" t="n">
         <v>2.08</v>
@@ -6813,16 +6813,16 @@
         <v>3.85</v>
       </c>
       <c r="T33" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U33" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V33" t="n">
         <v>1.14</v>
       </c>
       <c r="W33" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="X33" t="n">
         <v>13</v>
@@ -6843,13 +6843,13 @@
         <v>9.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE33" t="n">
         <v>140</v>
       </c>
       <c r="AF33" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG33" t="n">
         <v>10.5</v>
@@ -6861,7 +6861,7 @@
         <v>150</v>
       </c>
       <c r="AJ33" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK33" t="n">
         <v>19.5</v>
@@ -6879,16 +6879,16 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ33" t="n">
         <v>17.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS33" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT33" t="n">
         <v>6.2</v>
@@ -6900,7 +6900,7 @@
         <v>19.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX33" t="n">
         <v>7.6</v>
@@ -6912,29 +6912,29 @@
         <v>20</v>
       </c>
       <c r="BA33" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB33" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BE33" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG33" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-04 13:28:42</t>
+          <t>2026-03-04 15:39:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -766,7 +766,7 @@
         <v>3.85</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
@@ -787,10 +787,10 @@
         <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R2" t="n">
         <v>1.37</v>
@@ -799,7 +799,7 @@
         <v>3.65</v>
       </c>
       <c r="T2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U2" t="n">
         <v>2.14</v>
@@ -895,7 +895,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
         <v>48</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H3" t="n">
         <v>7</v>
@@ -963,73 +963,73 @@
         <v>7.6</v>
       </c>
       <c r="J3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K3" t="n">
         <v>4.3</v>
       </c>
-      <c r="K3" t="n">
-        <v>4.6</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
         <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
         <v>130</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
@@ -1038,83 +1038,83 @@
         <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS3" t="n">
         <v>18.5</v>
       </c>
-      <c r="AL3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AT3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.6</v>
+        <v>25</v>
       </c>
       <c r="AW3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="BA3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BB3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J4" t="n">
         <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
         <v>1.43</v>
@@ -1181,7 +1181,7 @@
         <v>2.24</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
         <v>4.3</v>
@@ -1193,13 +1193,13 @@
         <v>1.83</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="X4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
         <v>16</v>
@@ -1211,7 +1211,7 @@
         <v>180</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC4" t="n">
         <v>8.4</v>
@@ -1223,7 +1223,7 @@
         <v>110</v>
       </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
@@ -1232,7 +1232,7 @@
         <v>27</v>
       </c>
       <c r="AI4" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AJ4" t="n">
         <v>23</v>
@@ -1247,68 +1247,68 @@
         <v>180</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>4.2</v>
       </c>
       <c r="H5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I5" t="n">
         <v>2.48</v>
@@ -1354,7 +1354,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
         <v>1.46</v>
@@ -1366,7 +1366,7 @@
         <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
         <v>1.7</v>
@@ -1456,7 +1456,7 @@
         <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1480,29 +1480,29 @@
         <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BG5" t="n">
         <v>17.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G6" t="n">
         <v>2.52</v>
@@ -1542,7 +1542,7 @@
         <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J6" t="n">
         <v>3.1</v>
@@ -1563,10 +1563,10 @@
         <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
         <v>1.29</v>
@@ -1581,7 +1581,7 @@
         <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
         <v>1.65</v>
@@ -1590,7 +1590,7 @@
         <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
         <v>30</v>
@@ -1602,19 +1602,19 @@
         <v>11.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
         <v>22</v>
@@ -1626,19 +1626,19 @@
         <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
         <v>60</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
       </c>
       <c r="AP6" t="n">
         <v>10</v>
@@ -1647,10 +1647,10 @@
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.95</v>
+        <v>5.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
         <v>8</v>
@@ -1662,41 +1662,41 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>36</v>
+        <v>5.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>5.9</v>
       </c>
       <c r="H7" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="I7" t="n">
         <v>1.69</v>
@@ -1742,7 +1742,7 @@
         <v>4.7</v>
       </c>
       <c r="K7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.19</v>
@@ -1769,7 +1769,7 @@
         <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="U7" t="n">
         <v>2.52</v>
@@ -1862,7 +1862,7 @@
         <v>4.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AZ7" t="n">
         <v>4</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -1924,22 +1924,22 @@
         <v>2.22</v>
       </c>
       <c r="G8" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="H8" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
@@ -1951,7 +1951,7 @@
         <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
@@ -1963,16 +1963,16 @@
         <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X8" t="n">
         <v>16.5</v>
@@ -1981,10 +1981,10 @@
         <v>15.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB8" t="n">
         <v>12</v>
@@ -1993,13 +1993,13 @@
         <v>9.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG8" t="n">
         <v>14</v>
@@ -2011,7 +2011,7 @@
         <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK8" t="n">
         <v>32</v>
@@ -2023,68 +2023,68 @@
         <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP8" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
         <v>4</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.9</v>
+        <v>22</v>
       </c>
       <c r="BC8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BE8" t="n">
         <v>4.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -2118,22 +2118,22 @@
         <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H9" t="n">
         <v>3.5</v>
       </c>
       <c r="I9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="K9" t="n">
         <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="M9" t="n">
         <v>1.11</v>
@@ -2142,13 +2142,13 @@
         <v>2.52</v>
       </c>
       <c r="O9" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="P9" t="n">
         <v>1.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
@@ -2163,10 +2163,10 @@
         <v>1.65</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X9" t="n">
         <v>10</v>
@@ -2226,13 +2226,13 @@
         <v>7.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AR9" t="n">
-        <v>18</v>
+        <v>4.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AT9" t="n">
         <v>5.6</v>
@@ -2241,44 +2241,44 @@
         <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AX9" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -2324,10 +2324,10 @@
         <v>2.74</v>
       </c>
       <c r="K10" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M10" t="n">
         <v>1.11</v>
@@ -2339,7 +2339,7 @@
         <v>1.54</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q10" t="n">
         <v>2.4</v>
@@ -2351,7 +2351,7 @@
         <v>4.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
         <v>1.66</v>
@@ -2417,13 +2417,13 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS10" t="n">
         <v>6.2</v>
@@ -2438,7 +2438,7 @@
         <v>4.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AX10" t="n">
         <v>5</v>
@@ -2450,29 +2450,29 @@
         <v>5.3</v>
       </c>
       <c r="BA10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BF10" t="n">
         <v>1.79</v>
       </c>
-      <c r="BB10" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.78</v>
-      </c>
       <c r="BG10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -2709,13 +2709,13 @@
         <v>2.86</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
         <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
@@ -2739,16 +2739,16 @@
         <v>3.65</v>
       </c>
       <c r="T12" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="U12" t="n">
         <v>2.06</v>
       </c>
       <c r="V12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
         <v>15</v>
@@ -2808,22 +2808,22 @@
         <v>10.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
         <v>4.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW12" t="n">
         <v>4.5</v>
@@ -2835,7 +2835,7 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA12" t="n">
         <v>4.7</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>2.38</v>
       </c>
       <c r="G13" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H13" t="n">
         <v>3.35</v>
@@ -2915,7 +2915,7 @@
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
         <v>1.45</v>
@@ -2924,13 +2924,13 @@
         <v>1.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="T13" t="n">
         <v>1.95</v>
@@ -2954,7 +2954,7 @@
         <v>27</v>
       </c>
       <c r="AA13" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB13" t="n">
         <v>9.6</v>
@@ -3008,7 +3008,7 @@
         <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT13" t="n">
         <v>7.4</v>
@@ -3020,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
@@ -3032,7 +3032,7 @@
         <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB13" t="n">
         <v>4.6</v>
@@ -3041,7 +3041,7 @@
         <v>4.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE13" t="n">
         <v>5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -3088,16 +3088,16 @@
         <v>6.2</v>
       </c>
       <c r="G14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="H14" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K14" t="n">
         <v>5.3</v>
@@ -3121,7 +3121,7 @@
         <v>1.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S14" t="n">
         <v>2.42</v>
@@ -3133,10 +3133,10 @@
         <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="W14" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
         <v>29</v>
@@ -3148,7 +3148,7 @@
         <v>12.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AB14" t="n">
         <v>32</v>
@@ -3181,7 +3181,7 @@
         <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -3205,7 +3205,7 @@
         <v>12.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AU14" t="n">
         <v>10</v>
@@ -3217,7 +3217,7 @@
         <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AY14" t="n">
         <v>21</v>
@@ -3226,29 +3226,29 @@
         <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC14" t="n">
         <v>5.3</v>
       </c>
-      <c r="BC14" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BD14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG14" t="n">
         <v>5.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -3279,58 +3279,58 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="G15" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="H15" t="n">
         <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J15" t="n">
         <v>3.05</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P15" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T15" t="n">
         <v>1.88</v>
       </c>
       <c r="U15" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3348,7 +3348,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>980</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD15" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF15" t="n">
         <v>4</v>
       </c>
-      <c r="AW15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BG15" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H16" t="n">
         <v>5.1</v>
       </c>
       <c r="I16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J16" t="n">
         <v>4.3</v>
@@ -3497,7 +3497,7 @@
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.19</v>
@@ -3506,7 +3506,7 @@
         <v>2.42</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R16" t="n">
         <v>1.57</v>
@@ -3524,7 +3524,7 @@
         <v>1.22</v>
       </c>
       <c r="W16" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X16" t="n">
         <v>25</v>
@@ -3539,13 +3539,13 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC16" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>70</v>
@@ -3554,31 +3554,31 @@
         <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL16" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AO16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP16" t="n">
         <v>21</v>
@@ -3587,10 +3587,10 @@
         <v>20</v>
       </c>
       <c r="AR16" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
         <v>17.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
@@ -3614,7 +3614,7 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BB16" t="n">
         <v>15</v>
@@ -3626,17 +3626,17 @@
         <v>20</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BF16" t="n">
         <v>6.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G17" t="n">
         <v>2.26</v>
@@ -3691,7 +3691,7 @@
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.17</v>
@@ -3700,7 +3700,7 @@
         <v>2.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="R17" t="n">
         <v>1.62</v>
@@ -3709,10 +3709,10 @@
         <v>2.32</v>
       </c>
       <c r="T17" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="U17" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V17" t="n">
         <v>1.4</v>
@@ -3721,22 +3721,22 @@
         <v>1.79</v>
       </c>
       <c r="X17" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Y17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z17" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB17" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD17" t="n">
         <v>18</v>
@@ -3745,46 +3745,46 @@
         <v>40</v>
       </c>
       <c r="AF17" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
         <v>18</v>
       </c>
       <c r="AI17" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AK17" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM17" t="n">
         <v>65</v>
       </c>
       <c r="AN17" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP17" t="n">
         <v>22</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="AT17" t="n">
         <v>12.5</v>
@@ -3808,10 +3808,10 @@
         <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="BC17" t="n">
         <v>17</v>
@@ -3820,7 +3820,7 @@
         <v>19.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="BF17" t="n">
         <v>7.6</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G18" t="n">
         <v>1.96</v>
@@ -3873,13 +3873,13 @@
         <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
@@ -3903,7 +3903,7 @@
         <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -3939,7 +3939,7 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG18" t="n">
         <v>12</v>
@@ -3948,13 +3948,13 @@
         <v>23</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL18" t="n">
         <v>46</v>
@@ -3963,10 +3963,10 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP18" t="n">
         <v>12</v>
@@ -3975,10 +3975,10 @@
         <v>13.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -3990,7 +3990,7 @@
         <v>14.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -3999,32 +3999,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.7</v>
+        <v>32</v>
       </c>
       <c r="BE18" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF18" t="n">
         <v>11</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
         <v>2.8</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L19" t="n">
         <v>1.46</v>
@@ -4082,13 +4082,13 @@
         <v>2.76</v>
       </c>
       <c r="O19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P19" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="R19" t="n">
         <v>1.22</v>
@@ -4097,10 +4097,10 @@
         <v>4.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="V19" t="n">
         <v>1.67</v>
@@ -4124,7 +4124,7 @@
         <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD19" t="n">
         <v>1000</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G20" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="H20" t="n">
         <v>2.4</v>
@@ -4261,19 +4261,19 @@
         <v>2.62</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="K20" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
         <v>1.37</v>
@@ -4282,25 +4282,25 @@
         <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
         <v>3.85</v>
       </c>
       <c r="T20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U20" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V20" t="n">
         <v>1.61</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X20" t="n">
         <v>13.5</v>
@@ -4309,40 +4309,40 @@
         <v>10.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
         <v>13</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF20" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG20" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK20" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -4351,25 +4351,25 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
         <v>10</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR20" t="n">
         <v>13</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
         <v>6.4</v>
@@ -4378,7 +4378,7 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>22</v>
+        <v>6.4</v>
       </c>
       <c r="AX20" t="n">
         <v>19</v>
@@ -4387,32 +4387,32 @@
         <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BB20" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BD20" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BG20" t="n">
         <v>20</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -4449,16 +4449,16 @@
         <v>14.5</v>
       </c>
       <c r="H21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="I21" t="n">
         <v>1.43</v>
       </c>
       <c r="J21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L21" t="n">
         <v>1.38</v>
@@ -4470,10 +4470,10 @@
         <v>3.15</v>
       </c>
       <c r="O21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P21" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q21" t="n">
         <v>2.1</v>
@@ -4485,10 +4485,10 @@
         <v>3.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U21" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
         <v>3.3</v>
@@ -4563,7 +4563,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AT21" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AU21" t="n">
         <v>9.800000000000001</v>
@@ -4572,7 +4572,7 @@
         <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="AX21" t="n">
         <v>5.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -4849,34 +4849,34 @@
         <v>3.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="M23" t="n">
         <v>1.12</v>
       </c>
       <c r="N23" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="O23" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="P23" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S23" t="n">
         <v>5.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="U23" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="V23" t="n">
         <v>1.31</v>
@@ -4897,49 +4897,49 @@
         <v>110</v>
       </c>
       <c r="AB23" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE23" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF23" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI23" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ23" t="n">
         <v>44</v>
       </c>
       <c r="AK23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
         <v>42</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>44</v>
       </c>
       <c r="AO23" t="n">
         <v>110</v>
       </c>
       <c r="AP23" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ23" t="n">
         <v>9</v>
@@ -4948,7 +4948,7 @@
         <v>21</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AT23" t="n">
         <v>6.4</v>
@@ -4957,10 +4957,10 @@
         <v>6</v>
       </c>
       <c r="AV23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AX23" t="n">
         <v>11.5</v>
@@ -4969,32 +4969,32 @@
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB23" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BC23" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
         <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V24" t="n">
         <v>1.38</v>
@@ -5181,14 +5181,14 @@
         <v>6.2</v>
       </c>
       <c r="BF24" t="n">
-        <v>30</v>
+        <v>5.7</v>
       </c>
       <c r="BG24" t="n">
         <v>5.9</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v>9.4</v>
       </c>
       <c r="H25" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="I25" t="n">
         <v>1.59</v>
@@ -5351,7 +5351,7 @@
         <v>6</v>
       </c>
       <c r="AX25" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AY25" t="n">
         <v>6.8</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G26" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H26" t="n">
         <v>3.45</v>
       </c>
       <c r="I26" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J26" t="n">
         <v>3</v>
@@ -5458,13 +5458,13 @@
         <v>1.88</v>
       </c>
       <c r="U26" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V26" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W26" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="X26" t="n">
         <v>11</v>
@@ -5491,7 +5491,7 @@
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AG26" t="n">
         <v>12.5</v>
@@ -5506,7 +5506,7 @@
         <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL26" t="n">
         <v>1000</v>
@@ -5527,10 +5527,10 @@
         <v>9</v>
       </c>
       <c r="AR26" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT26" t="n">
         <v>6.8</v>
@@ -5542,41 +5542,41 @@
         <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BA26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB26" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB26" t="n">
-        <v>26</v>
-      </c>
       <c r="BC26" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BD26" t="n">
         <v>50</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>1.7</v>
       </c>
       <c r="G27" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H27" t="n">
         <v>5.6</v>
@@ -5622,7 +5622,7 @@
         <v>3.5</v>
       </c>
       <c r="K27" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -5634,10 +5634,10 @@
         <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="Q27" t="n">
         <v>2.14</v>
@@ -5658,13 +5658,13 @@
         <v>1.18</v>
       </c>
       <c r="W27" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X27" t="n">
         <v>13.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z27" t="n">
         <v>55</v>
@@ -5676,7 +5676,7 @@
         <v>7.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD27" t="n">
         <v>29</v>
@@ -5685,7 +5685,7 @@
         <v>130</v>
       </c>
       <c r="AF27" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG27" t="n">
         <v>11</v>
@@ -5700,7 +5700,7 @@
         <v>22</v>
       </c>
       <c r="AK27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL27" t="n">
         <v>980</v>
@@ -5721,22 +5721,22 @@
         <v>12</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.8</v>
+        <v>30</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT27" t="n">
         <v>6.2</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV27" t="n">
         <v>17.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AX27" t="n">
         <v>8.4</v>
@@ -5745,10 +5745,10 @@
         <v>9</v>
       </c>
       <c r="AZ27" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB27" t="n">
         <v>15.5</v>
@@ -5757,20 +5757,20 @@
         <v>18.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF27" t="n">
         <v>12.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -5804,13 +5804,13 @@
         <v>4.3</v>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H28" t="n">
         <v>1.94</v>
       </c>
       <c r="I28" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="J28" t="n">
         <v>3.25</v>
@@ -5849,10 +5849,10 @@
         <v>1.82</v>
       </c>
       <c r="V28" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X28" t="n">
         <v>12</v>
@@ -5909,40 +5909,40 @@
         <v>22</v>
       </c>
       <c r="AP28" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="AU28" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AV28" t="n">
         <v>9.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="AX28" t="n">
         <v>6.6</v>
       </c>
       <c r="AY28" t="n">
-        <v>5.9</v>
+        <v>16.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.2</v>
+        <v>40</v>
       </c>
       <c r="BB28" t="n">
         <v>7.8</v>
@@ -5960,11 +5960,11 @@
         <v>7.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G29" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="H29" t="n">
         <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J29" t="n">
         <v>3.35</v>
@@ -6013,13 +6013,13 @@
         <v>4.6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M29" t="n">
         <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="O29" t="n">
         <v>1.43</v>
@@ -6028,7 +6028,7 @@
         <v>1.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="R29" t="n">
         <v>1.23</v>
@@ -6043,10 +6043,10 @@
         <v>1.58</v>
       </c>
       <c r="V29" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W29" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU29" t="n">
         <v>3.75</v>
       </c>
-      <c r="AQ29" t="n">
+      <c r="AV29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB29" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR29" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV29" t="n">
+      <c r="BC29" t="n">
         <v>4.7</v>
       </c>
-      <c r="AW29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD29" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.3</v>
+        <v>2.86</v>
       </c>
       <c r="BF29" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.66</v>
+        <v>2.04</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G30" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I30" t="n">
         <v>3.2</v>
-      </c>
-      <c r="I30" t="n">
-        <v>3.25</v>
       </c>
       <c r="J30" t="n">
         <v>3.5</v>
@@ -6216,31 +6216,31 @@
         <v>4.3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P30" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R30" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
         <v>3.15</v>
       </c>
       <c r="T30" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U30" t="n">
         <v>2.36</v>
       </c>
       <c r="V30" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W30" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="X30" t="n">
         <v>15.5</v>
@@ -6249,10 +6249,10 @@
         <v>14</v>
       </c>
       <c r="Z30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA30" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB30" t="n">
         <v>12</v>
@@ -6270,7 +6270,7 @@
         <v>16</v>
       </c>
       <c r="AG30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH30" t="n">
         <v>15.5</v>
@@ -6291,7 +6291,7 @@
         <v>75</v>
       </c>
       <c r="AN30" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO30" t="n">
         <v>27</v>
@@ -6303,7 +6303,7 @@
         <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS30" t="n">
         <v>48</v>
@@ -6318,7 +6318,7 @@
         <v>13</v>
       </c>
       <c r="AW30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX30" t="n">
         <v>15</v>
@@ -6336,7 +6336,7 @@
         <v>30</v>
       </c>
       <c r="BC30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD30" t="n">
         <v>32</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         <v>1.65</v>
       </c>
       <c r="X32" t="n">
-        <v>8.199999999999999</v>
+        <v>980</v>
       </c>
       <c r="Y32" t="n">
         <v>12.5</v>
@@ -6685,16 +6685,16 @@
         <v>140</v>
       </c>
       <c r="AP32" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT32" t="n">
         <v>6.2</v>
@@ -6703,44 +6703,44 @@
         <v>6.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AW32" t="n">
         <v>4.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY32" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD32" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BE32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG32" t="n">
         <v>4.6</v>
       </c>
-      <c r="BF32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
         <v>4.4</v>
       </c>
       <c r="L33" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M33" t="n">
         <v>1.08</v>
@@ -6801,10 +6801,10 @@
         <v>1.37</v>
       </c>
       <c r="P33" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R33" t="n">
         <v>1.3</v>
@@ -6861,13 +6861,13 @@
         <v>150</v>
       </c>
       <c r="AJ33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK33" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL33" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AM33" t="n">
         <v>210</v>
@@ -6888,7 +6888,7 @@
         <v>10</v>
       </c>
       <c r="AS33" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT33" t="n">
         <v>6.2</v>
@@ -6900,7 +6900,7 @@
         <v>19.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX33" t="n">
         <v>7.6</v>
@@ -6912,7 +6912,7 @@
         <v>20</v>
       </c>
       <c r="BA33" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB33" t="n">
         <v>13</v>
@@ -6921,7 +6921,7 @@
         <v>16.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE33" t="n">
         <v>11.5</v>
@@ -6930,11 +6930,11 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG33" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-04 15:39:06</t>
+          <t>2026-03-04 17:52:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -781,10 +781,10 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
         <v>1.95</v>
@@ -796,10 +796,10 @@
         <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U2" t="n">
         <v>2.14</v>
@@ -829,7 +829,7 @@
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>46</v>
@@ -838,7 +838,7 @@
         <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
         <v>18</v>
@@ -862,7 +862,7 @@
         <v>17</v>
       </c>
       <c r="AO2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
         <v>12.5</v>
@@ -880,13 +880,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
         <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX2" t="n">
         <v>12</v>
@@ -895,7 +895,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA2" t="n">
         <v>48</v>
@@ -904,23 +904,23 @@
         <v>24</v>
       </c>
       <c r="BC2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="BF2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I3" t="n">
         <v>7.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.45</v>
@@ -975,34 +975,34 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V3" t="n">
         <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
         <v>13.5</v>
@@ -1014,7 +1014,7 @@
         <v>60</v>
       </c>
       <c r="AA3" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AB3" t="n">
         <v>7</v>
@@ -1023,7 +1023,7 @@
         <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="n">
         <v>130</v>
@@ -1062,22 +1062,22 @@
         <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR3" t="n">
         <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT3" t="n">
         <v>6.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW3" t="n">
         <v>17</v>
@@ -1092,10 +1092,10 @@
         <v>24</v>
       </c>
       <c r="BA3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
         <v>17</v>
@@ -1104,17 +1104,17 @@
         <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BF3" t="n">
         <v>9.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G4" t="n">
         <v>1.85</v>
@@ -1154,16 +1154,16 @@
         <v>5.5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1172,7 +1172,7 @@
         <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P4" t="n">
         <v>1.7</v>
@@ -1211,10 +1211,10 @@
         <v>180</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
         <v>23</v>
@@ -1223,19 +1223,19 @@
         <v>110</v>
       </c>
       <c r="AF4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI4" t="n">
         <v>120</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
         <v>23</v>
@@ -1259,10 +1259,10 @@
         <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
@@ -1274,19 +1274,19 @@
         <v>20</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB4" t="n">
         <v>17</v>
@@ -1295,20 +1295,20 @@
         <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -1339,40 +1339,40 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="I5" t="n">
         <v>2.48</v>
       </c>
       <c r="J5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R5" t="n">
         <v>1.26</v>
@@ -1390,7 +1390,7 @@
         <v>1.67</v>
       </c>
       <c r="W5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
@@ -1402,7 +1402,7 @@
         <v>17</v>
       </c>
       <c r="AA5" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB5" t="n">
         <v>14.5</v>
@@ -1426,7 +1426,7 @@
         <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
@@ -1435,19 +1435,19 @@
         <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
         <v>30</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.4</v>
@@ -1480,29 +1480,29 @@
         <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.4</v>
+        <v>28</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG5" t="n">
         <v>17.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G6" t="n">
         <v>2.52</v>
@@ -1542,7 +1542,7 @@
         <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
         <v>3.1</v>
@@ -1551,7 +1551,7 @@
         <v>3.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
@@ -1575,13 +1575,13 @@
         <v>3.75</v>
       </c>
       <c r="T6" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
         <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
         <v>1.65</v>
@@ -1590,7 +1590,7 @@
         <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z6" t="n">
         <v>30</v>
@@ -1599,19 +1599,19 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
         <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG6" t="n">
         <v>12.5</v>
@@ -1623,7 +1623,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK6" t="n">
         <v>34</v>
@@ -1638,7 +1638,7 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
         <v>10</v>
@@ -1647,10 +1647,10 @@
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT6" t="n">
         <v>8</v>
@@ -1662,7 +1662,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.8</v>
+        <v>36</v>
       </c>
       <c r="AX6" t="n">
         <v>12.5</v>
@@ -1671,32 +1671,32 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="BF6" t="n">
         <v>17</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
         <v>5.9</v>
       </c>
       <c r="H7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="I7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K7" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
         <v>1.19</v>
@@ -1751,10 +1751,10 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1763,28 +1763,28 @@
         <v>1.41</v>
       </c>
       <c r="R7" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U7" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V7" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="W7" t="n">
         <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Y7" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z7" t="n">
         <v>17</v>
@@ -1811,7 +1811,7 @@
         <v>27</v>
       </c>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
         <v>28</v>
@@ -1838,59 +1838,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AR7" t="n">
         <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY7" t="n">
         <v>4.3</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.2</v>
       </c>
       <c r="AZ7" t="n">
         <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.2</v>
+        <v>16.5</v>
       </c>
       <c r="BB7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC7" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC7" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BD7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG7" t="n">
         <v>4.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -1912,179 +1912,179 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>S.S.D. Casarano Calcio</t>
+          <t>US Latina Calcio</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="G8" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H8" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.45</v>
+        <v>2.52</v>
       </c>
       <c r="O8" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="X8" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="AG8" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="AI8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.4</v>
+        <v>5.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>17.5</v>
+        <v>5.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="AX8" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>5.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>22</v>
+        <v>5.7</v>
       </c>
       <c r="BC8" t="n">
-        <v>18.5</v>
+        <v>5.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>US Latina Calcio</t>
+          <t>S.S.D. Casarano Calcio</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="G9" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="H9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S9" t="n">
         <v>3.5</v>
       </c>
-      <c r="I9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.8</v>
-      </c>
       <c r="T9" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="U9" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="X9" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="Y9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AC9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>330</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT9" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AU9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC9" t="n">
         <v>21</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
+      <c r="BD9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF9" t="n">
         <v>17</v>
       </c>
-      <c r="AG9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BG9" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FC Giugliano</t>
+          <t>AZ Picerno ASD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Atalanta B</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="H10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I10" t="n">
         <v>2.86</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.3</v>
       </c>
-      <c r="J10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.54</v>
-      </c>
       <c r="O10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.54</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>1.44</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.47</v>
-      </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="AS10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF10" t="n">
         <v>6.2</v>
       </c>
-      <c r="AT10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.79</v>
-      </c>
       <c r="BG10" t="n">
-        <v>1.98</v>
+        <v>5.7</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>710</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>2.96</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -2551,10 +2551,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2614,59 +2614,59 @@
         <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AZ Picerno ASD</t>
+          <t>FC Giugliano</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atalanta B</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="H12" t="n">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="I12" t="n">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="K12" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="O12" t="n">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="P12" t="n">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="T12" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="V12" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="X12" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AD12" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>3.45</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.4</v>
+        <v>5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="AX12" t="n">
-        <v>15.5</v>
+        <v>5.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>3.45</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.7</v>
+        <v>2.66</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="BG12" t="n">
-        <v>21</v>
+        <v>3.05</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
         <v>3.05</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L13" t="n">
         <v>1.45</v>
@@ -2915,7 +2915,7 @@
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
         <v>1.45</v>
@@ -2933,10 +2933,10 @@
         <v>4.6</v>
       </c>
       <c r="T13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
         <v>1.39</v>
@@ -2969,7 +2969,7 @@
         <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG13" t="n">
         <v>14</v>
@@ -2981,7 +2981,7 @@
         <v>80</v>
       </c>
       <c r="AJ13" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK13" t="n">
         <v>38</v>
@@ -2990,7 +2990,7 @@
         <v>60</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
         <v>36</v>
@@ -3008,7 +3008,7 @@
         <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT13" t="n">
         <v>7.4</v>
@@ -3020,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
@@ -3032,29 +3032,29 @@
         <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.5</v>
+        <v>23</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>6.2</v>
       </c>
       <c r="G14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
         <v>1.52</v>
       </c>
       <c r="I14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="J14" t="n">
         <v>4.8</v>
       </c>
       <c r="K14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.29</v>
@@ -3109,13 +3109,13 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
         <v>1.58</v>
@@ -3130,10 +3130,10 @@
         <v>1.73</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="W14" t="n">
         <v>1.16</v>
@@ -3145,7 +3145,7 @@
         <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA14" t="n">
         <v>16.5</v>
@@ -3163,13 +3163,13 @@
         <v>17.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
         <v>29</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI14" t="n">
         <v>34</v>
@@ -3181,7 +3181,7 @@
         <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -3205,7 +3205,7 @@
         <v>12.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AU14" t="n">
         <v>10</v>
@@ -3217,38 +3217,38 @@
         <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AY14" t="n">
         <v>21</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BG14" t="n">
         <v>5.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -3270,67 +3270,67 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cavese 1919</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2.96</v>
+        <v>1.02</v>
       </c>
       <c r="O15" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="T15" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3345,10 +3345,10 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K16" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.26</v>
@@ -3497,70 +3497,70 @@
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="R16" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="T16" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U16" t="n">
         <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z16" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="AJ16" t="n">
         <v>18</v>
@@ -3572,40 +3572,40 @@
         <v>29</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO16" t="n">
         <v>55</v>
       </c>
       <c r="AP16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
         <v>20</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV16" t="n">
         <v>17.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="AX16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY16" t="n">
         <v>9</v>
@@ -3614,29 +3614,29 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="BB16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC16" t="n">
         <v>13.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -3667,31 +3667,31 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G17" t="n">
         <v>2.26</v>
       </c>
       <c r="H17" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="J17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M17" t="n">
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
         <v>1.17</v>
@@ -3709,19 +3709,19 @@
         <v>2.32</v>
       </c>
       <c r="T17" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="U17" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
         <v>1.79</v>
       </c>
       <c r="X17" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="Y17" t="n">
         <v>22</v>
@@ -3733,40 +3733,40 @@
         <v>60</v>
       </c>
       <c r="AB17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD17" t="n">
         <v>16.5</v>
       </c>
-      <c r="AC17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD17" t="n">
+      <c r="AE17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF17" t="n">
         <v>18</v>
       </c>
-      <c r="AE17" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AG17" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ17" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AK17" t="n">
         <v>21</v>
       </c>
       <c r="AL17" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM17" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN17" t="n">
         <v>10.5</v>
@@ -3781,22 +3781,22 @@
         <v>17.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AS17" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="AT17" t="n">
         <v>12.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV17" t="n">
         <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX17" t="n">
         <v>14.5</v>
@@ -3808,10 +3808,10 @@
         <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.6</v>
+        <v>29</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC17" t="n">
         <v>17</v>
@@ -3820,17 +3820,17 @@
         <v>19.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="BF17" t="n">
         <v>7.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G18" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H18" t="n">
         <v>4.5</v>
@@ -3873,25 +3873,25 @@
         <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
         <v>1.34</v>
       </c>
       <c r="P18" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
         <v>2.02</v>
@@ -3909,10 +3909,10 @@
         <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X18" t="n">
         <v>16</v>
@@ -3927,7 +3927,7 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC18" t="n">
         <v>9.6</v>
@@ -3936,16 +3936,16 @@
         <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF18" t="n">
         <v>13</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AH18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
         <v>80</v>
@@ -3957,16 +3957,16 @@
         <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AN18" t="n">
         <v>16</v>
       </c>
       <c r="AO18" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
         <v>12</v>
@@ -3975,10 +3975,10 @@
         <v>13.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -3990,7 +3990,7 @@
         <v>14.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -3999,32 +3999,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.4</v>
+        <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD18" t="n">
         <v>32</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF18" t="n">
         <v>11</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
         <v>1.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O19" t="n">
         <v>1.45</v>
@@ -4100,7 +4100,7 @@
         <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V19" t="n">
         <v>1.67</v>
@@ -4109,7 +4109,7 @@
         <v>1.31</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y19" t="n">
         <v>1000</v>
@@ -4124,7 +4124,7 @@
         <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="AD19" t="n">
         <v>1000</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="AR19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BC19" t="n">
         <v>4.9</v>
       </c>
-      <c r="AS19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG19" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Cavese 1919</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>1.89</v>
       </c>
       <c r="G20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="X20" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY20" t="n">
         <v>3.65</v>
       </c>
-      <c r="H20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="BC20" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="BF20" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -4443,25 +4443,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="G21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="H21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="I21" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="J21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K21" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
@@ -4473,10 +4473,10 @@
         <v>1.38</v>
       </c>
       <c r="P21" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R21" t="n">
         <v>1.27</v>
@@ -4485,13 +4485,13 @@
         <v>3.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="U21" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="V21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="W21" t="n">
         <v>1.07</v>
@@ -4500,25 +4500,25 @@
         <v>14.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AA21" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
         <v>1000</v>
@@ -4548,10 +4548,10 @@
         <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ21" t="n">
         <v>5.3</v>
@@ -4566,47 +4566,47 @@
         <v>20</v>
       </c>
       <c r="AU21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV21" t="n">
         <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="AX21" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY21" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC21" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG21" t="n">
         <v>6.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Trapani</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V22" t="n">
         <v>1.18</v>
       </c>
-      <c r="S22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>2.56</v>
       </c>
       <c r="H23" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I23" t="n">
         <v>4.2</v>
@@ -4846,7 +4846,7 @@
         <v>2.86</v>
       </c>
       <c r="K23" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L23" t="n">
         <v>1.47</v>
@@ -4873,7 +4873,7 @@
         <v>5.1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="U23" t="n">
         <v>1.82</v>
@@ -4897,43 +4897,43 @@
         <v>110</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD23" t="n">
         <v>20</v>
       </c>
       <c r="AE23" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI23" t="n">
         <v>100</v>
       </c>
       <c r="AJ23" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK23" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL23" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AO23" t="n">
         <v>110</v>
@@ -4942,13 +4942,13 @@
         <v>7.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR23" t="n">
         <v>21</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AT23" t="n">
         <v>6.4</v>
@@ -4960,7 +4960,7 @@
         <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AX23" t="n">
         <v>11.5</v>
@@ -4972,29 +4972,29 @@
         <v>18.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -5052,13 +5052,13 @@
         <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P24" t="n">
         <v>1.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R24" t="n">
         <v>1.17</v>
@@ -5070,7 +5070,7 @@
         <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V24" t="n">
         <v>1.38</v>
@@ -5088,7 +5088,7 @@
         <v>24</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB24" t="n">
         <v>8.800000000000001</v>
@@ -5097,13 +5097,13 @@
         <v>8</v>
       </c>
       <c r="AD24" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AF24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG24" t="n">
         <v>15</v>
@@ -5121,19 +5121,19 @@
         <v>42</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AP24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ24" t="n">
         <v>8</v>
@@ -5142,7 +5142,7 @@
         <v>19</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT24" t="n">
         <v>6.6</v>
@@ -5154,7 +5154,7 @@
         <v>13.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX24" t="n">
         <v>13</v>
@@ -5166,29 +5166,29 @@
         <v>19.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="BC24" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -5219,170 +5219,170 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="G25" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="H25" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="I25" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="J25" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K25" t="n">
         <v>4.7</v>
       </c>
       <c r="L25" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P25" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U25" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="V25" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>12</v>
-      </c>
       <c r="AP25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT25" t="n">
         <v>19</v>
       </c>
       <c r="AU25" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV25" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW25" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AX25" t="n">
-        <v>48</v>
+        <v>9.6</v>
       </c>
       <c r="AY25" t="n">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6.8</v>
+        <v>27</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB25" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BG25" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -5455,19 +5455,19 @@
         <v>5.1</v>
       </c>
       <c r="T26" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="U26" t="n">
         <v>1.82</v>
       </c>
       <c r="V26" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W26" t="n">
         <v>1.65</v>
       </c>
       <c r="X26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y26" t="n">
         <v>10.5</v>
@@ -5488,7 +5488,7 @@
         <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AF26" t="n">
         <v>14.5</v>
@@ -5497,13 +5497,13 @@
         <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AK26" t="n">
         <v>36</v>
@@ -5530,7 +5530,7 @@
         <v>20</v>
       </c>
       <c r="AS26" t="n">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AT26" t="n">
         <v>6.8</v>
@@ -5542,7 +5542,7 @@
         <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>8.800000000000001</v>
+        <v>48</v>
       </c>
       <c r="AX26" t="n">
         <v>12.5</v>
@@ -5551,32 +5551,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BA26" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BB26" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="BD26" t="n">
         <v>50</v>
       </c>
       <c r="BE26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF26" t="n">
         <v>10</v>
       </c>
-      <c r="BF26" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG26" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -5598,179 +5598,179 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trapani</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="G27" t="n">
-        <v>1.84</v>
+        <v>3.65</v>
       </c>
       <c r="H27" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="I27" t="n">
-        <v>6.6</v>
+        <v>2.62</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="K27" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M27" t="n">
         <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="P27" t="n">
         <v>1.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T27" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="U27" t="n">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="V27" t="n">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="W27" t="n">
-        <v>2.18</v>
+        <v>1.38</v>
       </c>
       <c r="X27" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG27" t="n">
         <v>20</v>
       </c>
-      <c r="Z27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G28" t="n">
         <v>5.1</v>
       </c>
       <c r="H28" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="I28" t="n">
         <v>2.06</v>
@@ -5816,7 +5816,7 @@
         <v>3.25</v>
       </c>
       <c r="K28" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L28" t="n">
         <v>1.44</v>
@@ -5855,7 +5855,7 @@
         <v>1.24</v>
       </c>
       <c r="X28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y28" t="n">
         <v>7.4</v>
@@ -5867,7 +5867,7 @@
         <v>26</v>
       </c>
       <c r="AB28" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AC28" t="n">
         <v>8</v>
@@ -5876,7 +5876,7 @@
         <v>11.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF28" t="n">
         <v>1000</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI28" t="n">
         <v>55</v>
@@ -5933,7 +5933,7 @@
         <v>21</v>
       </c>
       <c r="AX28" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AY28" t="n">
         <v>16.5</v>
@@ -5945,26 +5945,26 @@
         <v>40</v>
       </c>
       <c r="BB28" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC28" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF28" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG28" t="n">
         <v>16</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         <v>1.73</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I29" t="n">
         <v>9.199999999999999</v>
@@ -6010,10 +6010,10 @@
         <v>3.35</v>
       </c>
       <c r="K29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L29" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
         <v>1.09</v>
@@ -6025,10 +6025,10 @@
         <v>1.43</v>
       </c>
       <c r="P29" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="R29" t="n">
         <v>1.23</v>
@@ -6037,13 +6037,13 @@
         <v>4.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U29" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V29" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W29" t="n">
         <v>2.36</v>
@@ -6064,7 +6064,7 @@
         <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD29" t="n">
         <v>1000</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>4</v>
+        <v>2.06</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.6</v>
+        <v>1.94</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.4</v>
+        <v>1.85</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.88</v>
+        <v>1.88</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.7</v>
+        <v>1.87</v>
       </c>
       <c r="AX29" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AY29" t="n">
-        <v>3.95</v>
+        <v>2.02</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.7</v>
+        <v>1.87</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.3</v>
+        <v>2.16</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.7</v>
+        <v>1.84</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.4</v>
+        <v>1.84</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.86</v>
+        <v>1.88</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.2</v>
+        <v>2.12</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G30" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I30" t="n">
         <v>3.15</v>
-      </c>
-      <c r="I30" t="n">
-        <v>3.2</v>
       </c>
       <c r="J30" t="n">
         <v>3.5</v>
@@ -6207,7 +6207,7 @@
         <v>3.55</v>
       </c>
       <c r="L30" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
         <v>1.06</v>
@@ -6225,10 +6225,10 @@
         <v>1.88</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S30" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T30" t="n">
         <v>1.7</v>
@@ -6237,16 +6237,16 @@
         <v>2.36</v>
       </c>
       <c r="V30" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W30" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X30" t="n">
         <v>15.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z30" t="n">
         <v>21</v>
@@ -6267,13 +6267,13 @@
         <v>32</v>
       </c>
       <c r="AF30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG30" t="n">
         <v>11.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI30" t="n">
         <v>40</v>
@@ -6282,7 +6282,7 @@
         <v>34</v>
       </c>
       <c r="AK30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL30" t="n">
         <v>34</v>
@@ -6297,25 +6297,25 @@
         <v>27</v>
       </c>
       <c r="AP30" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS30" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AT30" t="n">
         <v>11</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW30" t="n">
         <v>29</v>
@@ -6324,13 +6324,13 @@
         <v>15</v>
       </c>
       <c r="AY30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ30" t="n">
         <v>14.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB30" t="n">
         <v>30</v>
@@ -6342,17 +6342,17 @@
         <v>32</v>
       </c>
       <c r="BE30" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BF30" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BG30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -6386,19 +6386,19 @@
         <v>2.88</v>
       </c>
       <c r="G31" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H31" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="I31" t="n">
         <v>3.05</v>
       </c>
       <c r="J31" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="K31" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="L31" t="n">
         <v>1.53</v>
@@ -6407,7 +6407,7 @@
         <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O31" t="n">
         <v>1.56</v>
@@ -6416,7 +6416,7 @@
         <v>1.49</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R31" t="n">
         <v>1.17</v>
@@ -6425,7 +6425,7 @@
         <v>5.2</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="U31" t="n">
         <v>1.72</v>
@@ -6434,13 +6434,13 @@
         <v>1.48</v>
       </c>
       <c r="W31" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X31" t="n">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="Y31" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z31" t="n">
         <v>1000</v>
@@ -6449,10 +6449,10 @@
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD31" t="n">
         <v>1000</v>
@@ -6491,62 +6491,62 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AS31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AX31" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BC31" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BG31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G32" t="n">
         <v>2.52</v>
@@ -6586,13 +6586,13 @@
         <v>3.8</v>
       </c>
       <c r="I32" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J32" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="K32" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L32" t="n">
         <v>1.5</v>
@@ -6610,7 +6610,7 @@
         <v>1.48</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R32" t="n">
         <v>1.17</v>
@@ -6625,22 +6625,22 @@
         <v>1.6</v>
       </c>
       <c r="V32" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W32" t="n">
         <v>1.65</v>
       </c>
       <c r="X32" t="n">
-        <v>980</v>
+        <v>14</v>
       </c>
       <c r="Y32" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z32" t="n">
         <v>980</v>
       </c>
       <c r="AA32" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB32" t="n">
         <v>8.6</v>
@@ -6652,7 +6652,7 @@
         <v>980</v>
       </c>
       <c r="AE32" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF32" t="n">
         <v>16.5</v>
@@ -6682,19 +6682,19 @@
         <v>980</v>
       </c>
       <c r="AO32" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP32" t="n">
-        <v>6.6</v>
+        <v>3.05</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT32" t="n">
         <v>6.2</v>
@@ -6703,10 +6703,10 @@
         <v>6.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX32" t="n">
         <v>9.4</v>
@@ -6715,32 +6715,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB32" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BD32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF32" t="n">
         <v>4.5</v>
       </c>
-      <c r="BE32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BG32" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G33" t="n">
         <v>1.64</v>
@@ -6786,7 +6786,7 @@
         <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L33" t="n">
         <v>1.44</v>
@@ -6816,7 +6816,7 @@
         <v>2.14</v>
       </c>
       <c r="U33" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V33" t="n">
         <v>1.14</v>
@@ -6861,7 +6861,7 @@
         <v>150</v>
       </c>
       <c r="AJ33" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AK33" t="n">
         <v>19</v>
@@ -6888,7 +6888,7 @@
         <v>10</v>
       </c>
       <c r="AS33" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT33" t="n">
         <v>6.2</v>
@@ -6900,7 +6900,7 @@
         <v>19.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AX33" t="n">
         <v>7.6</v>
@@ -6912,7 +6912,7 @@
         <v>20</v>
       </c>
       <c r="BA33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BB33" t="n">
         <v>13</v>
@@ -6921,7 +6921,7 @@
         <v>16.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BE33" t="n">
         <v>11.5</v>
@@ -6930,11 +6930,11 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG33" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-04 17:52:33</t>
+          <t>2026-03-04 20:04:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="H2" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="I2" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
         <v>1.43</v>
@@ -781,64 +781,64 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
         <v>2.02</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T2" t="n">
         <v>1.81</v>
       </c>
       <c r="U2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="X2" t="n">
         <v>13.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z2" t="n">
         <v>27</v>
       </c>
       <c r="AA2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
         <v>9.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
         <v>18</v>
@@ -847,10 +847,10 @@
         <v>55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL2" t="n">
         <v>38</v>
@@ -859,19 +859,19 @@
         <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
         <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS2" t="n">
         <v>60</v>
@@ -883,44 +883,44 @@
         <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
         <v>48</v>
       </c>
       <c r="BB2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE2" t="n">
         <v>85</v>
       </c>
       <c r="BF2" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G3" t="n">
         <v>1.57</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.59</v>
       </c>
       <c r="H3" t="n">
         <v>7.2</v>
@@ -963,49 +963,49 @@
         <v>7.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.45</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T3" t="n">
         <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V3" t="n">
         <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
@@ -1020,7 +1020,7 @@
         <v>7</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
         <v>29</v>
@@ -1029,10 +1029,10 @@
         <v>130</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH3" t="n">
         <v>26</v>
@@ -1053,68 +1053,68 @@
         <v>180</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO3" t="n">
         <v>190</v>
       </c>
       <c r="AP3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR3" t="n">
         <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV3" t="n">
         <v>26</v>
       </c>
       <c r="AW3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AX3" t="n">
         <v>7.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
         <v>24</v>
       </c>
       <c r="BA3" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BB3" t="n">
         <v>13</v>
       </c>
       <c r="BC3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE3" t="n">
-        <v>16.5</v>
+        <v>130</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G4" t="n">
         <v>1.85</v>
@@ -1199,16 +1199,16 @@
         <v>2.16</v>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y4" t="n">
         <v>16</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA4" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AB4" t="n">
         <v>7</v>
@@ -1232,7 +1232,7 @@
         <v>28</v>
       </c>
       <c r="AI4" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
         <v>22</v>
@@ -1241,16 +1241,16 @@
         <v>23</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM4" t="n">
-        <v>180</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
         <v>17.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP4" t="n">
         <v>9.800000000000001</v>
@@ -1259,10 +1259,10 @@
         <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
@@ -1274,10 +1274,10 @@
         <v>20</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY4" t="n">
         <v>9.199999999999999</v>
@@ -1286,29 +1286,29 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BB4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC4" t="n">
         <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF4" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="I5" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="J5" t="n">
         <v>3.05</v>
@@ -1357,7 +1357,7 @@
         <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -1366,7 +1366,7 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P5" t="n">
         <v>1.67</v>
@@ -1381,40 +1381,40 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U5" t="n">
         <v>1.94</v>
       </c>
       <c r="V5" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="W5" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="n">
         <v>10.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
         <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="n">
         <v>32</v>
@@ -1423,7 +1423,7 @@
         <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI5" t="n">
         <v>290</v>
@@ -1432,7 +1432,7 @@
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AL5" t="n">
         <v>380</v>
@@ -1444,7 +1444,7 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
         <v>9.199999999999999</v>
@@ -1456,7 +1456,7 @@
         <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1477,19 +1477,19 @@
         <v>13</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.8</v>
+        <v>23</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>28</v>
       </c>
       <c r="BE5" t="n">
         <v>28</v>
@@ -1498,11 +1498,11 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G6" t="n">
         <v>2.52</v>
@@ -1551,82 +1551,82 @@
         <v>3.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
         <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P6" t="n">
         <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
         <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
         <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
         <v>1.65</v>
       </c>
       <c r="X6" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
         <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>980</v>
+        <v>28</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AG6" t="n">
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AK6" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1641,7 +1641,7 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ6" t="n">
         <v>10</v>
@@ -1650,7 +1650,7 @@
         <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT6" t="n">
         <v>8</v>
@@ -1671,19 +1671,19 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BC6" t="n">
         <v>13</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE6" t="n">
         <v>28</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G7" t="n">
         <v>5.9</v>
       </c>
       <c r="H7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="J7" t="n">
         <v>4.6</v>
@@ -1775,13 +1775,13 @@
         <v>2.56</v>
       </c>
       <c r="V7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="W7" t="n">
         <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
         <v>18.5</v>
@@ -1847,50 +1847,50 @@
         <v>4.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AW7" t="n">
-        <v>11.5</v>
+        <v>4</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY7" t="n">
         <v>4.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA7" t="n">
         <v>16.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE7" t="n">
         <v>4.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
         <v>4.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
         <v>2.44</v>
       </c>
       <c r="H8" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I8" t="n">
         <v>3.8</v>
@@ -1954,7 +1954,7 @@
         <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
@@ -1966,7 +1966,7 @@
         <v>1.94</v>
       </c>
       <c r="U8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
         <v>1.36</v>
@@ -2002,7 +2002,7 @@
         <v>34</v>
       </c>
       <c r="AG8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH8" t="n">
         <v>70</v>
@@ -2011,7 +2011,7 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
         <v>1000</v>
@@ -2029,28 +2029,28 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
         <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX8" t="n">
         <v>6.4</v>
@@ -2059,32 +2059,32 @@
         <v>7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB8" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB8" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BC8" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -2178,10 +2178,10 @@
         <v>30</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>440</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
         <v>9.4</v>
@@ -2214,7 +2214,7 @@
         <v>50</v>
       </c>
       <c r="AM9" t="n">
-        <v>330</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
         <v>22</v>
@@ -2232,7 +2232,7 @@
         <v>20</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT9" t="n">
         <v>8.6</v>
@@ -2244,7 +2244,7 @@
         <v>12.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AX9" t="n">
         <v>12.5</v>
@@ -2256,7 +2256,7 @@
         <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB9" t="n">
         <v>14.5</v>
@@ -2265,10 +2265,10 @@
         <v>21</v>
       </c>
       <c r="BD9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE9" t="n">
         <v>4.6</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.4</v>
       </c>
       <c r="BF9" t="n">
         <v>17</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="G10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H10" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I10" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="J10" t="n">
         <v>3.15</v>
@@ -2327,7 +2327,7 @@
         <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
@@ -2336,25 +2336,25 @@
         <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
         <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
         <v>3.65</v>
       </c>
       <c r="T10" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U10" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V10" t="n">
         <v>1.54</v>
@@ -2363,37 +2363,37 @@
         <v>1.44</v>
       </c>
       <c r="X10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>13</v>
-      </c>
       <c r="AC10" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF10" t="n">
         <v>24</v>
       </c>
       <c r="AG10" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH10" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
         <v>55</v>
@@ -2405,19 +2405,19 @@
         <v>38</v>
       </c>
       <c r="AL10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>330</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
         <v>36</v>
       </c>
       <c r="AO10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
         <v>9</v>
@@ -2426,7 +2426,7 @@
         <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="AT10" t="n">
         <v>9.800000000000001</v>
@@ -2450,29 +2450,29 @@
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BC10" t="n">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>2.14</v>
       </c>
       <c r="G11" t="n">
-        <v>710</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
         <v>2.18</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
         <v>2.96</v>
@@ -2551,10 +2551,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
         <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
         <v>1.43</v>
@@ -2751,7 +2751,7 @@
         <v>1.47</v>
       </c>
       <c r="X12" t="n">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="n">
         <v>1000</v>
@@ -2760,13 +2760,13 @@
         <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
         <v>10</v>
       </c>
       <c r="AC12" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2787,7 +2787,7 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AU12" t="n">
         <v>5.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.05</v>
+        <v>5.3</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.66</v>
+        <v>4</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.05</v>
+        <v>5.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.05</v>
+        <v>7.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>2.38</v>
       </c>
       <c r="G13" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H13" t="n">
         <v>3.35</v>
@@ -2915,7 +2915,7 @@
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
         <v>1.45</v>
@@ -2978,7 +2978,7 @@
         <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="AJ13" t="n">
         <v>38</v>
@@ -2987,16 +2987,16 @@
         <v>38</v>
       </c>
       <c r="AL13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP13" t="n">
         <v>9</v>
@@ -3008,7 +3008,7 @@
         <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT13" t="n">
         <v>7.4</v>
@@ -3020,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
@@ -3032,19 +3032,19 @@
         <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB13" t="n">
         <v>14.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="BD13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE13" t="n">
         <v>5.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>5.4</v>
       </c>
       <c r="BF13" t="n">
         <v>5.7</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -3088,22 +3088,22 @@
         <v>6.2</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="H14" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="I14" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="J14" t="n">
         <v>4.8</v>
       </c>
       <c r="K14" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
@@ -3115,13 +3115,13 @@
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S14" t="n">
         <v>2.42</v>
@@ -3130,13 +3130,13 @@
         <v>1.73</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X14" t="n">
         <v>29</v>
@@ -3145,7 +3145,7 @@
         <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA14" t="n">
         <v>16.5</v>
@@ -3166,10 +3166,10 @@
         <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
         <v>34</v>
@@ -3190,7 +3190,7 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AP14" t="n">
         <v>21</v>
@@ -3205,7 +3205,7 @@
         <v>12.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="AU14" t="n">
         <v>10</v>
@@ -3217,7 +3217,7 @@
         <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY14" t="n">
         <v>21</v>
@@ -3226,29 +3226,29 @@
         <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC14" t="n">
         <v>5.9</v>
       </c>
-      <c r="BC14" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BD14" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>1.69</v>
       </c>
       <c r="G16" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H16" t="n">
         <v>5.2</v>
@@ -3485,28 +3485,28 @@
         <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O16" t="n">
         <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R16" t="n">
         <v>1.56</v>
@@ -3515,7 +3515,7 @@
         <v>2.52</v>
       </c>
       <c r="T16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
         <v>2.32</v>
@@ -3524,13 +3524,13 @@
         <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z16" t="n">
         <v>46</v>
@@ -3545,13 +3545,13 @@
         <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>65</v>
       </c>
       <c r="AF16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
@@ -3566,16 +3566,16 @@
         <v>18</v>
       </c>
       <c r="AK16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
       </c>
       <c r="AM16" t="n">
-        <v>580</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO16" t="n">
         <v>55</v>
@@ -3590,19 +3590,19 @@
         <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV16" t="n">
         <v>17.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="AX16" t="n">
         <v>10</v>
@@ -3626,17 +3626,17 @@
         <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BF16" t="n">
         <v>6.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -3679,10 +3679,10 @@
         <v>3.65</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
         <v>1.23</v>
@@ -3697,13 +3697,13 @@
         <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q17" t="n">
         <v>1.56</v>
       </c>
       <c r="R17" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S17" t="n">
         <v>2.32</v>
@@ -3712,7 +3712,7 @@
         <v>1.51</v>
       </c>
       <c r="U17" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="V17" t="n">
         <v>1.37</v>
@@ -3730,19 +3730,19 @@
         <v>30</v>
       </c>
       <c r="AA17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AB17" t="n">
         <v>16</v>
       </c>
       <c r="AC17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
         <v>16.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AF17" t="n">
         <v>18</v>
@@ -3751,7 +3751,7 @@
         <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI17" t="n">
         <v>85</v>
@@ -3766,7 +3766,7 @@
         <v>28</v>
       </c>
       <c r="AM17" t="n">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="AN17" t="n">
         <v>10.5</v>
@@ -3790,7 +3790,7 @@
         <v>12.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
         <v>12.5</v>
@@ -3805,7 +3805,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA17" t="n">
         <v>29</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -3951,16 +3951,16 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK18" t="n">
         <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AM18" t="n">
-        <v>430</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
         <v>16</v>
@@ -4002,7 +4002,7 @@
         <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB18" t="n">
         <v>10.5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G19" t="n">
         <v>4.3</v>
@@ -4109,7 +4109,7 @@
         <v>1.31</v>
       </c>
       <c r="X19" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="Y19" t="n">
         <v>1000</v>
@@ -4124,7 +4124,7 @@
         <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD19" t="n">
         <v>1000</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU19" t="n">
         <v>4</v>
       </c>
-      <c r="AR19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AV19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AW19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX19" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX19" t="n">
-        <v>6</v>
-      </c>
       <c r="AY19" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BD19" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="BF19" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>2.06</v>
       </c>
       <c r="H20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
         <v>6.4</v>
@@ -4264,7 +4264,7 @@
         <v>3.05</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
         <v>1.41</v>
@@ -4273,7 +4273,7 @@
         <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O20" t="n">
         <v>1.44</v>
@@ -4282,10 +4282,10 @@
         <v>1.65</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S20" t="n">
         <v>3.95</v>
@@ -4303,10 +4303,10 @@
         <v>1.97</v>
       </c>
       <c r="X20" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z20" t="n">
         <v>1000</v>
@@ -4321,28 +4321,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="AG20" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -4351,16 +4351,16 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.95</v>
+        <v>8.4</v>
       </c>
       <c r="AR20" t="n">
         <v>4.7</v>
@@ -4369,22 +4369,22 @@
         <v>5</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="AU20" t="n">
         <v>6</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AW20" t="n">
         <v>4.9</v>
       </c>
       <c r="AX20" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="AY20" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="AZ20" t="n">
         <v>4.4</v>
@@ -4393,10 +4393,10 @@
         <v>5</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BD20" t="n">
         <v>4.8</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="G21" t="n">
         <v>14</v>
@@ -4455,10 +4455,10 @@
         <v>1.42</v>
       </c>
       <c r="J21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K21" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L21" t="n">
         <v>1.42</v>
@@ -4482,13 +4482,13 @@
         <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="V21" t="n">
         <v>3.35</v>
@@ -4497,7 +4497,7 @@
         <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y21" t="n">
         <v>6.2</v>
@@ -4509,28 +4509,28 @@
         <v>11.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AC21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD21" t="n">
         <v>12</v>
       </c>
-      <c r="AD21" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF21" t="n">
         <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AJ21" t="n">
         <v>1000</v>
@@ -4572,41 +4572,41 @@
         <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="AX21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB21" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BC21" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BD21" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -4640,10 +4640,10 @@
         <v>1.7</v>
       </c>
       <c r="G22" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H22" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I22" t="n">
         <v>6.6</v>
@@ -4679,7 +4679,7 @@
         <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U22" t="n">
         <v>1.83</v>
@@ -4688,7 +4688,7 @@
         <v>1.18</v>
       </c>
       <c r="W22" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X22" t="n">
         <v>13.5</v>
@@ -4697,7 +4697,7 @@
         <v>20</v>
       </c>
       <c r="Z22" t="n">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
@@ -4712,7 +4712,7 @@
         <v>29</v>
       </c>
       <c r="AE22" t="n">
-        <v>130</v>
+        <v>480</v>
       </c>
       <c r="AF22" t="n">
         <v>9.800000000000001</v>
@@ -4724,7 +4724,7 @@
         <v>28</v>
       </c>
       <c r="AI22" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
         <v>22</v>
@@ -4733,16 +4733,16 @@
         <v>23</v>
       </c>
       <c r="AL22" t="n">
-        <v>980</v>
+        <v>290</v>
       </c>
       <c r="AM22" t="n">
-        <v>180</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
         <v>17</v>
       </c>
       <c r="AO22" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AP22" t="n">
         <v>9.4</v>
@@ -4754,7 +4754,7 @@
         <v>30</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT22" t="n">
         <v>6.2</v>
@@ -4766,7 +4766,7 @@
         <v>17.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX22" t="n">
         <v>8.4</v>
@@ -4778,7 +4778,7 @@
         <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB22" t="n">
         <v>15.5</v>
@@ -4787,7 +4787,7 @@
         <v>18.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BE22" t="n">
         <v>6.2</v>
@@ -4796,11 +4796,11 @@
         <v>12.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -4834,16 +4834,16 @@
         <v>2.28</v>
       </c>
       <c r="G23" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H23" t="n">
         <v>3.65</v>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J23" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K23" t="n">
         <v>3.25</v>
@@ -4879,7 +4879,7 @@
         <v>1.82</v>
       </c>
       <c r="V23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W23" t="n">
         <v>1.64</v>
@@ -4918,7 +4918,7 @@
         <v>26</v>
       </c>
       <c r="AI23" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="AJ23" t="n">
         <v>42</v>
@@ -4927,7 +4927,7 @@
         <v>34</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
@@ -4939,7 +4939,7 @@
         <v>110</v>
       </c>
       <c r="AP23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ23" t="n">
         <v>9.4</v>
@@ -4948,7 +4948,7 @@
         <v>21</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT23" t="n">
         <v>6.4</v>
@@ -4960,7 +4960,7 @@
         <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX23" t="n">
         <v>11.5</v>
@@ -4972,29 +4972,29 @@
         <v>18.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG23" t="n">
         <v>5.8</v>
       </c>
-      <c r="BF23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -5034,10 +5034,10 @@
         <v>3.35</v>
       </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J24" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K24" t="n">
         <v>3.1</v>
@@ -5049,13 +5049,13 @@
         <v>1.13</v>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O24" t="n">
         <v>1.55</v>
       </c>
       <c r="P24" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q24" t="n">
         <v>2.72</v>
@@ -5073,7 +5073,7 @@
         <v>1.75</v>
       </c>
       <c r="V24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W24" t="n">
         <v>1.58</v>
@@ -5082,43 +5082,43 @@
         <v>8.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z24" t="n">
         <v>24</v>
       </c>
       <c r="AA24" t="n">
-        <v>900</v>
+        <v>190</v>
       </c>
       <c r="AB24" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC24" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="AF24" t="n">
         <v>16</v>
       </c>
       <c r="AG24" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH24" t="n">
         <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AJ24" t="n">
         <v>44</v>
       </c>
       <c r="AK24" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL24" t="n">
         <v>460</v>
@@ -5127,7 +5127,7 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO24" t="n">
         <v>400</v>
@@ -5142,7 +5142,7 @@
         <v>19</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AT24" t="n">
         <v>6.6</v>
@@ -5154,7 +5154,7 @@
         <v>13.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="AX24" t="n">
         <v>13</v>
@@ -5166,7 +5166,7 @@
         <v>19.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BB24" t="n">
         <v>16</v>
@@ -5175,20 +5175,20 @@
         <v>16</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF24" t="n">
         <v>8.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -5225,10 +5225,10 @@
         <v>11</v>
       </c>
       <c r="H25" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I25" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="J25" t="n">
         <v>4.2</v>
@@ -5237,7 +5237,7 @@
         <v>4.7</v>
       </c>
       <c r="L25" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M25" t="n">
         <v>1.08</v>
@@ -5249,10 +5249,10 @@
         <v>1.38</v>
       </c>
       <c r="P25" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R25" t="n">
         <v>1.27</v>
@@ -5267,13 +5267,13 @@
         <v>1.61</v>
       </c>
       <c r="V25" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="W25" t="n">
         <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y25" t="n">
         <v>6.4</v>
@@ -5291,7 +5291,7 @@
         <v>11</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE25" t="n">
         <v>19</v>
@@ -5300,10 +5300,10 @@
         <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AI25" t="n">
         <v>500</v>
@@ -5324,13 +5324,13 @@
         <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="AR25" t="n">
         <v>6.2</v>
@@ -5345,34 +5345,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW25" t="n">
         <v>16</v>
       </c>
       <c r="AX25" t="n">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="AY25" t="n">
         <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BC25" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BF25" t="n">
         <v>15</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -5413,19 +5413,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="G26" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="H26" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K26" t="n">
         <v>3.2</v>
@@ -5449,22 +5449,22 @@
         <v>2.52</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S26" t="n">
         <v>5.1</v>
       </c>
       <c r="T26" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U26" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V26" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W26" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="X26" t="n">
         <v>9</v>
@@ -5473,10 +5473,10 @@
         <v>10.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB26" t="n">
         <v>7.8</v>
@@ -5488,25 +5488,25 @@
         <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="AF26" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="AG26" t="n">
         <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>980</v>
+        <v>900</v>
       </c>
       <c r="AK26" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
         <v>1000</v>
@@ -5554,7 +5554,7 @@
         <v>13</v>
       </c>
       <c r="BA26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB26" t="n">
         <v>14.5</v>
@@ -5566,17 +5566,17 @@
         <v>50</v>
       </c>
       <c r="BE26" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF26" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG26" t="n">
         <v>10</v>
       </c>
-      <c r="BG26" t="n">
-        <v>11</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G27" t="n">
         <v>3.65</v>
@@ -5619,7 +5619,7 @@
         <v>2.62</v>
       </c>
       <c r="J27" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K27" t="n">
         <v>3.4</v>
@@ -5670,7 +5670,7 @@
         <v>16.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>900</v>
+        <v>95</v>
       </c>
       <c r="AB27" t="n">
         <v>13</v>
@@ -5736,7 +5736,7 @@
         <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX27" t="n">
         <v>19</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
         <v>2.06</v>
       </c>
       <c r="J28" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
         <v>3.6</v>
@@ -5846,7 +5846,7 @@
         <v>2.04</v>
       </c>
       <c r="U28" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V28" t="n">
         <v>1.94</v>
@@ -5876,16 +5876,16 @@
         <v>11.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AG28" t="n">
         <v>21</v>
       </c>
       <c r="AH28" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AI28" t="n">
         <v>55</v>
@@ -5897,7 +5897,7 @@
         <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
         <v>4.7</v>
       </c>
       <c r="L29" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M29" t="n">
         <v>1.09</v>
@@ -6028,7 +6028,7 @@
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="R29" t="n">
         <v>1.23</v>
@@ -6061,7 +6061,7 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC29" t="n">
         <v>42</v>
@@ -6097,68 +6097,68 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>2.02</v>
+        <v>2.54</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="BB29" t="n">
-        <v>2.16</v>
+        <v>2.76</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -6222,19 +6222,19 @@
         <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R30" t="n">
         <v>1.43</v>
       </c>
       <c r="S30" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T30" t="n">
         <v>1.7</v>
       </c>
       <c r="U30" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V30" t="n">
         <v>1.46</v>
@@ -6246,10 +6246,10 @@
         <v>15.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA30" t="n">
         <v>50</v>
@@ -6267,7 +6267,7 @@
         <v>32</v>
       </c>
       <c r="AF30" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG30" t="n">
         <v>11.5</v>
@@ -6276,25 +6276,25 @@
         <v>15</v>
       </c>
       <c r="AI30" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ30" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL30" t="n">
         <v>34</v>
       </c>
       <c r="AM30" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN30" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP30" t="n">
         <v>15</v>
@@ -6303,7 +6303,7 @@
         <v>12.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS30" t="n">
         <v>44</v>
@@ -6321,7 +6321,7 @@
         <v>29</v>
       </c>
       <c r="AX30" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY30" t="n">
         <v>11</v>
@@ -6342,17 +6342,17 @@
         <v>32</v>
       </c>
       <c r="BE30" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF30" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="G31" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H31" t="n">
         <v>2.7</v>
@@ -6395,16 +6395,16 @@
         <v>3.05</v>
       </c>
       <c r="J31" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K31" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L31" t="n">
         <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N31" t="n">
         <v>2.44</v>
@@ -6434,37 +6434,37 @@
         <v>1.48</v>
       </c>
       <c r="W31" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X31" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y31" t="n">
         <v>8.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB31" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE31" t="n">
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AH31" t="n">
         <v>1000</v>
@@ -6473,7 +6473,7 @@
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK31" t="n">
         <v>1000</v>
@@ -6491,62 +6491,62 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT31" t="n">
         <v>4.9</v>
       </c>
       <c r="AU31" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV31" t="n">
         <v>9</v>
       </c>
       <c r="AW31" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
         <v>7.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC31" t="n">
         <v>8</v>
       </c>
-      <c r="BC31" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BD31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF31" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G32" t="n">
         <v>2.52</v>
@@ -6592,7 +6592,7 @@
         <v>2.72</v>
       </c>
       <c r="K32" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L32" t="n">
         <v>1.5</v>
@@ -6601,7 +6601,7 @@
         <v>1.12</v>
       </c>
       <c r="N32" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O32" t="n">
         <v>1.57</v>
@@ -6610,7 +6610,7 @@
         <v>1.48</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R32" t="n">
         <v>1.17</v>
@@ -6619,10 +6619,10 @@
         <v>5.5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U32" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="V32" t="n">
         <v>1.31</v>
@@ -6634,16 +6634,16 @@
         <v>14</v>
       </c>
       <c r="Y32" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Z32" t="n">
         <v>980</v>
       </c>
       <c r="AA32" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AB32" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC32" t="n">
         <v>8.4</v>
@@ -6652,19 +6652,19 @@
         <v>980</v>
       </c>
       <c r="AE32" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AF32" t="n">
-        <v>16.5</v>
+        <v>980</v>
       </c>
       <c r="AG32" t="n">
-        <v>15.5</v>
+        <v>980</v>
       </c>
       <c r="AH32" t="n">
         <v>980</v>
       </c>
       <c r="AI32" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ32" t="n">
         <v>980</v>
@@ -6673,28 +6673,28 @@
         <v>980</v>
       </c>
       <c r="AL32" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM32" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN32" t="n">
         <v>980</v>
       </c>
       <c r="AO32" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AP32" t="n">
-        <v>3.05</v>
+        <v>5.3</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT32" t="n">
         <v>6.2</v>
@@ -6703,10 +6703,10 @@
         <v>6.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AX32" t="n">
         <v>9.4</v>
@@ -6715,32 +6715,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BC32" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BF32" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
         <v>4.3</v>
       </c>
       <c r="L33" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M33" t="n">
         <v>1.08</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-04 20:04:18</t>
+          <t>2026-03-04 22:16:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>00:00:00</t>
+          <t>00:01:22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>2.44</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="P2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.8</v>
-      </c>
       <c r="X2" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>27</v>
       </c>
-      <c r="AA2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="AK2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>470</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>290</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>9.4</v>
       </c>
-      <c r="AC2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12</v>
-      </c>
       <c r="AR2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="AU2" t="n">
         <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BA2" t="n">
-        <v>48</v>
+        <v>7.2</v>
       </c>
       <c r="BB2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>26</v>
       </c>
-      <c r="BC2" t="n">
-        <v>21</v>
-      </c>
       <c r="BD2" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BE2" t="n">
-        <v>85</v>
+        <v>6.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>16.5</v>
+        <v>6</v>
       </c>
       <c r="BG2" t="n">
-        <v>48</v>
+        <v>6.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>00:00:00</t>
+          <t>00:06:09</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.56</v>
       </c>
-      <c r="G3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="S3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
         <v>7.6</v>
       </c>
-      <c r="J3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="X3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AH3" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="AI3" t="n">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
         <v>18</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="AM3" t="n">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="AN3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>10</v>
       </c>
-      <c r="AO3" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>24</v>
-      </c>
       <c r="BA3" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G4" t="n">
         <v>1.85</v>
@@ -1205,7 +1205,7 @@
         <v>16</v>
       </c>
       <c r="Z4" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AA4" t="n">
         <v>700</v>
@@ -1232,7 +1232,7 @@
         <v>28</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AJ4" t="n">
         <v>22</v>
@@ -1241,7 +1241,7 @@
         <v>23</v>
       </c>
       <c r="AL4" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
@@ -1259,10 +1259,10 @@
         <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
@@ -1274,7 +1274,7 @@
         <v>20</v>
       </c>
       <c r="AW4" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
         <v>9</v>
@@ -1298,17 +1298,17 @@
         <v>23</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF4" t="n">
         <v>14</v>
       </c>
       <c r="BG4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H5" t="n">
         <v>2.14</v>
       </c>
       <c r="I5" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="J5" t="n">
         <v>3.05</v>
@@ -1372,22 +1372,22 @@
         <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R5" t="n">
         <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U5" t="n">
         <v>1.94</v>
       </c>
       <c r="V5" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W5" t="n">
         <v>1.29</v>
@@ -1396,7 +1396,7 @@
         <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z5" t="n">
         <v>14</v>
@@ -1411,52 +1411,52 @@
         <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
         <v>32</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH5" t="n">
         <v>19.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="AL5" t="n">
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
         <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR5" t="n">
         <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1468,31 +1468,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AY5" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.4</v>
+        <v>40</v>
       </c>
       <c r="BB5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BE5" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BF5" t="n">
         <v>9.800000000000001</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -1551,13 +1551,13 @@
         <v>3.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.39</v>
@@ -1626,7 +1626,7 @@
         <v>85</v>
       </c>
       <c r="AK6" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1641,7 +1641,7 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ6" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
         <v>11</v>
@@ -1674,16 +1674,16 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BC6" t="n">
         <v>13</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE6" t="n">
         <v>28</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>1.69</v>
       </c>
       <c r="J7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K7" t="n">
         <v>6</v>
@@ -1751,7 +1751,7 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O7" t="n">
         <v>1.14</v>
@@ -1760,7 +1760,7 @@
         <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R7" t="n">
         <v>1.81</v>
@@ -1769,7 +1769,7 @@
         <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="U7" t="n">
         <v>2.56</v>
@@ -1814,7 +1814,7 @@
         <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
         <v>1000</v>
@@ -1838,59 +1838,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AR7" t="n">
         <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY7" t="n">
         <v>4.5</v>
       </c>
-      <c r="AU7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY7" t="n">
+      <c r="AZ7" t="n">
         <v>4.3</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BA7" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD7" t="n">
         <v>5</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BE7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
         <v>4.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -1912,179 +1912,179 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>US Latina Calcio</t>
+          <t>S.S.D. Casarano Calcio</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H8" t="n">
         <v>3.3</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>2.52</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="U8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.67</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.7</v>
-      </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG8" t="n">
         <v>14</v>
       </c>
-      <c r="AD8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>34</v>
       </c>
-      <c r="AG8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>70</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>900</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT8" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5.8</v>
       </c>
       <c r="AU8" t="n">
         <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG8" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>7</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>S.S.D. Casarano Calcio</t>
+          <t>US Latina Calcio</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="G9" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H9" t="n">
         <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="X9" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="AG9" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="AI9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>20</v>
+        <v>6.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU9" t="n">
         <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>14.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="BG9" t="n">
         <v>6.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AZ Picerno ASD</t>
+          <t>FC Giugliano</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atalanta B</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5</v>
+        <v>2.98</v>
       </c>
       <c r="I10" t="n">
-        <v>2.82</v>
+        <v>3.35</v>
       </c>
       <c r="J10" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="O10" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="V10" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>42</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>14.5</v>
+        <v>5.3</v>
       </c>
       <c r="AX10" t="n">
-        <v>17</v>
+        <v>7.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="BB10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC10" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BG10" t="n">
         <v>7.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FC Giugliano</t>
+          <t>AZ Picerno ASD</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Atalanta B</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="I12" t="n">
-        <v>3.35</v>
+        <v>2.82</v>
       </c>
       <c r="J12" t="n">
-        <v>2.74</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.54</v>
       </c>
-      <c r="P12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.43</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>42</v>
       </c>
       <c r="AB12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG12" t="n">
         <v>14</v>
       </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1000</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="AX12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF12" t="n">
         <v>7.6</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BG12" t="n">
         <v>7.6</v>
       </c>
-      <c r="AZ12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>3.35</v>
       </c>
       <c r="I13" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J13" t="n">
         <v>3.05</v>
@@ -2915,7 +2915,7 @@
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O13" t="n">
         <v>1.45</v>
@@ -2930,7 +2930,7 @@
         <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
         <v>1.96</v>
@@ -2978,10 +2978,10 @@
         <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="AK13" t="n">
         <v>38</v>
@@ -2990,16 +2990,16 @@
         <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="AQ13" t="n">
         <v>9.4</v>
@@ -3008,7 +3008,7 @@
         <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT13" t="n">
         <v>7.4</v>
@@ -3020,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
@@ -3032,7 +3032,7 @@
         <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB13" t="n">
         <v>14.5</v>
@@ -3041,10 +3041,10 @@
         <v>14.5</v>
       </c>
       <c r="BD13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE13" t="n">
         <v>5.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>5.5</v>
       </c>
       <c r="BF13" t="n">
         <v>5.7</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -3088,28 +3088,28 @@
         <v>6.2</v>
       </c>
       <c r="G14" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="H14" t="n">
         <v>1.48</v>
       </c>
       <c r="I14" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="J14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
@@ -3133,10 +3133,10 @@
         <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="W14" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
         <v>29</v>
@@ -3160,19 +3160,19 @@
         <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF14" t="n">
         <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="AH14" t="n">
         <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ14" t="n">
         <v>1000</v>
@@ -3181,7 +3181,7 @@
         <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -3190,7 +3190,7 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AP14" t="n">
         <v>21</v>
@@ -3205,7 +3205,7 @@
         <v>12.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AU14" t="n">
         <v>10</v>
@@ -3217,7 +3217,7 @@
         <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY14" t="n">
         <v>21</v>
@@ -3226,29 +3226,29 @@
         <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.9</v>
+        <v>28</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BG14" t="n">
         <v>5.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -3270,73 +3270,73 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Cavese 1919</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>1.02</v>
+        <v>2.68</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z15" t="n">
         <v>1000</v>
@@ -3345,34 +3345,34 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AE15" t="n">
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AI15" t="n">
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL15" t="n">
         <v>1000</v>
@@ -3381,68 +3381,68 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
         <v>12</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH16" t="n">
         <v>18</v>
@@ -3569,7 +3569,7 @@
         <v>16.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM16" t="n">
         <v>80</v>
@@ -3590,7 +3590,7 @@
         <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -3676,10 +3676,10 @@
         <v>3.35</v>
       </c>
       <c r="I17" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K17" t="n">
         <v>4.1</v>
@@ -3697,7 +3697,7 @@
         <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
         <v>1.56</v>
@@ -3706,13 +3706,13 @@
         <v>1.65</v>
       </c>
       <c r="S17" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U17" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="V17" t="n">
         <v>1.37</v>
@@ -3727,7 +3727,7 @@
         <v>22</v>
       </c>
       <c r="Z17" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="AA17" t="n">
         <v>150</v>
@@ -3736,13 +3736,13 @@
         <v>16</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD17" t="n">
         <v>16.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AF17" t="n">
         <v>18</v>
@@ -3766,7 +3766,7 @@
         <v>28</v>
       </c>
       <c r="AM17" t="n">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="AN17" t="n">
         <v>10.5</v>
@@ -3787,7 +3787,7 @@
         <v>23</v>
       </c>
       <c r="AT17" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AU17" t="n">
         <v>8.199999999999999</v>
@@ -3811,7 +3811,7 @@
         <v>29</v>
       </c>
       <c r="BB17" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BC17" t="n">
         <v>17</v>
@@ -3820,7 +3820,7 @@
         <v>19.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BF17" t="n">
         <v>7.6</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>1.85</v>
       </c>
       <c r="G18" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H18" t="n">
         <v>4.5</v>
@@ -3879,7 +3879,7 @@
         <v>3.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
@@ -3912,7 +3912,7 @@
         <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="X18" t="n">
         <v>16</v>
@@ -3927,13 +3927,13 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>190</v>
@@ -3948,13 +3948,13 @@
         <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ18" t="n">
         <v>22</v>
       </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
         <v>46</v>
@@ -3963,7 +3963,7 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
@@ -3975,10 +3975,10 @@
         <v>13.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -3987,10 +3987,10 @@
         <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -4002,7 +4002,7 @@
         <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB18" t="n">
         <v>10.5</v>
@@ -4014,17 +4014,17 @@
         <v>32</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF18" t="n">
         <v>11</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4208,7 @@
         <v>3.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.88</v>
+        <v>5.8</v>
       </c>
       <c r="BF19" t="n">
         <v>3.25</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -4240,109 +4240,109 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavese 1919</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.89</v>
+        <v>3.3</v>
       </c>
       <c r="G20" t="n">
-        <v>2.06</v>
+        <v>3.65</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="I20" t="n">
-        <v>6.4</v>
+        <v>2.64</v>
       </c>
       <c r="J20" t="n">
         <v>3.05</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="T20" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="U20" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="V20" t="n">
-        <v>1.19</v>
+        <v>1.61</v>
       </c>
       <c r="W20" t="n">
-        <v>1.97</v>
+        <v>1.38</v>
       </c>
       <c r="X20" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>60</v>
+        <v>12.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG20" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>65</v>
+        <v>17.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ20" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AK20" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -4351,68 +4351,68 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="AQ20" t="n">
         <v>8.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="AS20" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AX20" t="n">
-        <v>5.1</v>
+        <v>19</v>
       </c>
       <c r="AY20" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="BE20" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -4473,10 +4473,10 @@
         <v>1.38</v>
       </c>
       <c r="P21" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
         <v>1.27</v>
@@ -4515,10 +4515,10 @@
         <v>12.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF21" t="n">
         <v>1000</v>
@@ -4572,10 +4572,10 @@
         <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY21" t="n">
         <v>20</v>
@@ -4584,29 +4584,29 @@
         <v>20</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC21" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG21" t="n">
         <v>7.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trapani</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>1.02</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="T22" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
         <v>3.25</v>
       </c>
       <c r="L23" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
         <v>1.12</v>
@@ -4876,7 +4876,7 @@
         <v>1.99</v>
       </c>
       <c r="U23" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V23" t="n">
         <v>1.3</v>
@@ -4918,7 +4918,7 @@
         <v>26</v>
       </c>
       <c r="AI23" t="n">
-        <v>240</v>
+        <v>460</v>
       </c>
       <c r="AJ23" t="n">
         <v>42</v>
@@ -4981,7 +4981,7 @@
         <v>14.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE23" t="n">
         <v>6</v>
@@ -4990,11 +4990,11 @@
         <v>6.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -5025,19 +5025,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="G24" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="H24" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I24" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="J24" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K24" t="n">
         <v>3.1</v>
@@ -5052,7 +5052,7 @@
         <v>2.52</v>
       </c>
       <c r="O24" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P24" t="n">
         <v>1.49</v>
@@ -5073,7 +5073,7 @@
         <v>1.75</v>
       </c>
       <c r="V24" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
         <v>1.58</v>
@@ -5082,10 +5082,10 @@
         <v>8.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA24" t="n">
         <v>190</v>
@@ -5097,7 +5097,7 @@
         <v>7.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
         <v>150</v>
@@ -5115,10 +5115,10 @@
         <v>460</v>
       </c>
       <c r="AJ24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK24" t="n">
         <v>44</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>40</v>
       </c>
       <c r="AL24" t="n">
         <v>460</v>
@@ -5127,7 +5127,7 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AO24" t="n">
         <v>400</v>
@@ -5139,10 +5139,10 @@
         <v>8</v>
       </c>
       <c r="AR24" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT24" t="n">
         <v>6.6</v>
@@ -5154,7 +5154,7 @@
         <v>13.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX24" t="n">
         <v>13</v>
@@ -5166,7 +5166,7 @@
         <v>19.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB24" t="n">
         <v>16</v>
@@ -5175,20 +5175,20 @@
         <v>16</v>
       </c>
       <c r="BD24" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BE24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG24" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BF24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>9</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v>11</v>
       </c>
       <c r="H25" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="I25" t="n">
         <v>1.51</v>
@@ -5243,22 +5243,22 @@
         <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="Q25" t="n">
         <v>2.18</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T25" t="n">
         <v>2.36</v>
@@ -5276,7 +5276,7 @@
         <v>12.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Z25" t="n">
         <v>7.6</v>
@@ -5285,7 +5285,7 @@
         <v>13</v>
       </c>
       <c r="AB25" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="AC25" t="n">
         <v>11</v>
@@ -5324,13 +5324,13 @@
         <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AP25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AR25" t="n">
         <v>6.2</v>
@@ -5339,7 +5339,7 @@
         <v>10.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU25" t="n">
         <v>9.199999999999999</v>
@@ -5360,19 +5360,19 @@
         <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB25" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BD25" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BF25" t="n">
         <v>15</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -5416,13 +5416,13 @@
         <v>2.34</v>
       </c>
       <c r="G26" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H26" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I26" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J26" t="n">
         <v>3.05</v>
@@ -5449,10 +5449,10 @@
         <v>2.52</v>
       </c>
       <c r="R26" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T26" t="n">
         <v>2.08</v>
@@ -5464,7 +5464,7 @@
         <v>1.35</v>
       </c>
       <c r="W26" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X26" t="n">
         <v>9</v>
@@ -5473,10 +5473,10 @@
         <v>10.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AA26" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
         <v>7.8</v>
@@ -5494,10 +5494,10 @@
         <v>26</v>
       </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
@@ -5506,7 +5506,7 @@
         <v>900</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL26" t="n">
         <v>1000</v>
@@ -5515,16 +5515,16 @@
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR26" t="n">
         <v>20</v>
@@ -5554,7 +5554,7 @@
         <v>13</v>
       </c>
       <c r="BA26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BB26" t="n">
         <v>14.5</v>
@@ -5563,20 +5563,20 @@
         <v>16</v>
       </c>
       <c r="BD26" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="BE26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF26" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF26" t="n">
-        <v>9</v>
-      </c>
       <c r="BG26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -5598,179 +5598,179 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Trapani</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="G27" t="n">
-        <v>3.65</v>
+        <v>1.83</v>
       </c>
       <c r="H27" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="I27" t="n">
-        <v>2.62</v>
+        <v>6.6</v>
       </c>
       <c r="J27" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="K27" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
         <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P27" t="n">
         <v>1.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R27" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="V27" t="n">
-        <v>1.61</v>
+        <v>1.18</v>
       </c>
       <c r="W27" t="n">
-        <v>1.38</v>
+        <v>2.2</v>
       </c>
       <c r="X27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>250</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>480</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF27" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU27" t="n">
+      <c r="BG27" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>20</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -5825,13 +5825,13 @@
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
         <v>1.45</v>
       </c>
       <c r="P28" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q28" t="n">
         <v>2.32</v>
@@ -5846,7 +5846,7 @@
         <v>2.04</v>
       </c>
       <c r="U28" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V28" t="n">
         <v>1.94</v>
@@ -5873,7 +5873,7 @@
         <v>8</v>
       </c>
       <c r="AD28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE28" t="n">
         <v>48</v>
@@ -5909,7 +5909,7 @@
         <v>22</v>
       </c>
       <c r="AP28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ28" t="n">
         <v>6.2</v>
@@ -5942,29 +5942,29 @@
         <v>19</v>
       </c>
       <c r="BA28" t="n">
-        <v>40</v>
+        <v>8.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC28" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE28" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG28" t="n">
         <v>16</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
         <v>1.96</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AU29" t="n">
         <v>4.3</v>
@@ -6127,13 +6127,13 @@
         <v>1.95</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY29" t="n">
         <v>2.54</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BA29" t="n">
         <v>1.95</v>
@@ -6142,10 +6142,10 @@
         <v>2.76</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BE29" t="n">
         <v>1.96</v>
@@ -6154,11 +6154,11 @@
         <v>2.42</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -6195,10 +6195,10 @@
         <v>2.52</v>
       </c>
       <c r="H30" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I30" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J30" t="n">
         <v>3.5</v>
@@ -6234,22 +6234,22 @@
         <v>1.7</v>
       </c>
       <c r="U30" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V30" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W30" t="n">
         <v>1.65</v>
       </c>
       <c r="X30" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y30" t="n">
         <v>13.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA30" t="n">
         <v>50</v>
@@ -6276,13 +6276,13 @@
         <v>15</v>
       </c>
       <c r="AI30" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ30" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL30" t="n">
         <v>34</v>
@@ -6300,7 +6300,7 @@
         <v>15</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>19.5</v>
@@ -6315,7 +6315,7 @@
         <v>7.6</v>
       </c>
       <c r="AV30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW30" t="n">
         <v>29</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>2.84</v>
       </c>
       <c r="G31" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H31" t="n">
         <v>2.7</v>
@@ -6434,7 +6434,7 @@
         <v>1.48</v>
       </c>
       <c r="W31" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X31" t="n">
         <v>15.5</v>
@@ -6512,7 +6512,7 @@
         <v>9</v>
       </c>
       <c r="AW31" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX31" t="n">
         <v>7.6</v>
@@ -6530,23 +6530,23 @@
         <v>8.4</v>
       </c>
       <c r="BC31" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF31" t="n">
         <v>8.6</v>
       </c>
-      <c r="BE31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG31" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
         <v>2.28</v>
       </c>
       <c r="G32" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H32" t="n">
         <v>3.8</v>
@@ -6589,13 +6589,13 @@
         <v>4.2</v>
       </c>
       <c r="J32" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="K32" t="n">
         <v>3.25</v>
       </c>
       <c r="L32" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
         <v>1.12</v>
@@ -6610,7 +6610,7 @@
         <v>1.48</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R32" t="n">
         <v>1.17</v>
@@ -6625,10 +6625,10 @@
         <v>1.66</v>
       </c>
       <c r="V32" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W32" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X32" t="n">
         <v>14</v>
@@ -6643,7 +6643,7 @@
         <v>500</v>
       </c>
       <c r="AB32" t="n">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="AC32" t="n">
         <v>8.4</v>
@@ -6688,13 +6688,13 @@
         <v>5.3</v>
       </c>
       <c r="AQ32" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR32" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS32" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT32" t="n">
         <v>6.2</v>
@@ -6703,10 +6703,10 @@
         <v>6.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW32" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX32" t="n">
         <v>9.4</v>
@@ -6715,32 +6715,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA32" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB32" t="n">
         <v>6.6</v>
       </c>
       <c r="BC32" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD32" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG32" t="n">
         <v>7.8</v>
       </c>
-      <c r="BF32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="G33" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I33" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J33" t="n">
         <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L33" t="n">
         <v>1.38</v>
@@ -6813,25 +6813,25 @@
         <v>3.85</v>
       </c>
       <c r="T33" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U33" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V33" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="W33" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="X33" t="n">
         <v>13</v>
       </c>
       <c r="Y33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z33" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AA33" t="n">
         <v>260</v>
@@ -6843,13 +6843,13 @@
         <v>9.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AE33" t="n">
         <v>140</v>
       </c>
       <c r="AF33" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG33" t="n">
         <v>10.5</v>
@@ -6861,10 +6861,10 @@
         <v>150</v>
       </c>
       <c r="AJ33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK33" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL33" t="n">
         <v>980</v>
@@ -6873,7 +6873,7 @@
         <v>210</v>
       </c>
       <c r="AN33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO33" t="n">
         <v>1000</v>
@@ -6882,10 +6882,10 @@
         <v>11.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AR33" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="AS33" t="n">
         <v>11.5</v>
@@ -6900,7 +6900,7 @@
         <v>19.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX33" t="n">
         <v>7.6</v>
@@ -6909,19 +6909,19 @@
         <v>9</v>
       </c>
       <c r="AZ33" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA33" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB33" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC33" t="n">
         <v>16.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE33" t="n">
         <v>11.5</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-04 22:16:11</t>
+          <t>2026-03-05 00:32:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH33"/>
+  <dimension ref="A1:BH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>00:01:22</t>
+          <t>08:15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Dobrudzha</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="G2" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.15</v>
+        <v>2.28</v>
       </c>
       <c r="R2" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB2" t="n">
         <v>7.2</v>
       </c>
-      <c r="T2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="X2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>140</v>
+        <v>480</v>
       </c>
       <c r="AF2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG2" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG2" t="n">
-        <v>13</v>
-      </c>
       <c r="AH2" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>470</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU2" t="n">
         <v>7.2</v>
       </c>
       <c r="AV2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>20</v>
       </c>
-      <c r="AW2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY2" t="n">
+      <c r="BA2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG2" t="n">
         <v>11</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>65</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,184 +937,184 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>00:06:09</t>
+          <t>10:45:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF America</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="H3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2.32</v>
       </c>
-      <c r="I3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="R3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y3" t="n">
         <v>8.6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="U3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="Z3" t="n">
         <v>14</v>
       </c>
       <c r="AA3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>240</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>190</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD3" t="n">
         <v>46</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="BE3" t="n">
         <v>34</v>
       </c>
-      <c r="AT3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>60</v>
-      </c>
       <c r="BF3" t="n">
-        <v>19.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08:15:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dobrudzha</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.78</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="n">
-        <v>1.85</v>
+        <v>2.52</v>
       </c>
       <c r="H4" t="n">
-        <v>5.5</v>
+        <v>3.35</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8</v>
+        <v>3.75</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="U4" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="X4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG4" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AH4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>16</v>
       </c>
-      <c r="Z4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="BA4" t="n">
         <v>23</v>
       </c>
-      <c r="AE4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH4" t="n">
+      <c r="BB4" t="n">
         <v>28</v>
       </c>
-      <c r="AI4" t="n">
-        <v>290</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK4" t="n">
+      <c r="BC4" t="n">
         <v>23</v>
       </c>
-      <c r="AL4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR4" t="n">
+      <c r="BD4" t="n">
         <v>20</v>
       </c>
-      <c r="AS4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>23</v>
-      </c>
       <c r="BE4" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF4" t="n">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10:45:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>NK Aluminij</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="I5" t="n">
-        <v>2.32</v>
+        <v>1.66</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="P5" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.24</v>
+        <v>1.41</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2</v>
+        <v>2.06</v>
       </c>
       <c r="T5" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="U5" t="n">
-        <v>1.94</v>
+        <v>2.62</v>
       </c>
       <c r="V5" t="n">
-        <v>1.75</v>
+        <v>2.48</v>
       </c>
       <c r="W5" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="X5" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="AH5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI5" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>600</v>
+        <v>44</v>
       </c>
       <c r="AO5" t="n">
-        <v>55</v>
+        <v>5.8</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.5</v>
+        <v>5.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>13.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB5" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>24</v>
-      </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BD5" t="n">
-        <v>46</v>
+        <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>34</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FC Giugliano</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="G6" t="n">
-        <v>2.52</v>
+        <v>2.92</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>2.68</v>
       </c>
       <c r="O6" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>1.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y6" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="BA6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG6" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,184 +1713,184 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NK Aluminij</t>
+          <t>US Latina Calcio</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="G7" t="n">
-        <v>5.9</v>
+        <v>2.42</v>
       </c>
       <c r="H7" t="n">
-        <v>1.59</v>
+        <v>3.55</v>
       </c>
       <c r="I7" t="n">
-        <v>1.69</v>
+        <v>3.95</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.19</v>
+        <v>1.58</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU7" t="n">
         <v>6.8</v>
       </c>
-      <c r="O7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="V7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="AV7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AY7" t="n">
-        <v>4.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.3</v>
+        <v>23</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.2</v>
+        <v>28</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.6</v>
+        <v>12.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -1921,61 +1921,61 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H8" t="n">
         <v>3.3</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="O8" t="n">
         <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T8" t="n">
         <v>1.76</v>
       </c>
       <c r="U8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X8" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y8" t="n">
         <v>15.5</v>
@@ -1984,40 +1984,40 @@
         <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>440</v>
+        <v>170</v>
       </c>
       <c r="AB8" t="n">
         <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF8" t="n">
         <v>18</v>
       </c>
       <c r="AG8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AJ8" t="n">
         <v>34</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
@@ -2026,7 +2026,7 @@
         <v>22</v>
       </c>
       <c r="AO8" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AP8" t="n">
         <v>11.5</v>
@@ -2038,7 +2038,7 @@
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT8" t="n">
         <v>8.6</v>
@@ -2050,7 +2050,7 @@
         <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AX8" t="n">
         <v>12.5</v>
@@ -2062,7 +2062,7 @@
         <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BB8" t="n">
         <v>14.5</v>
@@ -2071,10 +2071,10 @@
         <v>21</v>
       </c>
       <c r="BD8" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BF8" t="n">
         <v>17</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Estonian Esiliiga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>US Latina Calcio</t>
+          <t>JK Welco Elekter</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>2.22</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>16.5</v>
       </c>
       <c r="L9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M9" t="n">
         <v>1.01</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.1</v>
-      </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>1.03</v>
       </c>
       <c r="O9" t="n">
-        <v>1.6</v>
+        <v>1.09</v>
       </c>
       <c r="P9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BF9" t="n">
         <v>1.55</v>
       </c>
-      <c r="Q9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X9" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>6</v>
-      </c>
       <c r="BG9" t="n">
-        <v>6.8</v>
+        <v>1.55</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FC Giugliano</t>
+          <t>AZ Picerno ASD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Atalanta B</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H10" t="n">
-        <v>2.98</v>
+        <v>2.6</v>
       </c>
       <c r="I10" t="n">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="J10" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.54</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.43</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX10" t="n">
         <v>16</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AY10" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BB10" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.4</v>
+        <v>40</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Estonian Esiliiga</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>JK Welco Elekter</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.14</v>
+        <v>2.46</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>2.58</v>
       </c>
       <c r="H11" t="n">
-        <v>2.18</v>
+        <v>3.25</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>3.45</v>
       </c>
       <c r="J11" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="P11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S11" t="n">
-        <v>1.09</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.47</v>
+        <v>1.96</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V11" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
-        <v>1.27</v>
+        <v>1.63</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.04</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.04</v>
+        <v>23</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.04</v>
+        <v>34</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.04</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.04</v>
+        <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.04</v>
+        <v>26</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.04</v>
+        <v>23</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.04</v>
+        <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.55</v>
+        <v>11</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.55</v>
+        <v>9</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AZ Picerno ASD</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atalanta B</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.86</v>
+        <v>6.6</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5</v>
+        <v>1.48</v>
       </c>
       <c r="I12" t="n">
-        <v>2.82</v>
+        <v>1.51</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>5.1</v>
       </c>
       <c r="K12" t="n">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8</v>
+        <v>2.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.02</v>
+        <v>1.59</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="S12" t="n">
-        <v>3.65</v>
+        <v>2.52</v>
       </c>
       <c r="T12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V12" t="n">
-        <v>1.54</v>
+        <v>2.96</v>
       </c>
       <c r="W12" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>42</v>
+        <v>14.5</v>
       </c>
       <c r="AB12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD12" t="n">
         <v>12</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE12" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BF12" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,45 +2877,45 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Cavese 1919</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="G13" t="n">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J13" t="n">
         <v>3.35</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>3.65</v>
       </c>
-      <c r="J13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.25</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="M13" t="n">
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
         <v>1.45</v>
@@ -2924,7 +2924,7 @@
         <v>1.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
         <v>1.24</v>
@@ -2933,135 +2933,135 @@
         <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="U13" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="W13" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="X13" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Y13" t="n">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="Z13" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
+      <c r="AR13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW13" t="n">
         <v>5.1</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AX13" t="n">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>14.5</v>
+        <v>4.7</v>
       </c>
       <c r="BC13" t="n">
-        <v>14.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>FC Basel</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Grasshoppers Zurich</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6.2</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF14" t="n">
         <v>7.2</v>
       </c>
-      <c r="H14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X14" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>400</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>7</v>
-      </c>
       <c r="BG14" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cavese 1919</t>
+          <t>St Gallen</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="G15" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="H15" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>2.68</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="P15" t="n">
-        <v>1.65</v>
+        <v>2.58</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.23</v>
+        <v>1.64</v>
       </c>
       <c r="S15" t="n">
-        <v>3.95</v>
+        <v>2.48</v>
       </c>
       <c r="T15" t="n">
-        <v>1.89</v>
+        <v>1.51</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7</v>
+        <v>2.74</v>
       </c>
       <c r="V15" t="n">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="W15" t="n">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="X15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Y15" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="AC15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR15" t="n">
         <v>22</v>
       </c>
-      <c r="AG15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AS15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.9</v>
+        <v>23</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AY15" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.6</v>
+        <v>25</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.7</v>
+        <v>17.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.8</v>
+        <v>22</v>
       </c>
       <c r="BE15" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="BG15" t="n">
-        <v>5</v>
+        <v>16.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FC Basel</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grasshoppers Zurich</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="G16" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="H16" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>5.4</v>
+        <v>3.85</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.52</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="U16" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="V16" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="W16" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="X16" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>320</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK16" t="n">
         <v>24</v>
       </c>
-      <c r="Y16" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF16" t="n">
+      <c r="AL16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
         <v>12</v>
       </c>
-      <c r="AG16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK16" t="n">
+      <c r="AQ16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV16" t="n">
         <v>16.5</v>
       </c>
-      <c r="AL16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AW16" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="AX16" t="n">
         <v>10</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BB16" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BC16" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>30</v>
+        <v>7.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Gallen</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.14</v>
+        <v>3.6</v>
       </c>
       <c r="G17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H17" t="n">
         <v>2.26</v>
       </c>
-      <c r="H17" t="n">
-        <v>3.35</v>
-      </c>
       <c r="I17" t="n">
-        <v>3.7</v>
+        <v>2.48</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="L17" t="n">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="M17" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.56</v>
+        <v>2.42</v>
       </c>
       <c r="R17" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="U17" t="n">
-        <v>2.76</v>
+        <v>1.88</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.68</v>
       </c>
       <c r="W17" t="n">
-        <v>1.79</v>
+        <v>1.32</v>
       </c>
       <c r="X17" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AD17" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>22</v>
+        <v>5.1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>13</v>
+        <v>5.9</v>
       </c>
       <c r="AS17" t="n">
-        <v>23</v>
+        <v>3.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>14</v>
+        <v>5.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="AX17" t="n">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="BA17" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="BB17" t="n">
-        <v>23</v>
+        <v>3.1</v>
       </c>
       <c r="BC17" t="n">
-        <v>17</v>
+        <v>3.55</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.5</v>
+        <v>3.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>38</v>
+        <v>5.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.6</v>
+        <v>3.05</v>
       </c>
       <c r="BG17" t="n">
-        <v>18</v>
+        <v>5.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="G18" t="n">
-        <v>1.92</v>
+        <v>3.65</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>2.42</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="K18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.9</v>
       </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.6</v>
-      </c>
       <c r="T18" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="X18" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>42</v>
+        <v>16.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="AF18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR18" t="n">
         <v>13</v>
       </c>
-      <c r="AG18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
+      <c r="AS18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY18" t="n">
         <v>12</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT18" t="n">
+      <c r="BA18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC18" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BD18" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="BG18" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,179 +4046,179 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="G19" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2</v>
+        <v>2.96</v>
       </c>
       <c r="I19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N19" t="n">
         <v>2.48</v>
       </c>
-      <c r="J19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="O19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P19" t="n">
         <v>1.46</v>
       </c>
-      <c r="M19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.65</v>
-      </c>
       <c r="Q19" t="n">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="S19" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="U19" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="V19" t="n">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="W19" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="X19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF19" t="n">
         <v>19</v>
       </c>
-      <c r="Y19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1000</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.9</v>
+        <v>12.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX19" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="AY19" t="n">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.9</v>
+        <v>19.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.6</v>
+        <v>16</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -4240,106 +4240,106 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="T20" t="n">
         <v>1.01</v>
       </c>
-      <c r="M20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.8</v>
-      </c>
       <c r="U20" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
         <v>1000</v>
@@ -4357,69 +4357,69 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>450</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>460</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX21" t="n">
         <v>11.5</v>
       </c>
-      <c r="G21" t="n">
-        <v>14</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="AY21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA21" t="n">
         <v>5.3</v>
       </c>
-      <c r="L21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>120</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>200</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>380</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ21" t="n">
+      <c r="BB21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG21" t="n">
         <v>5.3</v>
       </c>
-      <c r="AR21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,100 +4628,100 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>1.02</v>
+        <v>3.55</v>
       </c>
       <c r="O22" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF22" t="n">
         <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
@@ -4742,72 +4742,72 @@
         <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,179 +4822,179 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.28</v>
+        <v>8.6</v>
       </c>
       <c r="G23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.54</v>
       </c>
-      <c r="H23" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.99</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.83</v>
+        <v>1.54</v>
       </c>
       <c r="V23" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
         <v>10.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>13</v>
+        <v>5.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>32</v>
+        <v>7.6</v>
       </c>
       <c r="AA23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>510</v>
+      </c>
+      <c r="AG23" t="n">
         <v>110</v>
       </c>
-      <c r="AB23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD23" t="n">
+      <c r="AH23" t="n">
+        <v>90</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT23" t="n">
         <v>20</v>
       </c>
-      <c r="AE23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>460</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ23" t="n">
+      <c r="AU23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV23" t="n">
         <v>9.4</v>
       </c>
-      <c r="AR23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>14</v>
-      </c>
       <c r="AW23" t="n">
-        <v>5.6</v>
+        <v>17.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AY23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG23" t="n">
         <v>10</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -5016,85 +5016,85 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2.62</v>
       </c>
-      <c r="G24" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.72</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S24" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U24" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W24" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="X24" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="AA24" t="n">
-        <v>190</v>
+        <v>900</v>
       </c>
       <c r="AB24" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD24" t="n">
         <v>16</v>
@@ -5103,49 +5103,49 @@
         <v>150</v>
       </c>
       <c r="AF24" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AG24" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AI24" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AK24" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR24" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU24" t="n">
         <v>6.2</v>
@@ -5154,48 +5154,48 @@
         <v>13.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>9.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="AX24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BC24" t="n">
         <v>16</v>
       </c>
       <c r="BD24" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BE24" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BF24" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BG24" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Trapani</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>8.6</v>
+        <v>1.73</v>
       </c>
       <c r="G25" t="n">
-        <v>11</v>
+        <v>1.82</v>
       </c>
       <c r="H25" t="n">
-        <v>1.45</v>
+        <v>5.7</v>
       </c>
       <c r="I25" t="n">
-        <v>1.51</v>
+        <v>6.8</v>
       </c>
       <c r="J25" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="M25" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
         <v>1.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R25" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="U25" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="V25" t="n">
-        <v>2.96</v>
+        <v>1.18</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="X25" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="n">
-        <v>7.6</v>
+        <v>250</v>
       </c>
       <c r="AA25" t="n">
-        <v>13</v>
+        <v>900</v>
       </c>
       <c r="AB25" t="n">
-        <v>46</v>
+        <v>7.2</v>
       </c>
       <c r="AC25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>480</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG25" t="n">
         <v>11</v>
       </c>
-      <c r="AD25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>48</v>
-      </c>
       <c r="AH25" t="n">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="AI25" t="n">
         <v>500</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO25" t="n">
-        <v>11</v>
+        <v>700</v>
       </c>
       <c r="AP25" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="AS25" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="AT25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>20</v>
       </c>
-      <c r="AU25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>17</v>
-      </c>
       <c r="BA25" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BE25" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,117 +5399,117 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.34</v>
+        <v>4.4</v>
       </c>
       <c r="G26" t="n">
-        <v>2.46</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>3.55</v>
+        <v>1.97</v>
       </c>
       <c r="I26" t="n">
-        <v>3.85</v>
+        <v>2.06</v>
       </c>
       <c r="J26" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="P26" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="S26" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="U26" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="V26" t="n">
-        <v>1.35</v>
+        <v>1.94</v>
       </c>
       <c r="W26" t="n">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="X26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Y26" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="Z26" t="n">
-        <v>44</v>
+        <v>11.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB26" t="n">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="AF26" t="n">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="AG26" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AJ26" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>80</v>
+        <v>440</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
@@ -5518,72 +5518,72 @@
         <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV26" t="n">
         <v>9.4</v>
       </c>
-      <c r="AR26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AW26" t="n">
-        <v>48</v>
+        <v>19.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB26" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="BC26" t="n">
-        <v>16</v>
+        <v>9.6</v>
       </c>
       <c r="BD26" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE26" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="BF26" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trapani</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="H27" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="I27" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K27" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M27" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O27" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="P27" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="U27" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="V27" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="W27" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="X27" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>900</v>
       </c>
-      <c r="AB27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>480</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>22</v>
-      </c>
       <c r="AK27" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="AO27" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>9.4</v>
+        <v>3.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12</v>
+        <v>2.18</v>
       </c>
       <c r="AR27" t="n">
-        <v>30</v>
+        <v>1.92</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.4</v>
+        <v>1.89</v>
       </c>
       <c r="AT27" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>17.5</v>
+        <v>2.02</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.6</v>
+        <v>1.88</v>
       </c>
       <c r="AX27" t="n">
-        <v>8.4</v>
+        <v>4.7</v>
       </c>
       <c r="AY27" t="n">
-        <v>9</v>
+        <v>2.76</v>
       </c>
       <c r="AZ27" t="n">
-        <v>20</v>
+        <v>2.02</v>
       </c>
       <c r="BA27" t="n">
-        <v>6.2</v>
+        <v>1.88</v>
       </c>
       <c r="BB27" t="n">
-        <v>15.5</v>
+        <v>2.68</v>
       </c>
       <c r="BC27" t="n">
-        <v>18.5</v>
+        <v>1.98</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.9</v>
+        <v>1.88</v>
       </c>
       <c r="BE27" t="n">
-        <v>6.2</v>
+        <v>1.93</v>
       </c>
       <c r="BF27" t="n">
-        <v>12.5</v>
+        <v>2.64</v>
       </c>
       <c r="BG27" t="n">
-        <v>6.4</v>
+        <v>1.89</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,179 +5792,179 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Quindio</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="G28" t="n">
-        <v>5.1</v>
+        <v>2.52</v>
       </c>
       <c r="H28" t="n">
-        <v>1.93</v>
+        <v>3.15</v>
       </c>
       <c r="I28" t="n">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L28" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V28" t="n">
         <v>1.45</v>
       </c>
-      <c r="P28" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.94</v>
-      </c>
       <c r="W28" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="X28" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Y28" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="Z28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ28" t="n">
         <v>12</v>
       </c>
-      <c r="AA28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>85</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>460</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AR28" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="AS28" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="AT28" t="n">
         <v>11</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AZ28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF28" t="n">
         <v>19</v>
       </c>
-      <c r="BA28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BG28" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -5981,78 +5981,78 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Real Soacha Cundinamarc</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Internacional de Palmir</t>
         </is>
       </c>
       <c r="F29" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O29" t="n">
         <v>1.56</v>
       </c>
-      <c r="G29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H29" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.43</v>
-      </c>
       <c r="P29" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="R29" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="T29" t="n">
         <v>2.14</v>
       </c>
       <c r="U29" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="V29" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>2.36</v>
+        <v>1.72</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z29" t="n">
         <v>1000</v>
@@ -6061,23 +6061,23 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="AC29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG29" t="n">
         <v>42</v>
       </c>
-      <c r="AD29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1000</v>
-      </c>
       <c r="AH29" t="n">
         <v>1000</v>
       </c>
@@ -6085,10 +6085,10 @@
         <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AL29" t="n">
         <v>1000</v>
@@ -6097,75 +6097,75 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>2.28</v>
+        <v>5.1</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.92</v>
+        <v>7</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.96</v>
+        <v>8.6</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.95</v>
+        <v>5.9</v>
       </c>
       <c r="AU29" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AY29" t="n">
-        <v>2.54</v>
+        <v>5.3</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.93</v>
+        <v>6.8</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.95</v>
+        <v>8.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>2.76</v>
+        <v>7.2</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.16</v>
+        <v>7.2</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.91</v>
+        <v>8</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.96</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.42</v>
+        <v>7.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.88</v>
+        <v>8.6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>20:10:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="G30" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="H30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K30" t="n">
         <v>3.15</v>
       </c>
-      <c r="I30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="M30" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="N30" t="n">
-        <v>4.3</v>
+        <v>2.58</v>
       </c>
       <c r="O30" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.89</v>
+        <v>2.88</v>
       </c>
       <c r="R30" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="T30" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="U30" t="n">
-        <v>2.36</v>
+        <v>1.66</v>
       </c>
       <c r="V30" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="X30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="Z30" t="n">
-        <v>21</v>
+        <v>980</v>
       </c>
       <c r="AA30" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AB30" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>13.5</v>
+        <v>980</v>
       </c>
       <c r="AE30" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AF30" t="n">
-        <v>16.5</v>
+        <v>980</v>
       </c>
       <c r="AG30" t="n">
-        <v>11.5</v>
+        <v>980</v>
       </c>
       <c r="AH30" t="n">
-        <v>15</v>
+        <v>980</v>
       </c>
       <c r="AI30" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AJ30" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AK30" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="AL30" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AM30" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AN30" t="n">
-        <v>18.5</v>
+        <v>980</v>
       </c>
       <c r="AO30" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AP30" t="n">
-        <v>15</v>
+        <v>5.3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>5.2</v>
       </c>
       <c r="AR30" t="n">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>44</v>
+        <v>8.6</v>
       </c>
       <c r="AT30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX30" t="n">
         <v>11</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AY30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF30" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BG30" t="n">
-        <v>26</v>
+        <v>5.9</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,572 +6369,184 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>22:20:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarc</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Internacional de Palmir</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="G31" t="n">
-        <v>3.2</v>
+        <v>1.64</v>
       </c>
       <c r="H31" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>3.05</v>
+        <v>7.8</v>
       </c>
       <c r="J31" t="n">
-        <v>2.88</v>
+        <v>3.95</v>
       </c>
       <c r="K31" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>2.44</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="P31" t="n">
-        <v>1.49</v>
+        <v>1.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="R31" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
         <v>2.12</v>
       </c>
       <c r="U31" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="V31" t="n">
-        <v>1.48</v>
+        <v>1.16</v>
       </c>
       <c r="W31" t="n">
-        <v>1.45</v>
+        <v>2.56</v>
       </c>
       <c r="X31" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y31" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW31" t="n">
         <v>8.4</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>42</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="AX31" t="n">
         <v>7.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ31" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BA31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE31" t="n">
         <v>8.6</v>
       </c>
-      <c r="BB31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BF31" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BG31" t="n">
         <v>8.6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>20:10:00</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Llaneros FC</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Internacional de Bogotá</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X32" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>980</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>980</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-03-05 00:32:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>22:20:00</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Junior FC Barranquilla</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Alianza FC Valledupar</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="H33" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="I33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J33" t="n">
-        <v>4</v>
-      </c>
-      <c r="K33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="X33" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>260</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="G2" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I2" t="n">
         <v>5.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.5</v>
@@ -781,146 +781,146 @@
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="X2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="n">
         <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AA2" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>480</v>
+        <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AG2" t="n">
         <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>180</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP2" t="n">
         <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="AT2" t="n">
         <v>6.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="AX2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA2" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BB2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>17.5</v>
       </c>
-      <c r="BC2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>11</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>3.85</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="J3" t="n">
         <v>3.1</v>
@@ -969,67 +969,67 @@
         <v>3.35</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T3" t="n">
         <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="V3" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
         <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AB3" t="n">
         <v>13</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
         <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AF3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG3" t="n">
         <v>18.5</v>
@@ -1038,52 +1038,52 @@
         <v>19.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK3" t="n">
         <v>240</v>
       </c>
       <c r="AL3" t="n">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="AO3" t="n">
         <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
         <v>14.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU3" t="n">
         <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW3" t="n">
         <v>13.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
         <v>14.5</v>
@@ -1095,16 +1095,16 @@
         <v>23</v>
       </c>
       <c r="BB3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC3" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="BD3" t="n">
-        <v>46</v>
+        <v>8.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BF3" t="n">
         <v>9.800000000000001</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1148,10 @@
         <v>2.36</v>
       </c>
       <c r="G4" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I4" t="n">
         <v>3.75</v>
@@ -1160,49 +1160,49 @@
         <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
         <v>980</v>
@@ -1223,13 +1223,13 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>16.5</v>
+        <v>29</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
@@ -1238,31 +1238,31 @@
         <v>150</v>
       </c>
       <c r="AK4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AO4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
         <v>8.4</v>
@@ -1274,7 +1274,7 @@
         <v>11.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AX4" t="n">
         <v>12.5</v>
@@ -1283,13 +1283,13 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>23</v>
+        <v>9.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="BC4" t="n">
         <v>23</v>
@@ -1298,17 +1298,17 @@
         <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF4" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="BG4" t="n">
-        <v>15.5</v>
+        <v>8.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -1372,25 +1372,25 @@
         <v>3.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="S5" t="n">
         <v>2.06</v>
       </c>
       <c r="T5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V5" t="n">
         <v>2.48</v>
       </c>
       <c r="W5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1399,19 +1399,19 @@
         <v>18.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA5" t="n">
         <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC5" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1420,7 +1420,7 @@
         <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AH5" t="n">
         <v>19</v>
@@ -1441,68 +1441,68 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AP5" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU5" t="n">
         <v>6</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW5" t="n">
         <v>11</v>
       </c>
-      <c r="AV5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AX5" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
       <c r="BA5" t="n">
         <v>10.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G6" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>2.96</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K6" t="n">
         <v>3.2</v>
@@ -1557,40 +1557,40 @@
         <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O6" t="n">
         <v>1.55</v>
       </c>
       <c r="P6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R6" t="n">
         <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T6" t="n">
         <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V6" t="n">
         <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
         <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1611,7 +1611,7 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
         <v>1000</v>
@@ -1641,16 +1641,16 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ6" t="n">
         <v>5.1</v>
       </c>
       <c r="AR6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AT6" t="n">
         <v>4.9</v>
@@ -1662,41 +1662,41 @@
         <v>8.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY6" t="n">
         <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.15</v>
+        <v>48</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>16</v>
+        <v>8.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.2</v>
+        <v>29</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J7" t="n">
         <v>3.1</v>
@@ -1751,28 +1751,28 @@
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="O7" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="P7" t="n">
         <v>1.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="V7" t="n">
         <v>1.35</v>
@@ -1784,7 +1784,7 @@
         <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1796,22 +1796,22 @@
         <v>7</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AE7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AG7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH7" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
@@ -1838,22 +1838,22 @@
         <v>7.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AU7" t="n">
         <v>6.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7" t="n">
         <v>9.6</v>
@@ -1865,32 +1865,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="BC7" t="n">
         <v>14.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="BE7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG7" t="n">
         <v>10</v>
       </c>
-      <c r="BF7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="G8" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="J8" t="n">
         <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.43</v>
@@ -1945,13 +1945,13 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
         <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
         <v>2.02</v>
@@ -1966,28 +1966,28 @@
         <v>1.76</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="X8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="n">
         <v>15.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AA8" t="n">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC8" t="n">
         <v>9.199999999999999</v>
@@ -1996,13 +1996,13 @@
         <v>15.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF8" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
         <v>21</v>
@@ -2011,10 +2011,10 @@
         <v>250</v>
       </c>
       <c r="AJ8" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AK8" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="AL8" t="n">
         <v>120</v>
@@ -2023,68 +2023,68 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO8" t="n">
         <v>70</v>
       </c>
       <c r="AP8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC8" t="n">
         <v>11.5</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS8" t="n">
+      <c r="BD8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF8" t="n">
         <v>5.6</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>17</v>
       </c>
       <c r="BG8" t="n">
         <v>6.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2118,19 @@
         <v>2.14</v>
       </c>
       <c r="G9" t="n">
-        <v>2.46</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="I9" t="n">
-        <v>8.6</v>
+        <v>3.55</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="L9" t="n">
         <v>1.2</v>
@@ -2166,7 +2166,7 @@
         <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2223,52 +2223,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="BF9" t="n">
         <v>1.55</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="G10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="I10" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
         <v>3.55</v>
@@ -2333,31 +2333,31 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U10" t="n">
         <v>2.06</v>
       </c>
       <c r="V10" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W10" t="n">
         <v>1.48</v>
@@ -2381,7 +2381,7 @@
         <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
         <v>34</v>
@@ -2414,31 +2414,31 @@
         <v>34</v>
       </c>
       <c r="AO10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>9</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="AT10" t="n">
         <v>9.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV10" t="n">
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX10" t="n">
         <v>16</v>
@@ -2450,29 +2450,29 @@
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB10" t="n">
         <v>38</v>
       </c>
       <c r="BC10" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BD10" t="n">
         <v>40</v>
       </c>
       <c r="BE10" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BF10" t="n">
-        <v>27</v>
+        <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G11" t="n">
         <v>2.58</v>
       </c>
       <c r="H11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
         <v>3.35</v>
@@ -2536,19 +2536,19 @@
         <v>1.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U11" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="V11" t="n">
         <v>1.41</v>
@@ -2563,34 +2563,34 @@
         <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA11" t="n">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC11" t="n">
         <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>190</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
         <v>95</v>
@@ -2608,7 +2608,7 @@
         <v>32</v>
       </c>
       <c r="AO11" t="n">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AP11" t="n">
         <v>9.199999999999999</v>
@@ -2617,10 +2617,10 @@
         <v>9.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS11" t="n">
-        <v>23</v>
+        <v>7.2</v>
       </c>
       <c r="AT11" t="n">
         <v>7.4</v>
@@ -2632,7 +2632,7 @@
         <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>34</v>
+        <v>6.8</v>
       </c>
       <c r="AX11" t="n">
         <v>13</v>
@@ -2644,10 +2644,10 @@
         <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>28</v>
+        <v>7.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BC11" t="n">
         <v>23</v>
@@ -2656,7 +2656,7 @@
         <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BF11" t="n">
         <v>11</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -2706,10 +2706,10 @@
         <v>1.48</v>
       </c>
       <c r="I12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K12" t="n">
         <v>5.5</v>
@@ -2721,31 +2721,31 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O12" t="n">
         <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="R12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="T12" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U12" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V12" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="W12" t="n">
         <v>1.16</v>
@@ -2769,13 +2769,13 @@
         <v>13.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
         <v>75</v>
@@ -2814,53 +2814,53 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW12" t="n">
         <v>12.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AY12" t="n">
         <v>19.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA12" t="n">
         <v>21</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD12" t="n">
         <v>28</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF12" t="n">
         <v>15</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="I13" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L13" t="n">
         <v>1.52</v>
@@ -2924,31 +2924,31 @@
         <v>1.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U13" t="n">
         <v>1.7</v>
       </c>
       <c r="V13" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Y13" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2963,25 +2963,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH13" t="n">
         <v>60</v>
       </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>65</v>
-      </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>65</v>
@@ -2993,7 +2993,7 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
@@ -3005,7 +3005,7 @@
         <v>8.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AS13" t="n">
         <v>5</v>
@@ -3014,47 +3014,47 @@
         <v>4.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY13" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="BA13" t="n">
         <v>4.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G14" t="n">
         <v>1.76</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>4.2</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.32</v>
@@ -3127,10 +3127,10 @@
         <v>2.68</v>
       </c>
       <c r="T14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U14" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V14" t="n">
         <v>1.23</v>
@@ -3139,116 +3139,116 @@
         <v>2.3</v>
       </c>
       <c r="X14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y14" t="n">
         <v>24</v>
       </c>
       <c r="Z14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA14" t="n">
         <v>120</v>
       </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
       <c r="AB14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="AF14" t="n">
         <v>12</v>
       </c>
       <c r="AG14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>18</v>
       </c>
-      <c r="AI14" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AK14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM14" t="n">
-        <v>580</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO14" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP14" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AQ14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR14" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AT14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV14" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
         <v>23</v>
       </c>
       <c r="BB14" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="BE14" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G15" t="n">
         <v>2.38</v>
@@ -3291,7 +3291,7 @@
         <v>3.3</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
         <v>3.85</v>
@@ -3306,7 +3306,7 @@
         <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P15" t="n">
         <v>2.58</v>
@@ -3315,16 +3315,16 @@
         <v>1.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T15" t="n">
         <v>1.51</v>
       </c>
       <c r="U15" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V15" t="n">
         <v>1.43</v>
@@ -3333,31 +3333,31 @@
         <v>1.72</v>
       </c>
       <c r="X15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z15" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="AA15" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AB15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AF15" t="n">
-        <v>38</v>
+        <v>18.5</v>
       </c>
       <c r="AG15" t="n">
         <v>12</v>
@@ -3366,83 +3366,83 @@
         <v>14</v>
       </c>
       <c r="AI15" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AJ15" t="n">
         <v>32</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AM15" t="n">
         <v>55</v>
       </c>
       <c r="AN15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV15" t="n">
         <v>12.5</v>
       </c>
-      <c r="AO15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ15" t="n">
+      <c r="AW15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX15" t="n">
         <v>16.5</v>
       </c>
-      <c r="AR15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV15" t="n">
+      <c r="AY15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>12</v>
       </c>
-      <c r="AW15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BA15" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BB15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BC15" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BE15" t="n">
         <v>15</v>
       </c>
       <c r="BF15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG15" t="n">
         <v>16.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G16" t="n">
         <v>1.88</v>
       </c>
       <c r="H16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I16" t="n">
         <v>5</v>
@@ -3491,7 +3491,7 @@
         <v>3.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
@@ -3500,7 +3500,7 @@
         <v>3.85</v>
       </c>
       <c r="O16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
         <v>1.95</v>
@@ -3512,16 +3512,16 @@
         <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U16" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W16" t="n">
         <v>2.12</v>
@@ -3533,7 +3533,7 @@
         <v>18</v>
       </c>
       <c r="Z16" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
@@ -3569,34 +3569,34 @@
         <v>24</v>
       </c>
       <c r="AL16" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP16" t="n">
         <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR16" t="n">
         <v>30</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
         <v>16.5</v>
@@ -3620,23 +3620,23 @@
         <v>17</v>
       </c>
       <c r="BC16" t="n">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF16" t="n">
         <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -3679,16 +3679,16 @@
         <v>2.48</v>
       </c>
       <c r="J17" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="K17" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.53</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N17" t="n">
         <v>2.9</v>
@@ -3703,16 +3703,16 @@
         <v>2.42</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T17" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="U17" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="V17" t="n">
         <v>1.68</v>
@@ -3763,7 +3763,7 @@
         <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
@@ -3778,28 +3778,28 @@
         <v>5.1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AR17" t="n">
         <v>5.9</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AW17" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AY17" t="n">
         <v>6.2</v>
@@ -3808,29 +3808,29 @@
         <v>6.6</v>
       </c>
       <c r="BA17" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.55</v>
+        <v>38</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.8</v>
+        <v>2.86</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.05</v>
+        <v>2.58</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G18" t="n">
         <v>3.65</v>
@@ -3870,7 +3870,7 @@
         <v>2.42</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J18" t="n">
         <v>3.1</v>
@@ -3882,40 +3882,40 @@
         <v>1.46</v>
       </c>
       <c r="M18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>1.37</v>
       </c>
       <c r="P18" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="Q18" t="n">
         <v>2.16</v>
       </c>
       <c r="R18" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
         <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U18" t="n">
         <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y18" t="n">
         <v>10.5</v>
@@ -3951,80 +3951,80 @@
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AK18" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP18" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="AQ18" t="n">
         <v>8.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AS18" t="n">
         <v>7.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AU18" t="n">
         <v>6.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB18" t="n">
         <v>8.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF18" t="n">
         <v>8</v>
       </c>
-      <c r="BE18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>36</v>
-      </c>
       <c r="BG18" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G19" t="n">
         <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I19" t="n">
         <v>3.15</v>
@@ -4073,10 +4073,10 @@
         <v>3.05</v>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N19" t="n">
         <v>2.48</v>
@@ -4085,7 +4085,7 @@
         <v>1.63</v>
       </c>
       <c r="P19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q19" t="n">
         <v>3</v>
@@ -4097,13 +4097,13 @@
         <v>6.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="U19" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W19" t="n">
         <v>1.48</v>
@@ -4133,37 +4133,37 @@
         <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG19" t="n">
         <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AJ19" t="n">
         <v>110</v>
       </c>
       <c r="AK19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL19" t="n">
-        <v>190</v>
+        <v>460</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>980</v>
+        <v>600</v>
       </c>
       <c r="AO19" t="n">
         <v>75</v>
       </c>
       <c r="AP19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ19" t="n">
         <v>7.2</v>
@@ -4172,7 +4172,7 @@
         <v>16</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT19" t="n">
         <v>7.2</v>
@@ -4184,19 +4184,19 @@
         <v>12.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.6</v>
+        <v>40</v>
       </c>
       <c r="AX19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ19" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BB19" t="n">
         <v>16</v>
@@ -4205,20 +4205,20 @@
         <v>16</v>
       </c>
       <c r="BD19" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BG19" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -4267,28 +4267,28 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N20" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="O20" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P20" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I21" t="n">
         <v>3.9</v>
@@ -4458,7 +4458,7 @@
         <v>2.88</v>
       </c>
       <c r="K21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L21" t="n">
         <v>1.58</v>
@@ -4467,16 +4467,16 @@
         <v>1.13</v>
       </c>
       <c r="N21" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
         <v>1.51</v>
       </c>
       <c r="P21" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="R21" t="n">
         <v>1.2</v>
@@ -4485,31 +4485,31 @@
         <v>5.1</v>
       </c>
       <c r="T21" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="U21" t="n">
         <v>1.83</v>
       </c>
       <c r="V21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W21" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X21" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y21" t="n">
         <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA21" t="n">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC21" t="n">
         <v>7</v>
@@ -4521,7 +4521,7 @@
         <v>450</v>
       </c>
       <c r="AF21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG21" t="n">
         <v>12.5</v>
@@ -4533,37 +4533,37 @@
         <v>460</v>
       </c>
       <c r="AJ21" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK21" t="n">
         <v>36</v>
       </c>
       <c r="AL21" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AM21" t="n">
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO21" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AP21" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="AT21" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU21" t="n">
         <v>6</v>
@@ -4572,10 +4572,10 @@
         <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.2</v>
+        <v>23</v>
       </c>
       <c r="AX21" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY21" t="n">
         <v>10</v>
@@ -4584,7 +4584,7 @@
         <v>18.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="BB21" t="n">
         <v>14.5</v>
@@ -4593,20 +4593,20 @@
         <v>14.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="G22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="I22" t="n">
         <v>1.39</v>
       </c>
       <c r="J22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L22" t="n">
         <v>1.45</v>
@@ -4664,22 +4664,22 @@
         <v>3.55</v>
       </c>
       <c r="O22" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P22" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R22" t="n">
         <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="T22" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="U22" t="n">
         <v>1.56</v>
@@ -4706,7 +4706,7 @@
         <v>65</v>
       </c>
       <c r="AC22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD22" t="n">
         <v>11.5</v>
@@ -4724,7 +4724,7 @@
         <v>200</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ22" t="n">
         <v>1000</v>
@@ -4745,19 +4745,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AP22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ22" t="n">
         <v>5.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU22" t="n">
         <v>10.5</v>
@@ -4769,38 +4769,38 @@
         <v>16</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY22" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AZ22" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB22" t="n">
         <v>10</v>
       </c>
       <c r="BC22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BD22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG22" t="n">
         <v>7</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="G23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="H23" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K23" t="n">
         <v>4.4</v>
@@ -4858,7 +4858,7 @@
         <v>2.96</v>
       </c>
       <c r="O23" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P23" t="n">
         <v>1.65</v>
@@ -4867,28 +4867,28 @@
         <v>2.42</v>
       </c>
       <c r="R23" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S23" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="U23" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="V23" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="Z23" t="n">
         <v>7.6</v>
@@ -4897,25 +4897,25 @@
         <v>14</v>
       </c>
       <c r="AB23" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="AC23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD23" t="n">
         <v>11.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="n">
-        <v>510</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
         <v>150</v>
@@ -4936,25 +4936,25 @@
         <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AR23" t="n">
         <v>6.2</v>
       </c>
       <c r="AS23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT23" t="n">
         <v>20</v>
       </c>
       <c r="AU23" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV23" t="n">
         <v>9.4</v>
@@ -4963,38 +4963,38 @@
         <v>17.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="AY23" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="AZ23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB23" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC23" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BD23" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE23" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF23" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BG23" t="n">
         <v>10</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>2.42</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H24" t="n">
         <v>3.55</v>
@@ -5043,7 +5043,7 @@
         <v>3.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M24" t="n">
         <v>1.12</v>
@@ -5055,16 +5055,16 @@
         <v>1.52</v>
       </c>
       <c r="P24" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S24" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="T24" t="n">
         <v>2.08</v>
@@ -5076,10 +5076,10 @@
         <v>1.36</v>
       </c>
       <c r="W24" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X24" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y24" t="n">
         <v>10.5</v>
@@ -5127,13 +5127,13 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ24" t="n">
         <v>9</v>
@@ -5163,19 +5163,19 @@
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA24" t="n">
         <v>13.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BC24" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BD24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BE24" t="n">
         <v>15</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="G25" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="H25" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="I25" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K25" t="n">
         <v>4</v>
@@ -5243,7 +5243,7 @@
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
         <v>1.4</v>
@@ -5252,13 +5252,13 @@
         <v>1.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R25" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T25" t="n">
         <v>2.08</v>
@@ -5267,13 +5267,13 @@
         <v>1.83</v>
       </c>
       <c r="V25" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="X25" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y25" t="n">
         <v>20</v>
@@ -5297,7 +5297,7 @@
         <v>480</v>
       </c>
       <c r="AF25" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG25" t="n">
         <v>11</v>
@@ -5321,22 +5321,22 @@
         <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO25" t="n">
         <v>700</v>
       </c>
       <c r="AP25" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT25" t="n">
         <v>6</v>
@@ -5345,13 +5345,13 @@
         <v>7.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
@@ -5360,29 +5360,29 @@
         <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="BB25" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC25" t="n">
         <v>18.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G26" t="n">
         <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="I26" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J26" t="n">
         <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L26" t="n">
         <v>1.5</v>
@@ -5437,40 +5437,40 @@
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O26" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P26" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
         <v>1.87</v>
       </c>
       <c r="V26" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W26" t="n">
         <v>1.27</v>
       </c>
       <c r="X26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Z26" t="n">
         <v>11.5</v>
@@ -5506,10 +5506,10 @@
         <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
@@ -5521,10 +5521,10 @@
         <v>19.5</v>
       </c>
       <c r="AP26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR26" t="n">
         <v>9.6</v>
@@ -5533,16 +5533,16 @@
         <v>20</v>
       </c>
       <c r="AT26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV26" t="n">
         <v>9.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX26" t="n">
         <v>11.5</v>
@@ -5554,29 +5554,29 @@
         <v>18.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC26" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF26" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BG26" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="G27" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H27" t="n">
         <v>6.6</v>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>3.55</v>
       </c>
       <c r="K27" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L27" t="n">
         <v>1.52</v>
@@ -5631,7 +5631,7 @@
         <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O27" t="n">
         <v>1.45</v>
@@ -5655,10 +5655,10 @@
         <v>1.66</v>
       </c>
       <c r="V27" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W27" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -5685,7 +5685,7 @@
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AG27" t="n">
         <v>1000</v>
@@ -5718,59 +5718,59 @@
         <v>3.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.89</v>
+        <v>2.46</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AU27" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="AX27" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AY27" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2.02</v>
+        <v>7.8</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="BB27" t="n">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.93</v>
+        <v>2.46</v>
       </c>
       <c r="BF27" t="n">
-        <v>2.64</v>
+        <v>10.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G28" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H28" t="n">
         <v>3.15</v>
@@ -5813,16 +5813,16 @@
         <v>3.2</v>
       </c>
       <c r="J28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K28" t="n">
         <v>3.5</v>
       </c>
-      <c r="K28" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L28" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
         <v>4.1</v>
@@ -5834,25 +5834,25 @@
         <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R28" t="n">
         <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T28" t="n">
         <v>1.73</v>
       </c>
       <c r="U28" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V28" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W28" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X28" t="n">
         <v>15</v>
@@ -5876,7 +5876,7 @@
         <v>13.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF28" t="n">
         <v>16</v>
@@ -5885,7 +5885,7 @@
         <v>11.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI28" t="n">
         <v>40</v>
@@ -5897,7 +5897,7 @@
         <v>25</v>
       </c>
       <c r="AL28" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM28" t="n">
         <v>70</v>
@@ -5906,7 +5906,7 @@
         <v>19.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP28" t="n">
         <v>14.5</v>
@@ -5918,7 +5918,7 @@
         <v>20</v>
       </c>
       <c r="AS28" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT28" t="n">
         <v>11</v>
@@ -5957,14 +5957,14 @@
         <v>65</v>
       </c>
       <c r="BF28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BG28" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G29" t="n">
         <v>2.38</v>
       </c>
       <c r="H29" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J29" t="n">
         <v>3</v>
@@ -6016,7 +6016,7 @@
         <v>1.61</v>
       </c>
       <c r="M29" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N29" t="n">
         <v>2.6</v>
@@ -6028,7 +6028,7 @@
         <v>1.51</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R29" t="n">
         <v>1.18</v>
@@ -6040,16 +6040,16 @@
         <v>2.14</v>
       </c>
       <c r="U29" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V29" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W29" t="n">
         <v>1.72</v>
       </c>
       <c r="X29" t="n">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="Y29" t="n">
         <v>19</v>
@@ -6076,7 +6076,7 @@
         <v>36</v>
       </c>
       <c r="AG29" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AH29" t="n">
         <v>1000</v>
@@ -6103,16 +6103,16 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AR29" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT29" t="n">
         <v>5.9</v>
@@ -6124,41 +6124,41 @@
         <v>6.2</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX29" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AY29" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD29" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>8</v>
-      </c>
       <c r="BE29" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF29" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG29" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -6189,40 +6189,40 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G30" t="n">
         <v>2.46</v>
       </c>
       <c r="H30" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>2.96</v>
       </c>
       <c r="K30" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L30" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="M30" t="n">
         <v>1.14</v>
       </c>
       <c r="N30" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P30" t="n">
         <v>1.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
@@ -6234,13 +6234,13 @@
         <v>2.02</v>
       </c>
       <c r="U30" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W30" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X30" t="n">
         <v>14</v>
@@ -6261,7 +6261,7 @@
         <v>8.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AE30" t="n">
         <v>500</v>
@@ -6306,7 +6306,7 @@
         <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT30" t="n">
         <v>6.2</v>
@@ -6324,7 +6324,7 @@
         <v>11</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ30" t="n">
         <v>6.8</v>
@@ -6333,26 +6333,26 @@
         <v>8.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC30" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BD30" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BE30" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF30" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -6386,22 +6386,22 @@
         <v>1.6</v>
       </c>
       <c r="G31" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I31" t="n">
         <v>7.8</v>
       </c>
       <c r="J31" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
         <v>4.3</v>
       </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M31" t="n">
         <v>1.08</v>
@@ -6422,7 +6422,7 @@
         <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T31" t="n">
         <v>2.12</v>
@@ -6431,19 +6431,19 @@
         <v>1.79</v>
       </c>
       <c r="V31" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W31" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="X31" t="n">
         <v>15</v>
       </c>
       <c r="Y31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Z31" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AA31" t="n">
         <v>240</v>
@@ -6455,7 +6455,7 @@
         <v>10.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AE31" t="n">
         <v>130</v>
@@ -6485,7 +6485,7 @@
         <v>200</v>
       </c>
       <c r="AN31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
@@ -6500,7 +6500,7 @@
         <v>48</v>
       </c>
       <c r="AS31" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AT31" t="n">
         <v>6.2</v>
@@ -6512,7 +6512,7 @@
         <v>20</v>
       </c>
       <c r="AW31" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX31" t="n">
         <v>7.6</v>
@@ -6524,7 +6524,7 @@
         <v>21</v>
       </c>
       <c r="BA31" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB31" t="n">
         <v>12.5</v>
@@ -6536,17 +6536,17 @@
         <v>34</v>
       </c>
       <c r="BE31" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF31" t="n">
         <v>9.6</v>
       </c>
       <c r="BG31" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH31"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,154 +757,154 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
         <v>2.2</v>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN2" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AO2" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AP2" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>14.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS2" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BB2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD2" t="n">
         <v>38</v>
@@ -913,14 +913,14 @@
         <v>36</v>
       </c>
       <c r="BF2" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="I3" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="J3" t="n">
         <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.51</v>
@@ -975,133 +975,133 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
         <v>4.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="X3" t="n">
         <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AB3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
         <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AG3" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH3" t="n">
         <v>19.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AJ3" t="n">
         <v>500</v>
       </c>
       <c r="AK3" t="n">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="AL3" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AO3" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AP3" t="n">
         <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AT3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY3" t="n">
         <v>13.5</v>
       </c>
-      <c r="AX3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="BB3" t="n">
         <v>23</v>
       </c>
       <c r="BC3" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="BE3" t="n">
         <v>29</v>
@@ -1110,18 +1110,18 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Italian Serie D</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Enna Calcio</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>Club Atletico Palermo</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.36</v>
+        <v>3.05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="H4" t="n">
-        <v>3.45</v>
+        <v>2.34</v>
       </c>
       <c r="I4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N4" t="n">
         <v>3.75</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O4" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="R4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AS4" t="n">
         <v>1.3</v>
       </c>
-      <c r="S4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>23</v>
-      </c>
       <c r="AT4" t="n">
-        <v>8.4</v>
+        <v>1.28</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>1.19</v>
       </c>
       <c r="AV4" t="n">
-        <v>11.5</v>
+        <v>1.26</v>
       </c>
       <c r="AW4" t="n">
-        <v>19.5</v>
+        <v>1.27</v>
       </c>
       <c r="AX4" t="n">
-        <v>12.5</v>
+        <v>1.29</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>1.28</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>1.27</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.6</v>
+        <v>1.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>15</v>
+        <v>1.29</v>
       </c>
       <c r="BC4" t="n">
-        <v>23</v>
+        <v>1.29</v>
       </c>
       <c r="BD4" t="n">
-        <v>20</v>
+        <v>1.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>29</v>
+        <v>1.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>7</v>
+        <v>1.55</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.4</v>
+        <v>1.55</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,186 +1330,186 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NK Aluminij</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.9</v>
+        <v>2.22</v>
       </c>
       <c r="G5" t="n">
-        <v>5.6</v>
+        <v>2.34</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>1.66</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>7.2</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>3.15</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.87</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>2.06</v>
+        <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>2.48</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.22</v>
+        <v>1.76</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AA5" t="n">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="AB5" t="n">
-        <v>34</v>
+        <v>9.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
         <v>19</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO5" t="n">
         <v>60</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>5.9</v>
       </c>
       <c r="AP5" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="AS5" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="AT5" t="n">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="AX5" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="AY5" t="n">
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.1</v>
+        <v>40</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,184 +1519,184 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Giugliano</t>
+          <t>NK Aluminij</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.74</v>
+        <v>4.8</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="H6" t="n">
-        <v>2.96</v>
+        <v>1.62</v>
       </c>
       <c r="I6" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="J6" t="n">
-        <v>2.94</v>
+        <v>4.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>2.66</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="P6" t="n">
-        <v>1.53</v>
+        <v>3.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.64</v>
+        <v>1.42</v>
       </c>
       <c r="R6" t="n">
-        <v>1.19</v>
+        <v>1.85</v>
       </c>
       <c r="S6" t="n">
-        <v>5.3</v>
+        <v>2.06</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>1.54</v>
       </c>
       <c r="U6" t="n">
-        <v>1.76</v>
+        <v>2.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>2.48</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="Y6" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>18</v>
       </c>
       <c r="AB6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV6" t="n">
         <v>9.6</v>
       </c>
-      <c r="AC6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR6" t="n">
+      <c r="AW6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF6" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AS6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT6" t="n">
+      <c r="BG6" t="n">
         <v>4.9</v>
       </c>
-      <c r="AU6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>8</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
@@ -1718,179 +1718,179 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>US Latina Calcio</t>
+          <t>S.S.D. Casarano Calcio</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.56</v>
+        <v>3.55</v>
       </c>
       <c r="O7" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.52</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.68</v>
+        <v>2.04</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
         <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF7" t="n">
         <v>17</v>
       </c>
-      <c r="Y7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BG7" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>S.S.D. Casarano Calcio</t>
+          <t>US Latina Calcio</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="H8" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K8" t="n">
         <v>3.3</v>
       </c>
-      <c r="K8" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.02</v>
+        <v>2.72</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.76</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
       </c>
       <c r="AB8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY8" t="n">
         <v>10</v>
       </c>
-      <c r="AC8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="BC8" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.6</v>
+        <v>12</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Estonian Esiliiga</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,113 +2106,113 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JK Welco Elekter</t>
+          <t>FC Giugliano</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.14</v>
+        <v>2.78</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>2.18</v>
+        <v>2.94</v>
       </c>
       <c r="I9" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>13.5</v>
+        <v>3.25</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="O9" t="n">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.09</v>
+        <v>2.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.47</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>400</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
         <v>500</v>
       </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
@@ -2220,72 +2220,72 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.36</v>
+        <v>4.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.34</v>
+        <v>5.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.35</v>
+        <v>9</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.34</v>
+        <v>5</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.33</v>
+        <v>5.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.35</v>
+        <v>8.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.34</v>
+        <v>8</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.35</v>
+        <v>7.8</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.35</v>
+        <v>7.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.36</v>
+        <v>11.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.35</v>
+        <v>8.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.35</v>
+        <v>8.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.37</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Estonian Esiliiga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AZ Picerno ASD</t>
+          <t>JK Welco Elekter</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atalanta B</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.76</v>
+        <v>2.14</v>
       </c>
       <c r="G10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P10" t="n">
         <v>3.1</v>
       </c>
-      <c r="H10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.81</v>
-      </c>
       <c r="Q10" t="n">
-        <v>2.06</v>
+        <v>1.33</v>
       </c>
       <c r="R10" t="n">
-        <v>1.31</v>
+        <v>1.92</v>
       </c>
       <c r="S10" t="n">
-        <v>3.75</v>
+        <v>1.76</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="U10" t="n">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>13.5</v>
+        <v>500</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
         <v>55</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>34</v>
-      </c>
       <c r="AO10" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AP10" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>15.5</v>
+        <v>5.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>16</v>
+        <v>4.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.4</v>
+        <v>4.9</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>15</v>
+        <v>5.1</v>
       </c>
       <c r="AX10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AY10" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14.5</v>
+        <v>5.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="BB10" t="n">
-        <v>38</v>
+        <v>5.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>16</v>
+        <v>4.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>40</v>
+        <v>4.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,184 +2489,184 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>AZ Picerno ASD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Atalanta B</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="G11" t="n">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="H11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.2</v>
       </c>
-      <c r="I11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K11" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="U11" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W11" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="n">
         <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>46</v>
       </c>
       <c r="AB11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT11" t="n">
         <v>9.4</v>
       </c>
-      <c r="AC11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AU11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC11" t="n">
         <v>16.5</v>
       </c>
-      <c r="AE11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL11" t="n">
+      <c r="BD11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE11" t="n">
         <v>55</v>
       </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BF11" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU12" t="n">
         <v>6.6</v>
       </c>
-      <c r="G12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V12" t="n">
-        <v>3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X12" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y12" t="n">
+      <c r="AV12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG12" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cavese 1919</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.84</v>
+        <v>7.2</v>
       </c>
       <c r="G13" t="n">
-        <v>1.94</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="J13" t="n">
         <v>5.1</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N13" t="n">
         <v>6</v>
       </c>
-      <c r="J13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.98</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="P13" t="n">
-        <v>1.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.36</v>
+        <v>1.57</v>
       </c>
       <c r="R13" t="n">
-        <v>1.23</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
-        <v>4.7</v>
+        <v>2.46</v>
       </c>
       <c r="T13" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="W13" t="n">
-        <v>2.06</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y13" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AD13" t="n">
-        <v>46</v>
+        <v>10.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AF13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>240</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS13" t="n">
         <v>12</v>
       </c>
-      <c r="AG13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>5</v>
-      </c>
       <c r="AT13" t="n">
-        <v>4.2</v>
+        <v>27</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AV13" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.4</v>
+        <v>12.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="AY13" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.2</v>
+        <v>24</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BC13" t="n">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="BF13" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FC Basel</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grasshoppers Zurich</t>
+          <t>Cavese 1919</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="G14" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="M14" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.21</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.56</v>
-      </c>
       <c r="S14" t="n">
-        <v>2.68</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.68</v>
+        <v>2.26</v>
       </c>
       <c r="U14" t="n">
-        <v>2.34</v>
+        <v>1.69</v>
       </c>
       <c r="V14" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="X14" t="n">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="Y14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
         <v>12</v>
       </c>
       <c r="AC14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC14" t="n">
         <v>10</v>
       </c>
-      <c r="AD14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BD14" t="n">
-        <v>16</v>
+        <v>6.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>36</v>
+        <v>2.78</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>38</v>
+        <v>2.78</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>FC Basel</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St Gallen</t>
+          <t>Grasshoppers Zurich</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.34</v>
+        <v>1.69</v>
       </c>
       <c r="G15" t="n">
-        <v>2.38</v>
+        <v>1.71</v>
       </c>
       <c r="H15" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="P15" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="S15" t="n">
-        <v>2.46</v>
+        <v>2.76</v>
       </c>
       <c r="T15" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>2.76</v>
+        <v>2.32</v>
       </c>
       <c r="V15" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="W15" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="X15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Z15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA15" t="n">
         <v>27</v>
       </c>
-      <c r="AA15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="BB15" t="n">
         <v>16</v>
       </c>
-      <c r="AC15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="BC15" t="n">
         <v>14.5</v>
       </c>
-      <c r="AE15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS15" t="n">
+      <c r="BD15" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG15" t="n">
         <v>44</v>
       </c>
-      <c r="AT15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>15</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,25 +3464,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>St Gallen</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="H16" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="J16" t="n">
         <v>3.8</v>
@@ -3491,159 +3491,159 @@
         <v>3.9</v>
       </c>
       <c r="L16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.41</v>
       </c>
-      <c r="M16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="W16" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Y16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="AC16" t="n">
         <v>9.4</v>
       </c>
       <c r="AD16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP16" t="n">
         <v>21</v>
       </c>
-      <c r="AE16" t="n">
-        <v>320</v>
-      </c>
-      <c r="AF16" t="n">
+      <c r="AQ16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV16" t="n">
         <v>13</v>
       </c>
-      <c r="AG16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK16" t="n">
+      <c r="AW16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD16" t="n">
         <v>24</v>
       </c>
-      <c r="AL16" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW16" t="n">
+      <c r="BE16" t="n">
         <v>23</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BF16" t="n">
         <v>10</v>
       </c>
-      <c r="AY16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>11</v>
-      </c>
       <c r="BG16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.6</v>
+        <v>1.88</v>
       </c>
       <c r="G17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N17" t="n">
         <v>4.1</v>
       </c>
-      <c r="H17" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.9</v>
-      </c>
       <c r="O17" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="P17" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.42</v>
+        <v>1.91</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="T17" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="U17" t="n">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="V17" t="n">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="W17" t="n">
-        <v>1.32</v>
+        <v>2.08</v>
       </c>
       <c r="X17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>330</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH17" t="n">
         <v>19</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AI17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP17" t="n">
         <v>14</v>
       </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.9</v>
+        <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="AT17" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="AX17" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.6</v>
+        <v>25</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.64</v>
+        <v>17.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.6</v>
+        <v>29</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.86</v>
+        <v>28</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.58</v>
+        <v>10.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.4</v>
+        <v>26</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="G18" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="H18" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="I18" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L18" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="O18" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="P18" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="S18" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="T18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.83</v>
       </c>
-      <c r="U18" t="n">
-        <v>2.06</v>
-      </c>
       <c r="V18" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="W18" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.5</v>
+        <v>500</v>
       </c>
       <c r="AA18" t="n">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AC18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>380</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY18" t="n">
         <v>7.6</v>
       </c>
-      <c r="AD18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>170</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE18" t="n">
         <v>8.4</v>
       </c>
-      <c r="AR18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX18" t="n">
+      <c r="BF18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG18" t="n">
         <v>6.8</v>
       </c>
-      <c r="AY18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>7</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="G19" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="H19" t="n">
-        <v>2.98</v>
+        <v>2.42</v>
       </c>
       <c r="I19" t="n">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="J19" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>2.48</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
-        <v>1.63</v>
+        <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="R19" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU19" t="n">
         <v>6.4</v>
       </c>
-      <c r="T19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X19" t="n">
+      <c r="AV19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF19" t="n">
         <v>7.8</v>
       </c>
-      <c r="Y19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>460</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>42</v>
-      </c>
       <c r="BG19" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="M20" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="N20" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O20" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="P20" t="n">
         <v>1.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="M21" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="O21" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="P21" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="S21" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>2.4</v>
       </c>
       <c r="G22" t="n">
-        <v>14</v>
+        <v>2.6</v>
       </c>
       <c r="H22" t="n">
-        <v>1.37</v>
+        <v>3.5</v>
       </c>
       <c r="I22" t="n">
-        <v>1.39</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>4.8</v>
+        <v>2.86</v>
       </c>
       <c r="K22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S22" t="n">
         <v>5.4</v>
       </c>
-      <c r="L22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.85</v>
-      </c>
       <c r="T22" t="n">
-        <v>2.56</v>
+        <v>2.06</v>
       </c>
       <c r="U22" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="V22" t="n">
-        <v>3.55</v>
+        <v>1.33</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.63</v>
       </c>
       <c r="X22" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="AA22" t="n">
-        <v>11</v>
+        <v>190</v>
       </c>
       <c r="AB22" t="n">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="AC22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>450</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG22" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>120</v>
-      </c>
       <c r="AH22" t="n">
-        <v>200</v>
+        <v>24</v>
       </c>
       <c r="AI22" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO22" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR22" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="AS22" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AT22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW22" t="n">
         <v>23</v>
       </c>
-      <c r="AU22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>16</v>
-      </c>
       <c r="AX22" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="BA22" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG22" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BB22" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>7</v>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
@@ -4822,103 +4822,103 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="G23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="I23" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="J23" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="K23" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>2.96</v>
+        <v>3.55</v>
       </c>
       <c r="O23" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="P23" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="T23" t="n">
         <v>2.52</v>
       </c>
       <c r="U23" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="V23" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA23" t="n">
         <v>11</v>
       </c>
-      <c r="Y23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>14</v>
-      </c>
       <c r="AB23" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AC23" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD23" t="n">
         <v>11.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AF23" t="n">
         <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI23" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AJ23" t="n">
         <v>1000</v>
@@ -4936,65 +4936,65 @@
         <v>1000</v>
       </c>
       <c r="AO23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AP23" t="n">
         <v>12</v>
       </c>
-      <c r="AP23" t="n">
+      <c r="AQ23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV23" t="n">
         <v>9.6</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT23" t="n">
+      <c r="AW23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>20</v>
       </c>
-      <c r="AU23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BA23" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BB23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC23" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD23" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE23" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF23" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG23" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2.42</v>
       </c>
-      <c r="G24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="R24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="W24" t="n">
         <v>1.12</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.66</v>
-      </c>
       <c r="X24" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>44</v>
+        <v>7.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>900</v>
+        <v>14</v>
       </c>
       <c r="AB24" t="n">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
-        <v>150</v>
+        <v>22</v>
       </c>
       <c r="AF24" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
+        <v>95</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS24" t="n">
         <v>12</v>
       </c>
-      <c r="AH24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR24" t="n">
+      <c r="AT24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>20</v>
       </c>
-      <c r="AS24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>13</v>
-      </c>
       <c r="BA24" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="BB24" t="n">
         <v>11</v>
       </c>
       <c r="BC24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BE24" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF24" t="n">
         <v>15</v>
       </c>
-      <c r="BF24" t="n">
-        <v>11</v>
-      </c>
       <c r="BG24" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,55 +5210,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trapani</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>1.87</v>
+        <v>2.52</v>
       </c>
       <c r="H25" t="n">
-        <v>5.2</v>
+        <v>3.55</v>
       </c>
       <c r="I25" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="O25" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="P25" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="T25" t="n">
         <v>2.08</v>
@@ -5267,129 +5267,129 @@
         <v>1.83</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>2.12</v>
+        <v>1.66</v>
       </c>
       <c r="X25" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="Y25" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>250</v>
+        <v>44</v>
       </c>
       <c r="AA25" t="n">
         <v>900</v>
       </c>
       <c r="AB25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC25" t="n">
         <v>7.2</v>
       </c>
-      <c r="AC25" t="n">
-        <v>10</v>
-      </c>
       <c r="AD25" t="n">
-        <v>29</v>
+        <v>16.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="AF25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR25" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>290</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>34</v>
-      </c>
       <c r="AS25" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AW25" t="n">
-        <v>30</v>
+        <v>10.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BA25" t="n">
-        <v>38</v>
+        <v>11.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BC25" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="BD25" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.8</v>
+        <v>46</v>
       </c>
       <c r="BF25" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,184 +5399,184 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Quindio</t>
+          <t>Trapani</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4.5</v>
+        <v>1.74</v>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>1.83</v>
       </c>
       <c r="H26" t="n">
-        <v>1.96</v>
+        <v>5.6</v>
       </c>
       <c r="I26" t="n">
-        <v>2.04</v>
+        <v>6.8</v>
       </c>
       <c r="J26" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K26" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="P26" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U26" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="V26" t="n">
-        <v>1.96</v>
+        <v>1.18</v>
       </c>
       <c r="W26" t="n">
-        <v>1.27</v>
+        <v>2.18</v>
       </c>
       <c r="X26" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB26" t="n">
         <v>7.6</v>
       </c>
-      <c r="Z26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AR26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW26" t="n">
         <v>8</v>
       </c>
-      <c r="AD26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>85</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>460</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>20</v>
-      </c>
       <c r="AX26" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY26" t="n">
-        <v>16.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA26" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BB26" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BE26" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG26" t="n">
-        <v>16.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
@@ -5598,31 +5598,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.68</v>
+        <v>4.5</v>
       </c>
       <c r="G27" t="n">
-        <v>1.71</v>
+        <v>5.2</v>
       </c>
       <c r="H27" t="n">
-        <v>6.6</v>
+        <v>1.97</v>
       </c>
       <c r="I27" t="n">
-        <v>8.199999999999999</v>
+        <v>2.08</v>
       </c>
       <c r="J27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.55</v>
-      </c>
-      <c r="K27" t="n">
-        <v>4.1</v>
       </c>
       <c r="L27" t="n">
         <v>1.52</v>
@@ -5631,76 +5631,76 @@
         <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O27" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P27" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R27" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S27" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T27" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="U27" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="V27" t="n">
-        <v>1.14</v>
+        <v>1.92</v>
       </c>
       <c r="W27" t="n">
-        <v>2.38</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB27" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="AC27" t="n">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF27" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ27" t="n">
         <v>900</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AL27" t="n">
         <v>1000</v>
@@ -5709,75 +5709,75 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP27" t="n">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2.34</v>
+        <v>6.2</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.14</v>
+        <v>9.4</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.46</v>
+        <v>20</v>
       </c>
       <c r="AT27" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AU27" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.46</v>
+        <v>21</v>
       </c>
       <c r="AX27" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>2.94</v>
+        <v>17</v>
       </c>
       <c r="AZ27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA27" t="n">
         <v>7.8</v>
       </c>
-      <c r="BA27" t="n">
-        <v>2.46</v>
-      </c>
       <c r="BB27" t="n">
-        <v>2.86</v>
+        <v>8.6</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD27" t="n">
-        <v>2.08</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.46</v>
+        <v>8.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>2.1</v>
+        <v>18.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,186 +5792,186 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.54</v>
+        <v>1.57</v>
       </c>
       <c r="G28" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W28" t="n">
         <v>2.56</v>
       </c>
-      <c r="H28" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.64</v>
-      </c>
       <c r="X28" t="n">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="Y28" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
         <v>11.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="AH28" t="n">
-        <v>15.5</v>
+        <v>500</v>
       </c>
       <c r="AI28" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AK28" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AL28" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>19.5</v>
+        <v>55</v>
       </c>
       <c r="AO28" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>14.5</v>
+        <v>5.3</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="AR28" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="AS28" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV28" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AW28" t="n">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX28" t="n">
-        <v>15.5</v>
+        <v>4.8</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="AZ28" t="n">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="BA28" t="n">
-        <v>38</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB28" t="n">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="BC28" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="BD28" t="n">
-        <v>32</v>
+        <v>3.95</v>
       </c>
       <c r="BE28" t="n">
-        <v>65</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF28" t="n">
-        <v>18</v>
+        <v>5.9</v>
       </c>
       <c r="BG28" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarc</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Internacional de Palmir</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="G29" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="H29" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="I29" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="K29" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="M29" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="P29" t="n">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.72</v>
+        <v>1.97</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="U29" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="V29" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="W29" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="X29" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB29" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL29" t="n">
         <v>36</v>
       </c>
-      <c r="AG29" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>220</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>280</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1000</v>
-      </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP29" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AR29" t="n">
-        <v>7.2</v>
+        <v>19.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.800000000000001</v>
+        <v>48</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="AX29" t="n">
-        <v>5.8</v>
+        <v>15.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="AZ29" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="BB29" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BC29" t="n">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="BD29" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BE29" t="n">
-        <v>9.199999999999999</v>
+        <v>65</v>
       </c>
       <c r="BF29" t="n">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,135 +6175,135 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Real Soacha Cundinamarc</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Internacional de Palmir</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G30" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="H30" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="J30" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K30" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L30" t="n">
         <v>1.61</v>
       </c>
       <c r="M30" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O30" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="P30" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="T30" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U30" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="V30" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W30" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="X30" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y30" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AA30" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
         <v>7.4</v>
       </c>
       <c r="AC30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>280</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>460</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>980</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AQ30" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR30" t="n">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="AS30" t="n">
         <v>8.4</v>
@@ -6315,44 +6315,44 @@
         <v>6</v>
       </c>
       <c r="AV30" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ30" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA30" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB30" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BC30" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG30" t="n">
         <v>8.4</v>
       </c>
-      <c r="BD30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>
@@ -6369,184 +6369,378 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>22:20:00</t>
+          <t>20:10:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="F31" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O31" t="n">
         <v>1.6</v>
       </c>
-      <c r="G31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H31" t="n">
+      <c r="P31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP31" t="n">
         <v>7.2</v>
       </c>
-      <c r="I31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J31" t="n">
-        <v>4</v>
-      </c>
-      <c r="K31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X31" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>240</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="AQ31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS31" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>8</v>
       </c>
       <c r="AT31" t="n">
         <v>6.2</v>
       </c>
       <c r="AU31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW31" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AV31" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AX31" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BA31" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB31" t="n">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="BC31" t="n">
-        <v>16.5</v>
+        <v>7.4</v>
       </c>
       <c r="BD31" t="n">
-        <v>34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE31" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF31" t="n">
         <v>9.6</v>
       </c>
       <c r="BG31" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-05 05:05:01</t>
+          <t>2026-03-05 07:22:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>22:20:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquilla</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Alianza FC Valledupar</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X32" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:22:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:15:00</t>
+          <t>08:16:06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.78</v>
+        <v>1.08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.83</v>
+        <v>1.09</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1</v>
+        <v>110</v>
       </c>
       <c r="I2" t="n">
-        <v>5.4</v>
+        <v>170</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>15.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T2" t="n">
         <v>4.2</v>
       </c>
-      <c r="T2" t="n">
-        <v>2.02</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>2.2</v>
+        <v>12</v>
       </c>
       <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY2" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AZ2" t="n">
+        <v>80</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>140</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE2" t="n">
         <v>24</v>
       </c>
-      <c r="AI2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>36</v>
-      </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BG2" t="n">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="H3" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P3" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V3" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="X3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD3" t="n">
         <v>11</v>
       </c>
-      <c r="Y3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AE3" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AF3" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AG3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AK3" t="n">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>380</v>
+        <v>75</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN3" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AO3" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>7.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS3" t="n">
         <v>25</v>
       </c>
       <c r="AT3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
         <v>10</v>
       </c>
       <c r="AW3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX3" t="n">
         <v>24</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AY3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>44</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>55</v>
+      </c>
+      <c r="BG3" t="n">
         <v>21</v>
       </c>
-      <c r="AY3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>29</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -1145,40 +1145,40 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="G4" t="n">
         <v>3.3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I4" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>1.43</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R4" t="n">
         <v>1.35</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -1339,121 +1339,121 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="H5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S5" t="n">
         <v>3.7</v>
       </c>
-      <c r="I5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.9</v>
-      </c>
       <c r="T5" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA5" t="n">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC5" t="n">
         <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN5" t="n">
         <v>19</v>
       </c>
-      <c r="AI5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>21</v>
-      </c>
       <c r="AO5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS5" t="n">
         <v>38</v>
@@ -1462,47 +1462,47 @@
         <v>8.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
         <v>13.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AX5" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
         <v>23</v>
       </c>
       <c r="BB5" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC5" t="n">
         <v>20</v>
       </c>
-      <c r="BC5" t="n">
-        <v>22</v>
-      </c>
       <c r="BD5" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BE5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BF5" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>40</v>
+        <v>11.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>4.8</v>
       </c>
       <c r="G6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="I6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="J6" t="n">
         <v>4.7</v>
@@ -1557,46 +1557,46 @@
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P6" t="n">
         <v>3.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R6" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="S6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T6" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="V6" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="W6" t="n">
         <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Y6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AA6" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="AB6" t="n">
         <v>80</v>
@@ -1617,7 +1617,7 @@
         <v>48</v>
       </c>
       <c r="AH6" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
         <v>65</v>
@@ -1626,7 +1626,7 @@
         <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1638,65 +1638,65 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AP6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT6" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>14</v>
       </c>
       <c r="AU6" t="n">
         <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BB6" t="n">
         <v>11</v>
       </c>
       <c r="BC6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BD6" t="n">
         <v>9.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG6" t="n">
         <v>4.9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
         <v>3.6</v>
@@ -1751,13 +1751,13 @@
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q7" t="n">
         <v>2.04</v>
@@ -1766,19 +1766,19 @@
         <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="U7" t="n">
         <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X7" t="n">
         <v>14</v>
@@ -1790,25 +1790,25 @@
         <v>27</v>
       </c>
       <c r="AA7" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AB7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AF7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
         <v>18.5</v>
@@ -1817,19 +1817,19 @@
         <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AL7" t="n">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO7" t="n">
         <v>980</v>
@@ -1841,56 +1841,56 @@
         <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="AT7" t="n">
         <v>8.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="AX7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7" t="n">
         <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="BB7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC7" t="n">
         <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BG7" t="n">
         <v>36</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G8" t="n">
         <v>2.34</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.46</v>
-      </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
         <v>1.59</v>
@@ -1954,7 +1954,7 @@
         <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
@@ -1963,16 +1963,16 @@
         <v>5.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
         <v>1.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="X8" t="n">
         <v>9</v>
@@ -1984,25 +1984,25 @@
         <v>44</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC8" t="n">
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="AH8" t="n">
         <v>60</v>
@@ -2011,49 +2011,49 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="AK8" t="n">
         <v>80</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY8" t="n">
         <v>10</v>
@@ -2062,7 +2062,7 @@
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB8" t="n">
         <v>15</v>
@@ -2071,20 +2071,20 @@
         <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="BE8" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -2118,28 +2118,28 @@
         <v>2.78</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="H9" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L9" t="n">
         <v>1.58</v>
       </c>
       <c r="M9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O9" t="n">
         <v>1.55</v>
@@ -2148,43 +2148,43 @@
         <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X9" t="n">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z9" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AD9" t="n">
         <v>28</v>
@@ -2193,7 +2193,7 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG9" t="n">
         <v>27</v>
@@ -2208,77 +2208,77 @@
         <v>400</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AL9" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AO9" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AR9" t="n">
         <v>9</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AX9" t="n">
         <v>7.8</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
         <v>11.5</v>
       </c>
       <c r="BA9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF9" t="n">
         <v>8.6</v>
       </c>
-      <c r="BB9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G10" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="H10" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="I10" t="n">
         <v>3.3</v>
@@ -2327,41 +2327,41 @@
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>3.85</v>
+        <v>7.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="R10" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="S10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.76</v>
       </c>
-      <c r="T10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.68</v>
-      </c>
       <c r="X10" t="n">
         <v>1000</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
@@ -2390,7 +2390,7 @@
         <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
         <v>1000</v>
@@ -2408,71 +2408,71 @@
         <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
         <v>55</v>
       </c>
       <c r="AO10" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AU10" t="n">
         <v>5.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.2</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
         <v>5.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -2506,16 +2506,16 @@
         <v>2.76</v>
       </c>
       <c r="G11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H11" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I11" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
         <v>3.55</v>
@@ -2527,13 +2527,13 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
         <v>2.08</v>
@@ -2542,31 +2542,31 @@
         <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X11" t="n">
         <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AB11" t="n">
         <v>11.5</v>
@@ -2587,22 +2587,22 @@
         <v>13.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI11" t="n">
         <v>50</v>
       </c>
       <c r="AJ11" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AK11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL11" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
         <v>34</v>
@@ -2614,13 +2614,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="AT11" t="n">
         <v>9.4</v>
@@ -2632,7 +2632,7 @@
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AX11" t="n">
         <v>16</v>
@@ -2641,32 +2641,32 @@
         <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BB11" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BC11" t="n">
-        <v>16.5</v>
+        <v>9.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="G12" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="H12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.3</v>
       </c>
-      <c r="I12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="O12" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Y12" t="n">
         <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA12" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AC12" t="n">
         <v>7.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF12" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
         <v>32</v>
       </c>
       <c r="AL12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AN12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO12" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AX12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BF12" t="n">
         <v>17.5</v>
       </c>
-      <c r="BA12" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>13</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG12" t="n">
-        <v>11.5</v>
+        <v>48</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -2894,19 +2894,19 @@
         <v>7.2</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H13" t="n">
         <v>1.46</v>
       </c>
       <c r="I13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="J13" t="n">
         <v>5.1</v>
       </c>
       <c r="K13" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L13" t="n">
         <v>1.29</v>
@@ -2933,7 +2933,7 @@
         <v>2.46</v>
       </c>
       <c r="T13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U13" t="n">
         <v>2.16</v>
@@ -2969,7 +2969,7 @@
         <v>14</v>
       </c>
       <c r="AF13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG13" t="n">
         <v>28</v>
@@ -2981,7 +2981,7 @@
         <v>28</v>
       </c>
       <c r="AJ13" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="AK13" t="n">
         <v>90</v>
@@ -2999,7 +2999,7 @@
         <v>5.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AQ13" t="n">
         <v>10</v>
@@ -3011,7 +3011,7 @@
         <v>12</v>
       </c>
       <c r="AT13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU13" t="n">
         <v>11</v>
@@ -3023,38 +3023,38 @@
         <v>12.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AY13" t="n">
         <v>24</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
         <v>24</v>
       </c>
       <c r="BB13" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="BD13" t="n">
         <v>30</v>
       </c>
       <c r="BE13" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BF13" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="BG13" t="n">
         <v>5.1</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>1.76</v>
       </c>
       <c r="G14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H14" t="n">
         <v>5.6</v>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
         <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
         <v>1.56</v>
@@ -3130,7 +3130,7 @@
         <v>2.26</v>
       </c>
       <c r="U14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V14" t="n">
         <v>1.18</v>
@@ -3139,7 +3139,7 @@
         <v>2.16</v>
       </c>
       <c r="X14" t="n">
-        <v>90</v>
+        <v>15.5</v>
       </c>
       <c r="Y14" t="n">
         <v>1000</v>
@@ -3151,37 +3151,37 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
         <v>22</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>25</v>
       </c>
       <c r="AG14" t="n">
         <v>23</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="AK14" t="n">
         <v>80</v>
       </c>
       <c r="AL14" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ14" t="n">
         <v>8.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="AS14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>13</v>
       </c>
-      <c r="AT14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BA14" t="n">
-        <v>2.76</v>
+        <v>12</v>
       </c>
       <c r="BB14" t="n">
         <v>9</v>
       </c>
       <c r="BC14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="BF14" t="n">
         <v>3.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I15" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J15" t="n">
         <v>4.2</v>
@@ -3312,52 +3312,52 @@
         <v>2.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R15" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S15" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="T15" t="n">
         <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X15" t="n">
         <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z15" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AA15" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB15" t="n">
         <v>11</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG15" t="n">
         <v>9.800000000000001</v>
@@ -3369,7 +3369,7 @@
         <v>60</v>
       </c>
       <c r="AJ15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK15" t="n">
         <v>16</v>
@@ -3381,10 +3381,10 @@
         <v>80</v>
       </c>
       <c r="AN15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AO15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP15" t="n">
         <v>21</v>
@@ -3393,10 +3393,10 @@
         <v>21</v>
       </c>
       <c r="AR15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS15" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AT15" t="n">
         <v>10</v>
@@ -3405,19 +3405,19 @@
         <v>9</v>
       </c>
       <c r="AV15" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AX15" t="n">
         <v>10.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA15" t="n">
         <v>27</v>
@@ -3429,20 +3429,20 @@
         <v>14.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE15" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -3473,76 +3473,76 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G16" t="n">
         <v>2.24</v>
       </c>
-      <c r="G16" t="n">
-        <v>2.28</v>
-      </c>
       <c r="H16" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P16" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="S16" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="T16" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="U16" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA16" t="n">
         <v>60</v>
       </c>
       <c r="AB16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
         <v>14.5</v>
@@ -3557,86 +3557,86 @@
         <v>11.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL16" t="n">
         <v>27</v>
       </c>
       <c r="AM16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN16" t="n">
         <v>11</v>
       </c>
       <c r="AO16" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS16" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AT16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV16" t="n">
         <v>13.5</v>
       </c>
-      <c r="AU16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>13</v>
-      </c>
       <c r="AW16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX16" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY16" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA16" t="n">
         <v>30</v>
       </c>
       <c r="BB16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG16" t="n">
         <v>18</v>
       </c>
-      <c r="BD16" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>23</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>19</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G17" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H17" t="n">
         <v>4.6</v>
@@ -3682,7 +3682,7 @@
         <v>3.85</v>
       </c>
       <c r="K17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>1.4</v>
@@ -3691,70 +3691,70 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
         <v>1.8</v>
       </c>
       <c r="U17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X17" t="n">
         <v>15.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA17" t="n">
-        <v>330</v>
+        <v>110</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
         <v>18</v>
       </c>
       <c r="AE17" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AF17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG17" t="n">
         <v>9.6</v>
       </c>
       <c r="AH17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ17" t="n">
         <v>21</v>
@@ -3766,37 +3766,37 @@
         <v>34</v>
       </c>
       <c r="AM17" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO17" t="n">
         <v>60</v>
       </c>
       <c r="AP17" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU17" t="n">
         <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AX17" t="n">
         <v>10.5</v>
@@ -3805,32 +3805,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BB17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC17" t="n">
         <v>17.5</v>
       </c>
-      <c r="BC17" t="n">
-        <v>17</v>
-      </c>
       <c r="BD17" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE17" t="n">
         <v>29</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BF17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG17" t="n">
         <v>28</v>
       </c>
-      <c r="BF17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>26</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="G18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H18" t="n">
         <v>2.26</v>
       </c>
       <c r="I18" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L18" t="n">
         <v>1.52</v>
@@ -3909,43 +3909,43 @@
         <v>1.83</v>
       </c>
       <c r="V18" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W18" t="n">
         <v>1.33</v>
       </c>
       <c r="X18" t="n">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AA18" t="n">
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AH18" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
@@ -3969,31 +3969,31 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.4</v>
+        <v>5.9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AS18" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AU18" t="n">
         <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
         <v>7.6</v>
@@ -4002,7 +4002,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB18" t="n">
         <v>8</v>
@@ -4017,14 +4017,14 @@
         <v>8.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.75</v>
+        <v>8</v>
       </c>
       <c r="BG18" t="n">
         <v>6.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -4055,19 +4055,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G19" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H19" t="n">
         <v>2.42</v>
       </c>
       <c r="I19" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K19" t="n">
         <v>3.35</v>
@@ -4082,76 +4082,76 @@
         <v>3.35</v>
       </c>
       <c r="O19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q19" t="n">
         <v>2.16</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T19" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U19" t="n">
         <v>2.04</v>
       </c>
       <c r="V19" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X19" t="n">
         <v>12</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AB19" t="n">
         <v>13</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD19" t="n">
         <v>12.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AF19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG19" t="n">
         <v>16</v>
       </c>
       <c r="AH19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ19" t="n">
         <v>220</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
@@ -4163,62 +4163,62 @@
         <v>27</v>
       </c>
       <c r="AP19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
         <v>12.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT19" t="n">
         <v>10.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV19" t="n">
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX19" t="n">
         <v>20</v>
       </c>
       <c r="AY19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BC19" t="n">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="BD19" t="n">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF19" t="n">
         <v>8.6</v>
       </c>
-      <c r="BF19" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BG19" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -4249,170 +4249,170 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J20" t="n">
         <v>2.92</v>
       </c>
-      <c r="G20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2.84</v>
       </c>
-      <c r="K20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="V20" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="X20" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AA20" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI20" t="n">
         <v>90</v>
       </c>
       <c r="AJ20" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK20" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AL20" t="n">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AO20" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR20" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS20" t="n">
         <v>23</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU20" t="n">
         <v>6.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA20" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="BC20" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="BG20" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -4461,28 +4461,28 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M21" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="N21" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="P21" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="R21" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="G22" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="H22" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J22" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="K22" t="n">
         <v>3.2</v>
@@ -4661,85 +4661,85 @@
         <v>1.13</v>
       </c>
       <c r="N22" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P22" t="n">
         <v>1.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R22" t="n">
         <v>1.19</v>
       </c>
       <c r="S22" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T22" t="n">
         <v>2.06</v>
       </c>
       <c r="U22" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V22" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W22" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="X22" t="n">
         <v>9</v>
       </c>
       <c r="Y22" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AA22" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AB22" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC22" t="n">
         <v>7.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AE22" t="n">
-        <v>450</v>
+        <v>160</v>
       </c>
       <c r="AF22" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH22" t="n">
         <v>24</v>
       </c>
       <c r="AI22" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AJ22" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AK22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
         <v>36</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>42</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
@@ -4748,59 +4748,59 @@
         <v>7.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR22" t="n">
         <v>21</v>
       </c>
       <c r="AS22" t="n">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU22" t="n">
         <v>6</v>
       </c>
       <c r="AV22" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW22" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AX22" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
         <v>19</v>
       </c>
       <c r="BA22" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="BB22" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BC22" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BD22" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BE22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG22" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="J23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L23" t="n">
         <v>1.45</v>
@@ -4861,28 +4861,28 @@
         <v>1.36</v>
       </c>
       <c r="P23" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T23" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="U23" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V23" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
         <v>15</v>
@@ -4891,22 +4891,22 @@
         <v>6.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AA23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AC23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF23" t="n">
         <v>1000</v>
@@ -4936,65 +4936,65 @@
         <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AP23" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR23" t="n">
         <v>6</v>
       </c>
       <c r="AS23" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="AU23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW23" t="n">
         <v>15.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AZ23" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BA23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE23" t="n">
         <v>28</v>
       </c>
-      <c r="BB23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BF23" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -5028,16 +5028,16 @@
         <v>8.6</v>
       </c>
       <c r="G24" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="H24" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="I24" t="n">
         <v>1.58</v>
       </c>
       <c r="J24" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K24" t="n">
         <v>4.1</v>
@@ -5046,31 +5046,31 @@
         <v>1.53</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N24" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P24" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S24" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T24" t="n">
         <v>2.46</v>
       </c>
       <c r="U24" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V24" t="n">
         <v>2.72</v>
@@ -5079,22 +5079,22 @@
         <v>1.12</v>
       </c>
       <c r="X24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD24" t="n">
         <v>11</v>
@@ -5103,46 +5103,46 @@
         <v>22</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG24" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI24" t="n">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AO24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AP24" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT24" t="n">
         <v>18.5</v>
@@ -5151,44 +5151,44 @@
         <v>8.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX24" t="n">
-        <v>9.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="AY24" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="AZ24" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BA24" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="BB24" t="n">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="BC24" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>50</v>
+        <v>17.5</v>
       </c>
       <c r="BF24" t="n">
         <v>15</v>
       </c>
       <c r="BG24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -5219,61 +5219,61 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G25" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H25" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L25" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="M25" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N25" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P25" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S25" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U25" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="V25" t="n">
         <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25" t="n">
         <v>10.5</v>
@@ -5282,16 +5282,16 @@
         <v>44</v>
       </c>
       <c r="AA25" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC25" t="n">
         <v>7.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="AE25" t="n">
         <v>300</v>
@@ -5306,40 +5306,40 @@
         <v>42</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AK25" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="AO25" t="n">
         <v>600</v>
       </c>
       <c r="AP25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AS25" t="n">
-        <v>11.5</v>
+        <v>48</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU25" t="n">
         <v>6.4</v>
@@ -5348,41 +5348,41 @@
         <v>14</v>
       </c>
       <c r="AW25" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AX25" t="n">
         <v>12.5</v>
       </c>
       <c r="AY25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BF25" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ25" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BG25" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G26" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H26" t="n">
         <v>5.6</v>
@@ -5425,7 +5425,7 @@
         <v>6.8</v>
       </c>
       <c r="J26" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
         <v>4</v>
@@ -5437,34 +5437,34 @@
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
         <v>1.38</v>
       </c>
       <c r="P26" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q26" t="n">
         <v>2.16</v>
       </c>
       <c r="R26" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T26" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U26" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V26" t="n">
         <v>1.18</v>
       </c>
       <c r="W26" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="X26" t="n">
         <v>12.5</v>
@@ -5488,7 +5488,7 @@
         <v>26</v>
       </c>
       <c r="AE26" t="n">
-        <v>700</v>
+        <v>480</v>
       </c>
       <c r="AF26" t="n">
         <v>10.5</v>
@@ -5500,22 +5500,22 @@
         <v>24</v>
       </c>
       <c r="AI26" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AJ26" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK26" t="n">
         <v>22</v>
       </c>
       <c r="AL26" t="n">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="AM26" t="n">
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO26" t="n">
         <v>700</v>
@@ -5527,13 +5527,13 @@
         <v>14.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT26" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU26" t="n">
         <v>7.4</v>
@@ -5542,7 +5542,7 @@
         <v>20</v>
       </c>
       <c r="AW26" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX26" t="n">
         <v>8.199999999999999</v>
@@ -5554,7 +5554,7 @@
         <v>19</v>
       </c>
       <c r="BA26" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB26" t="n">
         <v>15</v>
@@ -5566,17 +5566,17 @@
         <v>36</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF26" t="n">
         <v>12</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -5607,76 +5607,76 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G27" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H27" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="I27" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="J27" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K27" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L27" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N27" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="O27" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="P27" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="R27" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="S27" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U27" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="V27" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X27" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="Z27" t="n">
         <v>11.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AB27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD27" t="n">
         <v>11.5</v>
@@ -5685,16 +5685,16 @@
         <v>48</v>
       </c>
       <c r="AF27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG27" t="n">
         <v>21</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AI27" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AJ27" t="n">
         <v>900</v>
@@ -5709,16 +5709,16 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="AP27" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AR27" t="n">
         <v>9.4</v>
@@ -5727,50 +5727,50 @@
         <v>20</v>
       </c>
       <c r="AT27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU27" t="n">
         <v>6.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW27" t="n">
         <v>21</v>
       </c>
       <c r="AX27" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="BB27" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BD27" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE27" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -5801,19 +5801,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G28" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H28" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J28" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K28" t="n">
         <v>3.9</v>
@@ -5825,7 +5825,7 @@
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>1.44</v>
@@ -5843,19 +5843,19 @@
         <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U28" t="n">
         <v>1.62</v>
       </c>
       <c r="V28" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W28" t="n">
         <v>2.56</v>
       </c>
       <c r="X28" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="Y28" t="n">
         <v>1000</v>
@@ -5867,10 +5867,10 @@
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD28" t="n">
         <v>1000</v>
@@ -5879,13 +5879,13 @@
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="AG28" t="n">
         <v>40</v>
       </c>
       <c r="AH28" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="AI28" t="n">
         <v>1000</v>
@@ -5909,7 +5909,7 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ28" t="n">
         <v>6.8</v>
@@ -5921,10 +5921,10 @@
         <v>10</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AV28" t="n">
         <v>7.8</v>
@@ -5933,7 +5933,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AX28" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AY28" t="n">
         <v>5.3</v>
@@ -5942,29 +5942,29 @@
         <v>7.8</v>
       </c>
       <c r="BA28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC28" t="n">
         <v>7</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BG28" t="n">
         <v>10</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G29" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H29" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J29" t="n">
         <v>3.45</v>
@@ -6013,16 +6013,16 @@
         <v>3.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P29" t="n">
         <v>2</v>
@@ -6043,31 +6043,31 @@
         <v>2.3</v>
       </c>
       <c r="V29" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W29" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X29" t="n">
         <v>14.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA29" t="n">
         <v>50</v>
       </c>
       <c r="AB29" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE29" t="n">
         <v>34</v>
@@ -6079,25 +6079,25 @@
         <v>11.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI29" t="n">
         <v>40</v>
       </c>
       <c r="AJ29" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK29" t="n">
         <v>25</v>
       </c>
       <c r="AL29" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM29" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN29" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO29" t="n">
         <v>32</v>
@@ -6106,7 +6106,7 @@
         <v>14</v>
       </c>
       <c r="AQ29" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR29" t="n">
         <v>19.5</v>
@@ -6118,10 +6118,10 @@
         <v>10.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW29" t="n">
         <v>32</v>
@@ -6133,7 +6133,7 @@
         <v>11</v>
       </c>
       <c r="AZ29" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA29" t="n">
         <v>38</v>
@@ -6151,14 +6151,14 @@
         <v>65</v>
       </c>
       <c r="BF29" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G30" t="n">
         <v>2.52</v>
@@ -6198,10 +6198,10 @@
         <v>3.4</v>
       </c>
       <c r="I30" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="J30" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K30" t="n">
         <v>3.35</v>
@@ -6231,13 +6231,13 @@
         <v>5.6</v>
       </c>
       <c r="T30" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U30" t="n">
         <v>1.76</v>
       </c>
       <c r="V30" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W30" t="n">
         <v>1.66</v>
@@ -6297,7 +6297,7 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ30" t="n">
         <v>8.4</v>
@@ -6306,7 +6306,7 @@
         <v>19.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="AT30" t="n">
         <v>6.2</v>
@@ -6315,10 +6315,10 @@
         <v>6</v>
       </c>
       <c r="AV30" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AW30" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="AX30" t="n">
         <v>11.5</v>
@@ -6327,32 +6327,32 @@
         <v>10</v>
       </c>
       <c r="AZ30" t="n">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="BA30" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB30" t="n">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BC30" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="BD30" t="n">
-        <v>8.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="BE30" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF30" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG30" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="G31" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="H31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I31" t="n">
         <v>3.75</v>
-      </c>
-      <c r="I31" t="n">
-        <v>4.1</v>
       </c>
       <c r="J31" t="n">
         <v>2.92</v>
@@ -6401,46 +6401,46 @@
         <v>3.1</v>
       </c>
       <c r="L31" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="M31" t="n">
         <v>1.14</v>
       </c>
       <c r="N31" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O31" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="P31" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="R31" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="T31" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U31" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="V31" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W31" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="X31" t="n">
         <v>8.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>11</v>
+        <v>500</v>
       </c>
       <c r="Z31" t="n">
         <v>980</v>
@@ -6452,7 +6452,7 @@
         <v>7.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD31" t="n">
         <v>500</v>
@@ -6467,7 +6467,7 @@
         <v>28</v>
       </c>
       <c r="AH31" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="AI31" t="n">
         <v>500</v>
@@ -6476,7 +6476,7 @@
         <v>500</v>
       </c>
       <c r="AK31" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL31" t="n">
         <v>500</v>
@@ -6488,31 +6488,31 @@
         <v>980</v>
       </c>
       <c r="AO31" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP31" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AR31" t="n">
-        <v>19</v>
+        <v>7.4</v>
       </c>
       <c r="AS31" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW31" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX31" t="n">
         <v>11.5</v>
@@ -6524,29 +6524,29 @@
         <v>15</v>
       </c>
       <c r="BA31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC31" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD31" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE31" t="n">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BF31" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG31" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G32" t="n">
         <v>1.59</v>
       </c>
       <c r="H32" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I32" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J32" t="n">
         <v>4.1</v>
@@ -6610,7 +6610,7 @@
         <v>1.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R32" t="n">
         <v>1.32</v>
@@ -6619,25 +6619,25 @@
         <v>3.9</v>
       </c>
       <c r="T32" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U32" t="n">
         <v>1.78</v>
       </c>
       <c r="V32" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W32" t="n">
         <v>2.68</v>
       </c>
       <c r="X32" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y32" t="n">
         <v>23</v>
       </c>
       <c r="Z32" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA32" t="n">
         <v>280</v>
@@ -6646,7 +6646,7 @@
         <v>7.2</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD32" t="n">
         <v>32</v>
@@ -6655,7 +6655,7 @@
         <v>150</v>
       </c>
       <c r="AF32" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG32" t="n">
         <v>10.5</v>
@@ -6667,10 +6667,10 @@
         <v>150</v>
       </c>
       <c r="AJ32" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK32" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL32" t="n">
         <v>46</v>
@@ -6685,16 +6685,16 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ32" t="n">
         <v>19.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>8.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="AS32" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT32" t="n">
         <v>6.4</v>
@@ -6706,19 +6706,19 @@
         <v>22</v>
       </c>
       <c r="AW32" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AX32" t="n">
         <v>7.4</v>
       </c>
       <c r="AY32" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
         <v>20</v>
       </c>
       <c r="BA32" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BB32" t="n">
         <v>12.5</v>
@@ -6727,20 +6727,20 @@
         <v>15.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="BE32" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF32" t="n">
         <v>9</v>
       </c>
       <c r="BG32" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-05 07:22:34</t>
+          <t>2026-03-05 09:40:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:16:06</t>
+          <t>10:48:12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dobrudzha</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.08</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>1.09</v>
+        <v>70</v>
       </c>
       <c r="H2" t="n">
-        <v>110</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>170</v>
+        <v>1.11</v>
       </c>
       <c r="J2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -781,35 +781,35 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.87</v>
+        <v>3.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>1.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>4.8</v>
+        <v>2.78</v>
       </c>
       <c r="T2" t="n">
-        <v>4.2</v>
+        <v>1.96</v>
       </c>
       <c r="U2" t="n">
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.01</v>
       </c>
-      <c r="W2" t="n">
-        <v>12</v>
-      </c>
       <c r="X2" t="n">
         <v>1000</v>
       </c>
@@ -817,117 +817,117 @@
         <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
         <v>5.2</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AE2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>460</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>21</v>
       </c>
-      <c r="AD2" t="n">
-        <v>190</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>190</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1000</v>
-      </c>
       <c r="AR2" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="AU2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AV2" t="n">
-        <v>120</v>
+        <v>4.9</v>
       </c>
       <c r="AW2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF2" t="n">
         <v>130</v>
       </c>
-      <c r="AX2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>80</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>140</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>100</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>7</v>
-      </c>
       <c r="BG2" t="n">
-        <v>100</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-05 09:40:36</t>
+          <t>2026-03-05 12:03:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Italian Serie D</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10:45:00</t>
+          <t>11:01:17</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Enna Calcio</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Club Atletico Palermo</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.9</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1</v>
+        <v>900</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2</v>
+        <v>1.07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.28</v>
+        <v>1.09</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>13.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V3" t="n">
+        <v>12</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>410</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AW3" t="n">
         <v>3.15</v>
       </c>
-      <c r="O3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>23</v>
-      </c>
       <c r="AX3" t="n">
-        <v>24</v>
+        <v>2.06</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>2.06</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17.5</v>
+        <v>4</v>
       </c>
       <c r="BA3" t="n">
-        <v>44</v>
+        <v>4.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>48</v>
+        <v>2.06</v>
       </c>
       <c r="BC3" t="n">
-        <v>44</v>
+        <v>2.06</v>
       </c>
       <c r="BD3" t="n">
-        <v>40</v>
+        <v>4.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>70</v>
+        <v>2.04</v>
       </c>
       <c r="BF3" t="n">
-        <v>55</v>
+        <v>2.06</v>
       </c>
       <c r="BG3" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-05 09:40:36</t>
+          <t>2026-03-05 12:03:07</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Italian Serie D</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Enna Calcio</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Club Atletico Palermo</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.98</v>
+        <v>2.24</v>
       </c>
       <c r="G4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
         <v>3.3</v>
       </c>
-      <c r="H4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N4" t="n">
         <v>3.65</v>
       </c>
-      <c r="K4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.85</v>
-      </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
         <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.28</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.24</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.29</v>
+        <v>23</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.3</v>
+        <v>65</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.28</v>
+        <v>8.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.19</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.26</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.27</v>
+        <v>40</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.29</v>
+        <v>12</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.28</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.27</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.3</v>
+        <v>46</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.29</v>
+        <v>25</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.29</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.3</v>
+        <v>34</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.3</v>
+        <v>29</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.55</v>
+        <v>16</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.55</v>
+        <v>25</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-05 09:40:36</t>
+          <t>2026-03-05 12:03:07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,186 +1330,186 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>NK Aluminij</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.18</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.26</v>
+        <v>5.7</v>
       </c>
       <c r="H5" t="n">
-        <v>3.85</v>
+        <v>1.61</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>1.65</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>3.65</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>3.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.06</v>
+        <v>1.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.34</v>
+        <v>1.89</v>
       </c>
       <c r="S5" t="n">
-        <v>3.7</v>
+        <v>2.04</v>
       </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="V5" t="n">
-        <v>1.31</v>
+        <v>2.52</v>
       </c>
       <c r="W5" t="n">
-        <v>1.79</v>
+        <v>1.21</v>
       </c>
       <c r="X5" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC5" t="n">
         <v>13</v>
       </c>
-      <c r="Y5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AD5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD5" t="n">
         <v>28</v>
       </c>
-      <c r="AA5" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ5" t="n">
+      <c r="BE5" t="n">
+        <v>24</v>
+      </c>
+      <c r="BF5" t="n">
         <v>29</v>
       </c>
-      <c r="AK5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BG5" t="n">
-        <v>11.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-05 09:40:36</t>
+          <t>2026-03-05 12:03:07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,184 +1519,184 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NK Aluminij</t>
+          <t>FC Giugliano</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.8</v>
+        <v>2.76</v>
       </c>
       <c r="G6" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S6" t="n">
         <v>5.5</v>
       </c>
-      <c r="H6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.04</v>
-      </c>
       <c r="T6" t="n">
-        <v>1.5</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>2.72</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>2.46</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="X6" t="n">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>24</v>
+        <v>9.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AA6" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
-        <v>15.5</v>
+        <v>980</v>
       </c>
       <c r="AF6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI6" t="n">
         <v>500</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AJ6" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK6" t="n">
         <v>48</v>
       </c>
-      <c r="AH6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>700</v>
-      </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>5.6</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="AR6" t="n">
         <v>12.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AT6" t="n">
-        <v>16.5</v>
+        <v>7.2</v>
       </c>
       <c r="AU6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX6" t="n">
         <v>11</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AY6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG6" t="n">
         <v>9.4</v>
       </c>
-      <c r="AW6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>24</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-05 09:40:36</t>
+          <t>2026-03-05 12:03:07</t>
         </is>
       </c>
     </row>
@@ -1718,179 +1718,179 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S.S.D. Casarano Calcio</t>
+          <t>US Latina Calcio</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2.2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I7" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>2.56</v>
       </c>
       <c r="O7" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="P7" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>3.65</v>
+        <v>5.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.76</v>
+        <v>2.24</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
         <v>1.73</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AA7" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AE7" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>18.5</v>
+        <v>46</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>32</v>
+        <v>170</v>
       </c>
       <c r="AK7" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AL7" t="n">
-        <v>42</v>
+        <v>380</v>
       </c>
       <c r="AM7" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="AO7" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR7" t="n">
         <v>22</v>
       </c>
       <c r="AS7" t="n">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="AU7" t="n">
         <v>6.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AW7" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="AX7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BA7" t="n">
-        <v>44</v>
+        <v>9.4</v>
       </c>
       <c r="BB7" t="n">
         <v>15</v>
       </c>
       <c r="BC7" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BG7" t="n">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-05 09:40:36</t>
+          <t>2026-03-05 12:03:07</t>
         </is>
       </c>
     </row>
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>US Latina Calcio</t>
+          <t>S.S.D. Casarano Calcio</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.52</v>
+        <v>1.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.68</v>
+        <v>2.04</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>5.6</v>
+        <v>3.65</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>1.78</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB8" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF8" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI8" t="n">
         <v>60</v>
       </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>170</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="AL8" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU8" t="n">
         <v>6.8</v>
       </c>
       <c r="AV8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>15</v>
       </c>
-      <c r="AW8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>13</v>
-      </c>
       <c r="BA8" t="n">
-        <v>9.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BB8" t="n">
         <v>15</v>
       </c>
       <c r="BC8" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BD8" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BE8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-05 09:40:36</t>
+          <t>2026-03-05 12:03:07</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Estonian Esiliiga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,97 +2106,97 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FC Giugliano</t>
+          <t>JK Welco Elekter</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.78</v>
+        <v>1.92</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="I9" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>2.66</v>
+        <v>6.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="P9" t="n">
-        <v>1.53</v>
+        <v>2.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.62</v>
+        <v>1.44</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>1.8</v>
       </c>
       <c r="S9" t="n">
-        <v>5.6</v>
+        <v>2.08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="U9" t="n">
-        <v>1.79</v>
+        <v>2.54</v>
       </c>
       <c r="V9" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="W9" t="n">
-        <v>1.52</v>
+        <v>1.98</v>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>16</v>
+        <v>500</v>
       </c>
       <c r="Z9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>17.5</v>
+        <v>130</v>
       </c>
       <c r="AC9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>48</v>
+        <v>190</v>
       </c>
       <c r="AG9" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AH9" t="n">
         <v>60</v>
@@ -2205,87 +2205,87 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK9" t="n">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT9" t="n">
         <v>7</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT9" t="n">
+      <c r="AU9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG9" t="n">
         <v>5.3</v>
       </c>
-      <c r="AU9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-05 09:40:36</t>
+          <t>2026-03-05 12:03:07</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Estonian Esiliiga</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JK Welco Elekter</t>
+          <t>AZ Picerno ASD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Atalanta B</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.16</v>
+        <v>2.76</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>2.98</v>
+        <v>2.6</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>7.2</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>3.15</v>
+        <v>1.82</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.39</v>
+        <v>2.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.89</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>1.98</v>
+        <v>3.85</v>
       </c>
       <c r="T10" t="n">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="U10" t="n">
-        <v>2.88</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W10" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR10" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.6</v>
+        <v>36</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.7</v>
+        <v>9.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="AX10" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.5</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.5</v>
+        <v>38</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.6</v>
+        <v>25</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.7</v>
+        <v>40</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.4</v>
+        <v>28</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.25</v>
+        <v>15</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.35</v>
+        <v>8.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-05 09:40:36</t>
+          <t>2026-03-05 12:03:07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,184 +2489,184 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AZ Picerno ASD</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atalanta B</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.76</v>
+        <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="H11" t="n">
-        <v>2.62</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
-        <v>2.96</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
         <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>2.86</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="Q11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.08</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.79</v>
-      </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="V11" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="X11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF11" t="n">
         <v>13</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AG11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF11" t="n">
+      <c r="AR11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>20</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>15</v>
       </c>
       <c r="BA11" t="n">
         <v>38</v>
       </c>
       <c r="BB11" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BC11" t="n">
-        <v>9.4</v>
+        <v>26</v>
       </c>
       <c r="BD11" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BE11" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="BF11" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.6</v>
+        <v>60</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-05 09:40:36</t>
+          <t>2026-03-05 12:03:07</t>
         </is>
       </c>
     </row>
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.34</v>
+        <v>7.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="H12" t="n">
-        <v>3.65</v>
+        <v>1.47</v>
       </c>
       <c r="I12" t="n">
-        <v>3.85</v>
+        <v>1.49</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>2.92</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="P12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.66</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.23</v>
-      </c>
       <c r="S12" t="n">
-        <v>4.9</v>
+        <v>2.42</v>
       </c>
       <c r="T12" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>3.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.72</v>
+        <v>1.15</v>
       </c>
       <c r="X12" t="n">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="AA12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF12" t="n">
         <v>75</v>
       </c>
-      <c r="AB12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>26</v>
       </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>240</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL12" t="n">
         <v>75</v>
       </c>
-      <c r="AJ12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>55</v>
-      </c>
       <c r="AM12" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AN12" t="n">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="AO12" t="n">
-        <v>70</v>
+        <v>5.6</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="AQ12" t="n">
         <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AY12" t="n">
         <v>23</v>
       </c>
-      <c r="AT12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BB12" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="BC12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BD12" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BE12" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="BF12" t="n">
-        <v>17.5</v>
+        <v>80</v>
       </c>
       <c r="BG12" t="n">
-        <v>48</v>
+        <v>5.1</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-05 09:40:36</t>
+          <t>2026-03-05 12:03:07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Cavese 1919</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I13" t="n">
         <v>7.2</v>
       </c>
-      <c r="G13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.48</v>
-      </c>
       <c r="J13" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>2.84</v>
       </c>
       <c r="O13" t="n">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="P13" t="n">
-        <v>2.66</v>
+        <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.57</v>
+        <v>2.46</v>
       </c>
       <c r="R13" t="n">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>2.46</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.77</v>
+        <v>2.22</v>
       </c>
       <c r="U13" t="n">
-        <v>2.16</v>
+        <v>1.7</v>
       </c>
       <c r="V13" t="n">
-        <v>3</v>
+        <v>1.16</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>2.22</v>
       </c>
       <c r="X13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y13" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV13" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AW13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC13" t="n">
         <v>10.5</v>
       </c>
-      <c r="AA13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="BD13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG13" t="n">
         <v>12</v>
       </c>
-      <c r="AD13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>200</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>60</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>60</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-05 09:40:36</t>
+          <t>2026-03-05 12:03:07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>FC Basel</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cavese 1919</t>
+          <t>Grasshoppers Zurich</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G14" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="M14" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>1.59</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
-        <v>1.21</v>
+        <v>1.51</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="T14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W14" t="n">
         <v>2.26</v>
       </c>
-      <c r="U14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.16</v>
-      </c>
       <c r="X14" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+